--- a/dev/dane/import-do-arkusza.xlsx
+++ b/dev/dane/import-do-arkusza.xlsx
@@ -1091,7 +1091,11 @@
           <t>p07, p51, p21, p01</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>/img/produkty/p06-800.webp</t>
+        </is>
+      </c>
       <c r="V7" t="n">
         <v>6</v>
       </c>
@@ -1186,7 +1190,11 @@
           <t>p06, p01, p02, p14</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>/img/produkty/p07-800.webp</t>
+        </is>
+      </c>
       <c r="V8" t="n">
         <v>7</v>
       </c>
@@ -1281,7 +1289,11 @@
           <t>p40, p43, p22, p46, p45</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>/img/produkty/p08-800.webp</t>
+        </is>
+      </c>
       <c r="V9" t="n">
         <v>8</v>
       </c>
@@ -1376,7 +1388,11 @@
           <t>p01, p10, p27, p33</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>/img/produkty/p09-800.webp</t>
+        </is>
+      </c>
       <c r="V10" t="n">
         <v>9</v>
       </c>
@@ -1471,7 +1487,11 @@
           <t>p35, p28, p09</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>/img/produkty/p10-800.webp</t>
+        </is>
+      </c>
       <c r="V11" t="n">
         <v>10</v>
       </c>
@@ -1566,7 +1586,11 @@
           <t>p12, p22, p52</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>/img/produkty/p11-800.webp</t>
+        </is>
+      </c>
       <c r="V12" t="n">
         <v>11</v>
       </c>
@@ -1659,7 +1683,11 @@
           <t>p11, p52, p53, p22</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>/img/produkty/p12-800.webp</t>
+        </is>
+      </c>
       <c r="V13" t="n">
         <v>12</v>
       </c>
@@ -1845,7 +1873,11 @@
           <t>p07, p51, p21</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>/img/produkty/p14-800.webp</t>
+        </is>
+      </c>
       <c r="V15" t="n">
         <v>14</v>
       </c>
@@ -1940,7 +1972,11 @@
           <t>p20, p59, p36</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>/img/produkty/p15-800.webp</t>
+        </is>
+      </c>
       <c r="V16" t="n">
         <v>15</v>
       </c>
@@ -2035,7 +2071,11 @@
           <t>p09, p15</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>/img/produkty/p16-800.webp</t>
+        </is>
+      </c>
       <c r="V17" t="n">
         <v>16</v>
       </c>
@@ -2130,7 +2170,11 @@
           <t>p19, p05, p49, p38</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>/img/produkty/p17-800.webp</t>
+        </is>
+      </c>
       <c r="V18" t="n">
         <v>17</v>
       </c>
@@ -2316,7 +2360,11 @@
           <t>p17, p05, p38</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>/img/produkty/p19-800.webp</t>
+        </is>
+      </c>
       <c r="V20" t="n">
         <v>19</v>
       </c>
@@ -2411,7 +2459,11 @@
           <t>p15, p36, p49</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>/img/produkty/p20-800.webp</t>
+        </is>
+      </c>
       <c r="V21" t="n">
         <v>20</v>
       </c>
@@ -2504,7 +2556,11 @@
           <t>p02, p51, p07, p62</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>/img/produkty/p21-800.webp</t>
+        </is>
+      </c>
       <c r="V22" t="n">
         <v>21</v>
       </c>
@@ -2597,7 +2653,11 @@
           <t>p11, p52, p44</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>/img/produkty/p22-800.webp</t>
+        </is>
+      </c>
       <c r="V23" t="n">
         <v>22</v>
       </c>
@@ -2690,7 +2750,11 @@
           <t>p14, p02, p47</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>/img/produkty/p23-800.webp</t>
+        </is>
+      </c>
       <c r="V24" t="n">
         <v>23</v>
       </c>
@@ -2783,7 +2847,11 @@
           <t>p28, p10, p70</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>/img/produkty/p24-800.webp</t>
+        </is>
+      </c>
       <c r="V25" t="n">
         <v>24</v>
       </c>
@@ -2876,7 +2944,11 @@
           <t>p10, p35, p04, p28</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>/img/produkty/p25-800.webp</t>
+        </is>
+      </c>
       <c r="V26" t="n">
         <v>25</v>
       </c>
@@ -3060,7 +3132,11 @@
           <t>p29, p10, p24</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>/img/produkty/p27-800.webp</t>
+        </is>
+      </c>
       <c r="V28" t="n">
         <v>27</v>
       </c>
@@ -3153,7 +3229,11 @@
           <t>p29, p25, p10, p04</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>/img/produkty/p28-800.webp</t>
+        </is>
+      </c>
       <c r="V29" t="n">
         <v>28</v>
       </c>
@@ -3246,7 +3326,11 @@
           <t>p28, p08, p27, p24, p10</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>/img/produkty/p29-800.webp</t>
+        </is>
+      </c>
       <c r="V30" t="n">
         <v>29</v>
       </c>
@@ -3339,7 +3423,11 @@
           <t>p28, p41, p60, p05, p25</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>/img/produkty/p30-800.webp</t>
+        </is>
+      </c>
       <c r="V31" t="n">
         <v>30</v>
       </c>
@@ -3432,7 +3520,11 @@
           <t>p16, p43, p11, p20, p36</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>/img/produkty/p31-800.webp</t>
+        </is>
+      </c>
       <c r="V32" t="n">
         <v>31</v>
       </c>
@@ -3525,7 +3617,11 @@
           <t>p04, p38, p61, p25</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>/img/produkty/p32-800.webp</t>
+        </is>
+      </c>
       <c r="V33" t="n">
         <v>32</v>
       </c>
@@ -3618,7 +3714,11 @@
           <t>p38, p09, p10, p64</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>/img/produkty/p33-800.webp</t>
+        </is>
+      </c>
       <c r="V34" t="n">
         <v>33</v>
       </c>
@@ -3709,7 +3809,11 @@
           <t>p24, p27, p10</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>/img/produkty/p34-800.webp</t>
+        </is>
+      </c>
       <c r="V35" t="n">
         <v>34</v>
       </c>
@@ -3804,7 +3908,11 @@
           <t>p10, p25, p04</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>/img/produkty/p35-800.webp</t>
+        </is>
+      </c>
       <c r="V36" t="n">
         <v>35</v>
       </c>
@@ -3897,7 +4005,11 @@
           <t>p20, p15, p44</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>/img/produkty/p36-800.webp</t>
+        </is>
+      </c>
       <c r="V37" t="n">
         <v>36</v>
       </c>
@@ -3988,7 +4100,11 @@
           <t>p36, p20, p44</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>/img/produkty/p37-800.webp</t>
+        </is>
+      </c>
       <c r="V38" t="n">
         <v>37</v>
       </c>
@@ -4083,7 +4199,11 @@
           <t>p19, p05, p32, p17</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>/img/produkty/p38-800.webp</t>
+        </is>
+      </c>
       <c r="V39" t="n">
         <v>38</v>
       </c>
@@ -4176,7 +4296,11 @@
           <t>p44, p15, p36, p41</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>/img/produkty/p39-800.webp</t>
+        </is>
+      </c>
       <c r="V40" t="n">
         <v>39</v>
       </c>
@@ -4269,7 +4393,11 @@
           <t>p08, p48, p28</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>/img/produkty/p40-800.webp</t>
+        </is>
+      </c>
       <c r="V41" t="n">
         <v>40</v>
       </c>
@@ -4364,7 +4492,11 @@
           <t>p05, p49, p04</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>/img/produkty/p41-800.webp</t>
+        </is>
+      </c>
       <c r="V42" t="n">
         <v>41</v>
       </c>
@@ -4647,7 +4779,11 @@
           <t>p39, p65, p49</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>/img/produkty/p44-800.webp</t>
+        </is>
+      </c>
       <c r="V45" t="n">
         <v>44</v>
       </c>
@@ -4740,7 +4876,11 @@
           <t>p01, p09, p46</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>/img/produkty/p45-800.webp</t>
+        </is>
+      </c>
       <c r="V46" t="n">
         <v>45</v>
       </c>
@@ -4833,7 +4973,11 @@
           <t>p01, p45, p09</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>/img/produkty/p46-800.webp</t>
+        </is>
+      </c>
       <c r="V47" t="n">
         <v>46</v>
       </c>
@@ -4926,7 +5070,11 @@
           <t>p07, p23, p02</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>/img/produkty/p47-800.webp</t>
+        </is>
+      </c>
       <c r="V48" t="n">
         <v>47</v>
       </c>
@@ -5019,7 +5167,11 @@
           <t>p40, p08</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>/img/produkty/p48-800.webp</t>
+        </is>
+      </c>
       <c r="V49" t="n">
         <v>48</v>
       </c>
@@ -5112,7 +5264,11 @@
           <t>p39, p41, p20</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>/img/produkty/p49-800.webp</t>
+        </is>
+      </c>
       <c r="V50" t="n">
         <v>49</v>
       </c>
@@ -5205,7 +5361,11 @@
           <t>p49, p33</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>/img/produkty/p50-800.webp</t>
+        </is>
+      </c>
       <c r="V51" t="n">
         <v>50</v>
       </c>
@@ -5958,7 +6118,11 @@
           <t>p60, p54, p38</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr"/>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>/img/produkty/p59-800.webp</t>
+        </is>
+      </c>
       <c r="V60" t="n">
         <v>59</v>
       </c>
@@ -6144,7 +6308,11 @@
           <t>p32, p59, p70</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr"/>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>/img/produkty/p61-800.webp</t>
+        </is>
+      </c>
       <c r="V62" t="n">
         <v>61</v>
       </c>
@@ -6237,7 +6405,11 @@
           <t>p51, p21, p22</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr"/>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>/img/produkty/p62-800.webp</t>
+        </is>
+      </c>
       <c r="V63" t="n">
         <v>62</v>
       </c>
@@ -6607,7 +6779,11 @@
           <t>p55, p63</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr"/>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>/img/produkty/p66-800.webp</t>
+        </is>
+      </c>
       <c r="V67" t="n">
         <v>66</v>
       </c>
@@ -6698,7 +6874,11 @@
           <t>p14, p46</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr"/>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>/img/produkty/p67-800.webp</t>
+        </is>
+      </c>
       <c r="V68" t="n">
         <v>67</v>
       </c>
@@ -6789,7 +6969,11 @@
           <t>p55, p59</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr"/>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>/img/produkty/p68-800.webp</t>
+        </is>
+      </c>
       <c r="V69" t="n">
         <v>68</v>
       </c>
@@ -6880,7 +7064,11 @@
           <t>p51, p14, p06</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr"/>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>/img/produkty/p69-800.webp</t>
+        </is>
+      </c>
       <c r="V70" t="n">
         <v>69</v>
       </c>
@@ -6973,7 +7161,11 @@
           <t>p71, p10, p61</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr"/>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>/img/produkty/p70-800.webp</t>
+        </is>
+      </c>
       <c r="V71" t="n">
         <v>70</v>
       </c>
@@ -7066,7 +7258,11 @@
           <t>p52, p70, p59</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr"/>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>/img/produkty/p71-800.webp</t>
+        </is>
+      </c>
       <c r="V72" t="n">
         <v>71</v>
       </c>
@@ -7331,7 +7527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7397,32 +7593,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>p02</t>
+          <t>p01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Louis Vuitton Pacific Chill</t>
+          <t>Louis Vuitton Imagination</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>sezon</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Lato (upały), późna wiosna</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>wiosna, lato</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
@@ -7439,182 +7627,166 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>Lato (upały), późna wiosna</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>wiosna, lato</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p03</t>
+          <t>p02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Louis Vuitton Afternoon Swim</t>
+          <t>Louis Vuitton Pacific Chill</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>p05</t>
+          <t>p02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Louis Vuitton Ombre Nomade</t>
+          <t>Louis Vuitton Pacific Chill</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Agarowo-różana</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>orientalna</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>p05</t>
+          <t>p03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Louis Vuitton Ombre Nomade</t>
+          <t>Louis Vuitton Afternoon Swim</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Amouage Otlands -&gt; otlands</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>p06</t>
+          <t>p03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Xerjoff Torino21</t>
+          <t>Louis Vuitton Afternoon Swim</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>podobne</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>p07</t>
+          <t>p04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance (XJ 1861)</t>
+          <t>Louis Vuitton Nouveau Monde</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sezon</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Wiosna, lato, wczesna jesień</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>wiosna, lato, jesień</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>p08</t>
+          <t>p05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Xerjoff Erba Pura</t>
+          <t>Louis Vuitton Ombre Nomade</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7624,12 +7796,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Owocowo-ambrowa</t>
+          <t>Agarowo-różana</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ambrowa</t>
+          <t>orientalna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -7641,584 +7813,568 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>p08</t>
+          <t>p05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Xerjoff Erba Pura</t>
+          <t>Louis Vuitton Ombre Nomade</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i lato</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>wiosna, lato, jesień, zima</t>
-        </is>
-      </c>
+          <t>Amouage Otlands -&gt; otlands</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>p09</t>
+          <t>p05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Xerjoff Uden</t>
+          <t>Louis Vuitton Ombre Nomade</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sezon</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Jesień, zima, wczesna wiosna</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>wiosna, jesień, zima</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>p09</t>
+          <t>p06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Xerjoff Uden</t>
+          <t>Xerjoff Torino21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wieczór, chłodny dzień</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>uniwersalna</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Creed Aventus</t>
+          <t>Xerjoff Renaissance (XJ 1861)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Owocowo-drzewna</t>
+          <t>Wiosna, lato, wczesna jesień</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>wiosna, lato, jesień</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Creed Aventus</t>
+          <t>Xerjoff Erba Pura</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
+          <t>Owocowo-ambrowa</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>ambrowa</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Creed Absolu Aventus</t>
+          <t>Xerjoff Erba Pura</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Cały rok, najlepiej wiosna i lato</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Creed Absolu Aventus</t>
+          <t>Xerjoff Uden</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>owocowo-drzewna</t>
+          <t>Jesień, zima, wczesna wiosna</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>wiosna, jesień, zima</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>p13</t>
+          <t>p09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Creed Virgin Island Water</t>
+          <t>Xerjoff Uden</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nazwa</t>
+          <t>pora</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Virgin Island Water</t>
+          <t>Wieczór, chłodny dzień</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Virgin Island Water</t>
+          <t>uniwersalna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>nazwa do potwierdzenia (w ofercie „Virgin Mountain Water”)</t>
+          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>p13</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Creed Virgin Island Water</t>
+          <t>Creed Aventus</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
+          <t>Owocowo-drzewna</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>p14</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Creed Silver Mountain Water</t>
+          <t>Creed Aventus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>zielono-herbaciana</t>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>świeża</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>p14</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Creed Silver Mountain Water</t>
+          <t>Creed Absolu Aventus</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Amouage Search</t>
+          <t>Creed Absolu Aventus</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wiosna, jesień (uniwersalny)</t>
+          <t>owocowo-drzewna</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>wiosna, jesień</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Amouage Search</t>
+          <t>Creed Virgin Island Water</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ceny</t>
+          <t>nazwa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5 ml – 120 zł | 10 ml – 220 zł | 20 ml – 400 zł (promocja)</t>
+          <t>Virgin Island Water</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5 ml 120 zł | 10 ml 220 zł | 20 ml 400 zł</t>
+          <t>Virgin Island Water</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>cena oznaczona jako promocja; API nie ma pola na starą cenę, pokażemy ją jako zwykłą</t>
+          <t>nazwa do potwierdzenia (w ofercie „Virgin Mountain Water”)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Amouage Reflection Man</t>
+          <t>Creed Virgin Island Water</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
+          <t>NIEDOSTĘPNY</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amouage Interlude Black Iris</t>
+          <t>Creed Silver Mountain Water</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>pewność danych: niska</t>
+          <t>zielono-herbaciana</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>świeża</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Amouage Interlude Black Iris</t>
+          <t>Creed Silver Mountain Water</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Irysowo-kadzidlana</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>kwiatowa</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Amouage Interlude Black Iris</t>
+          <t>Amouage Search</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
+          <t>Wiosna, jesień (uniwersalny)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>wiosna, jesień</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Amouage Interlude Man</t>
+          <t>Amouage Search</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>ceny</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Dymno-żywiczna</t>
+          <t>5 ml – 120 zł | 10 ml – 220 zł | 20 ml – 400 zł (promocja)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>5 ml 120 zł | 10 ml 220 zł | 20 ml 400 zł</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>cena oznaczona jako promocja; API nie ma pola na starą cenę, pokażemy ją jako zwykłą</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Amouage Interlude Man</t>
+          <t>Amouage Reflection Man</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8228,12 +8384,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Zima, późna jesień</t>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>jesień, zima</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -8245,232 +8401,232 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>p21</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mancera Lemon Line</t>
+          <t>Amouage Interlude Black Iris</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>aktywny</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>pewność danych: niska</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>p21</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mancera Lemon Line</t>
+          <t>Amouage Interlude Black Iris</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>Irysowo-kadzidlana</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>kwiatowa</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>p24</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mancera Tonka Cola</t>
+          <t>Amouage Interlude Black Iris</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>NIEDOSTĘPNY</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mancera Red Tobacco</t>
+          <t>Amouage Interlude Man</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Dymno-żywiczna</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mancera Red Tobacco</t>
+          <t>Amouage Interlude Man</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Korzenna</t>
+          <t>Zima, późna jesień</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>orientalna</t>
+          <t>jesień, zima</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>p26</t>
+          <t>p21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mancera Instant Crush</t>
+          <t>Mancera Lemon Line</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>pewność danych: niska</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>p26</t>
+          <t>p21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mancera Instant Crush</t>
+          <t>Mancera Lemon Line</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>p30</t>
+          <t>p24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Montale Honey Aoud</t>
+          <t>Mancera Tonka Cola</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -8497,100 +8653,108 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>p31</t>
+          <t>p25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Montale Intense Pepper</t>
+          <t>Mancera Red Tobacco</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Amouage Reflection -&gt; reflection</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>p32</t>
+          <t>p25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tom Ford Ombré Leather</t>
+          <t>Mancera Red Tobacco</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LV Nouvau Monde -&gt; nouvau monde</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>Korzenna</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>orientalna</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>p33</t>
+          <t>p26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tom Ford Noir Extreme</t>
+          <t>Mancera Instant Crush</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>aktywny</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Korzenno-gourmand</t>
+          <t>pewność danych: niska</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>gourmand</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>p34</t>
+          <t>p26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tom Ford Lost Cherry</t>
+          <t>Mancera Instant Crush</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -8617,544 +8781,536 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>p35</t>
+          <t>p30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tom Ford Tobacco Vanille</t>
+          <t>Montale Honey Aoud</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Korzenno-gourmand</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>gourmand</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>p36</t>
+          <t>p31</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tom Ford Bois Pacifique</t>
+          <t>Montale Intense Pepper</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Jesień, zima, wczesna wiosna</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>wiosna, jesień, zima</t>
-        </is>
-      </c>
+          <t>Amouage Reflection -&gt; reflection</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>p37</t>
+          <t>p32</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tom Ford Oud Wood</t>
+          <t>Tom Ford Ombré Leather</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>LV Nouvau Monde -&gt; nouvau monde</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>p38</t>
+          <t>p33</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tom Ford Ébène Fumé</t>
+          <t>Tom Ford Noir Extreme</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Korzenno-gourmand</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>gourmand</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>p38</t>
+          <t>p34</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tom Ford Ébène Fumé</t>
+          <t>Tom Ford Lost Cherry</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Dymno-drzewna</t>
+          <t>NIEDOSTĘPNY</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>p39</t>
+          <t>p35</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Marc-Antoine Barrois Ganymede</t>
+          <t>Tom Ford Tobacco Vanille</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wiosna, jesień (uniwersalny)</t>
+          <t>Korzenno-gourmand</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>wiosna, jesień</t>
+          <t>gourmand</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>p39</t>
+          <t>p36</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Marc-Antoine Barrois Ganymede</t>
+          <t>Tom Ford Bois Pacifique</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ceny</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5 ml – 70 zł | 10 ml – 140 zł (?) | 20 ml – 250 zł</t>
+          <t>Jesień, zima, wczesna wiosna</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5 ml 70 zł | 20 ml 250 zł</t>
+          <t>wiosna, jesień, zima</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>cena 10 ml oznaczona w źródle jako niepewna "(?)", wariant pominięty do potwierdzenia</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>p40</t>
+          <t>p37</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tiziana Terenzi Kirke</t>
+          <t>Tom Ford Oud Wood</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
+          <t>NIEDOSTĘPNY</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>p41</t>
+          <t>p38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Maison Crivelli Oud Maracujá</t>
+          <t>Tom Ford Ébène Fumé</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Owocowo-agarowa</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>słodka</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>p41</t>
+          <t>p38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Maison Crivelli Oud Maracujá</t>
+          <t>Tom Ford Ébène Fumé</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Jesień, zima, chłodna wiosna</t>
+          <t>Dymno-drzewna</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>wiosna, jesień, zima</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>p41</t>
+          <t>p39</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Maison Crivelli Oud Maracujá</t>
+          <t>Marc-Antoine Barrois Ganymede</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LV Nouvau Monde -&gt; nouvau monde</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>Wiosna, jesień (uniwersalny)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>wiosna, jesień</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p39</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
+          <t>Marc-Antoine Barrois Ganymede</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>ceny</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej jesień i zima</t>
+          <t>5 ml – 70 zł | 10 ml – 140 zł (?) | 20 ml – 250 zł</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>5 ml 70 zł | 20 ml 250 zł</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>cena 10 ml oznaczona w źródle jako niepewna "(?)", wariant pominięty do potwierdzenia</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p40</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
+          <t>Tiziana Terenzi Kirke</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wieczór (działa też w dzień)</t>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>uniwersalna</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>p44</t>
+          <t>p41</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Essential Parfums Bois Impérial</t>
+          <t>Maison Crivelli Oud Maracujá</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Nous Tous Saffrano Absolu -&gt; saffrano absolu</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>Owocowo-agarowa</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>słodka</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>p47</t>
+          <t>p41</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nous Tous Secco di Como</t>
+          <t>Maison Crivelli Oud Maracujá</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>Jesień, zima, chłodna wiosna</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>wiosna, jesień, zima</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>p48</t>
+          <t>p41</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nous Tous Aurora Siciliana</t>
+          <t>Maison Crivelli Oud Maracujá</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Owocowo-kwiatowa</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>kwiatowa</t>
-        </is>
-      </c>
+          <t>LV Nouvau Monde -&gt; nouvau monde</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>p50</t>
+          <t>p42</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nous Tous Milano 3AM</t>
+          <t>Maison Francis Kurkdjian Grand Soir</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>korzenna</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>orientalna</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>p50</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nous Tous Milano 3AM</t>
+          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -9164,7 +9320,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej chłodne wieczory</t>
+          <t>Cały rok, najlepiej jesień i zima</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -9181,401 +9337,433 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>p53</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dior Sauvage Elixir</t>
+          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>pora</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Korzenno-ambrowa</t>
+          <t>Wieczór (działa też w dzień)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ambrowa</t>
+          <t>uniwersalna</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>p55</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Versace Eros Parfum</t>
+          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p44</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>Essential Parfums Bois Impérial</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>marka, nazwa</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>podobne</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Nous Tous Saffrano Absolu -&gt; saffrano absolu</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>Nous Tous Secco di Como</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sezon</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>podobne</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p48</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>Nous Tous Aurora Siciliana</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>pora</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Owocowo-kwiatowa</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>kwiatowa</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p50</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>Nous Tous Milano 3AM</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>trwalosc</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>korzenna</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>orientalna</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p50</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>Nous Tous Milano 3AM</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>projekcja</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Cały rok, najlepiej chłodne wieczory</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień, zima</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p51</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>Dior Homme Cologne</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>marka, nazwa</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>Dior Sauvage Parfum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Korzenno-drzewna</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>drzewna</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p53</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>Dior Sauvage Elixir</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>sezon</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Korzenno-ambrowa</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>ambrowa</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p53</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>Dior Sauvage Elixir</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p54</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>Dior Sauvage Extrait</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>trwalosc</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p55</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>Versace Eros Parfum</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>projekcja</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p55</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>Versace Eros Parfum</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>marka, nazwa</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p56</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>wiersz Lp. 56 (bez nazwy)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>marka, nazwa</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p56</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>wiersz Lp. 56 (bez nazwy)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -9589,17 +9777,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p56</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>wiersz Lp. 56 (bez nazwy)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>trwalosc</t>
+          <t>pora</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -9613,17 +9801,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p56</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>wiersz Lp. 56 (bez nazwy)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>projekcja</t>
+          <t>trwalosc</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -9637,324 +9825,260 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p56</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>wiersz Lp. 56 (bez nazwy)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ceny</t>
+          <t>projekcja</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>brak cen</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>p59</t>
+          <t>p56</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Elixir</t>
+          <t>wiersz Lp. 56 (bez nazwy)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>p59</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Elixir</t>
+          <t>wiersz Lp. 57 (bez nazwy)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Korzenno-drzewna</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>drzewna</t>
-        </is>
-      </c>
+          <t>marka, nazwa</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>p60</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Absolu</t>
+          <t>wiersz Lp. 57 (bez nazwy)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>pewność danych: niska</t>
+          <t>Korzenno-drzewna</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>p60</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Absolu</t>
+          <t>wiersz Lp. 57 (bez nazwy)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Korzenno-gourmand</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>gourmand</t>
-        </is>
-      </c>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>p61</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Beyond</t>
+          <t>wiersz Lp. 57 (bez nazwy)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>pora</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>p63</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>YSL Y Parfum</t>
+          <t>wiersz Lp. 57 (bez nazwy)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>trwalosc</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>p63</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>YSL Y Parfum</t>
+          <t>wiersz Lp. 57 (bez nazwy)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>sezon</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>wiosna, lato, jesień, zima</t>
-        </is>
-      </c>
+          <t>projekcja</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>p64</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>YSL MYSLF Parfum</t>
+          <t>wiersz Lp. 57 (bez nazwy)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>p65</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
+          <t>wiersz Lp. 58 (bez nazwy)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>marka, nazwa</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>p65</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
+          <t>wiersz Lp. 58 (bez nazwy)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -9962,191 +10086,143 @@
           <t>sezon</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Wiosna, lato, wczesna jesień</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>wiosna, lato, jesień</t>
-        </is>
-      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>p66</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Rabanne Black XS</t>
+          <t>wiersz Lp. 58 (bez nazwy)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>pora</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>p66</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Rabanne Black XS</t>
+          <t>wiersz Lp. 58 (bez nazwy)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Korzenno-cytrusowa</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>cytrusowa</t>
-        </is>
-      </c>
+          <t>trwalosc</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>p68</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Rabanne One Million</t>
+          <t>wiersz Lp. 58 (bez nazwy)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Korzenno-słodka</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>słodka</t>
-        </is>
-      </c>
+          <t>projekcja</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>p69</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Azzaro Chrome</t>
+          <t>wiersz Lp. 58 (bez nazwy)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>ceny</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak cen</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>p70</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Azzaro Forever Wanted Elixir</t>
+          <t>wiersz Lp. 58 (bez nazwy)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>p71</t>
+          <t>p59</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Azzaro The Most Wanted Parfum</t>
+          <t>Hugo Boss Bottled Elixir</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10173,12 +10249,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>p71</t>
+          <t>p59</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Azzaro The Most Wanted Parfum</t>
+          <t>Hugo Boss Bottled Elixir</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10205,484 +10281,556 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>z01</t>
+          <t>p60</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>LV DISCOVERY SET</t>
+          <t>Hugo Boss Bottled Absolu</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
+          <t>aktywny</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>pewność danych: niska</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>z01</t>
+          <t>p60</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LV DISCOVERY SET</t>
+          <t>Hugo Boss Bottled Absolu</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Korzenno-gourmand</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>p60</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>Hugo Boss Bottled Absolu</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>5 × 5 ml (do ustalenia skład, sugerowane: Torino21, Renaissance, Erba Pura, Uden, Naxos)</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>p06:5, p07:5, p08:5, p09:5, p10:5</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>skład „do ustalenia”; wpisano propozycję ze źródła, zestaw wyłączony</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>p61</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>Hugo Boss Bottled Beyond</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>sklad</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr"/>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>p63</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>YSL Y Parfum</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>p63</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>YSL Y Parfum</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień, zima</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>z03</t>
+          <t>p63</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>NOUS TOUS DISCOVERY SET</t>
+          <t>YSL Y Parfum</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>cena</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>350 zł</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>cena zapisana jako tekst</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>z03</t>
+          <t>p64</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>NOUS TOUS DISCOVERY SET</t>
+          <t>YSL MYSLF Parfum</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>z03</t>
+          <t>p64</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>NOUS TOUS DISCOVERY SET</t>
+          <t>YSL MYSLF Parfum</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>z04</t>
+          <t>p65</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SWEET &amp; SPICY SET</t>
+          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>gourmand</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>propozycja z opisu zestawu w źródle (gourmand wprost w treści)</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>z04</t>
+          <t>p65</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SWEET &amp; SPICY SET</t>
+          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Wiosna, lato, wczesna jesień</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>z05</t>
+          <t>p65</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>ENTRY SET</t>
+          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Amouage Reflection -&gt; reflection</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>z05</t>
+          <t>p66</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ENTRY SET</t>
+          <t>Rabanne Black XS</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>z05</t>
+          <t>p66</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ENTRY SET</t>
+          <t>Rabanne Black XS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Korzenno-cytrusowa</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>cytrusowa</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>z06</t>
+          <t>p68</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>AUTUMN DISCOVERY SET</t>
+          <t>Rabanne One Million</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>sklad</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>YSL Y le Parfum -&gt; y le parfum</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>Korzenno-słodka</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>słodka</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>z06</t>
+          <t>p69</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>AUTUMN DISCOVERY SET</t>
+          <t>Azzaro Chrome</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>z06</t>
+          <t>p70</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>AUTUMN DISCOVERY SET</t>
+          <t>Azzaro Forever Wanted Elixir</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>z07</t>
+          <t>p71</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>WINTER DISCOVERY SET</t>
+          <t>Azzaro The Most Wanted Parfum</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>sklad</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>5x ml (BOSS Bottled Absolu, MFK Grand Soir, Maison Crivelli Oud Maracuja, Tom Ford Tobacco Vanille, Montale Arabians Tonka)</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>p60:5, p42:5, p41:5, p35:5, p28:5</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>w źródle „5x ml” bez pojemności; przyjęto 5 ml</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>z07</t>
+          <t>p71</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>WINTER DISCOVERY SET</t>
+          <t>Azzaro The Most Wanted Parfum</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -10690,33 +10838,537 @@
           <t>rodzina</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Korzenno-drzewna</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>z07</t>
+          <t>z01</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>WINTER DISCOVERY SET</t>
+          <t>LV DISCOVERY SET</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
+        <is>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>z01</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>LV DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>z02</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>XERJOFF DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>5 × 5 ml (do ustalenia skład, sugerowane: Torino21, Renaissance, Erba Pura, Uden, Naxos)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>p06:5, p07:5, p08:5, p09:5, p10:5</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>skład „do ustalenia”; wpisano propozycję ze źródła, zestaw wyłączony</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>z02</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>XERJOFF DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>z02</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>XERJOFF DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>z02</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>XERJOFF DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>z03</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>NOUS TOUS DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>cena</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>350 zł</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>cena zapisana jako tekst</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>z03</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>NOUS TOUS DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>z03</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>NOUS TOUS DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>z04</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SWEET &amp; SPICY SET</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>propozycja z opisu zestawu w źródle (gourmand wprost w treści)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>z04</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SWEET &amp; SPICY SET</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>z05</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ENTRY SET</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Amouage Reflection -&gt; reflection</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>z05</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ENTRY SET</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>z05</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>ENTRY SET</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>z06</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>AUTUMN DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>YSL Y le Parfum -&gt; y le parfum</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>z06</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>AUTUMN DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>z06</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>AUTUMN DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>z07</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>WINTER DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>5x ml (BOSS Bottled Absolu, MFK Grand Soir, Maison Crivelli Oud Maracuja, Tom Ford Tobacco Vanille, Montale Arabians Tonka)</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>p60:5, p42:5, p41:5, p35:5, p28:5</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>w źródle „5x ml” bez pojemności; przyjęto 5 ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>z07</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>WINTER DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>z07</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>WINTER DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr">
         <is>
           <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>

--- a/dev/dane/import-do-arkusza.xlsx
+++ b/dev/dane/import-do-arkusza.xlsx
@@ -620,7 +620,11 @@
           <t>p46, p45, p06, p03</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>/img/produkty/p01-800.webp</t>
+        </is>
+      </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
@@ -711,7 +715,11 @@
           <t>p03, p21, p07</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>/img/produkty/p02-800.webp</t>
+        </is>
+      </c>
       <c r="V3" t="n">
         <v>2</v>
       </c>
@@ -806,7 +814,11 @@
           <t>p02, p08, p21</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>/img/produkty/p03-800.webp</t>
+        </is>
+      </c>
       <c r="V4" t="n">
         <v>3</v>
       </c>
@@ -901,7 +913,11 @@
           <t>p05, p32, p19, p17</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>/img/produkty/p04-800.webp</t>
+        </is>
+      </c>
       <c r="V5" t="n">
         <v>4</v>
       </c>
@@ -996,7 +1012,11 @@
           <t>p04, p19, p17</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>/img/produkty/p05-800.webp</t>
+        </is>
+      </c>
       <c r="V6" t="n">
         <v>5</v>
       </c>
@@ -4591,7 +4611,11 @@
           <t>p10, p35, p70</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>/img/produkty/p42-800.webp</t>
+        </is>
+      </c>
       <c r="V43" t="n">
         <v>42</v>
       </c>
@@ -4686,7 +4710,11 @@
           <t>p42, p40, p08</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>/img/produkty/p43-800.webp</t>
+        </is>
+      </c>
       <c r="V44" t="n">
         <v>43</v>
       </c>
@@ -5458,7 +5486,11 @@
           <t>p14, p06, p62</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>/img/produkty/p51-800.webp</t>
+        </is>
+      </c>
       <c r="V52" t="n">
         <v>51</v>
       </c>
@@ -5644,7 +5676,11 @@
           <t>p54, p52, p11, p70</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>/img/produkty/p53-800.webp</t>
+        </is>
+      </c>
       <c r="V54" t="n">
         <v>53</v>
       </c>
@@ -5739,7 +5775,11 @@
           <t>p53, p38, p05, p41</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>/img/produkty/p54-800.webp</t>
+        </is>
+      </c>
       <c r="V55" t="n">
         <v>54</v>
       </c>
@@ -5832,7 +5872,11 @@
           <t>p08, p09</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>/img/produkty/p55-800.webp</t>
+        </is>
+      </c>
       <c r="V56" t="n">
         <v>55</v>
       </c>
@@ -6502,7 +6546,11 @@
           <t>p44, p52, p10</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr"/>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>/img/produkty/p63-800.webp</t>
+        </is>
+      </c>
       <c r="V64" t="n">
         <v>63</v>
       </c>
@@ -6595,7 +6643,11 @@
           <t>p63, p33, p52</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr"/>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>/img/produkty/p64-800.webp</t>
+        </is>
+      </c>
       <c r="V65" t="n">
         <v>64</v>
       </c>
@@ -6688,7 +6740,11 @@
           <t>p44, p11, p45</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr"/>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>/img/produkty/p65-800.webp</t>
+        </is>
+      </c>
       <c r="V66" t="n">
         <v>65</v>
       </c>
@@ -7527,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F134"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7593,24 +7649,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>p01</t>
+          <t>p02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Louis Vuitton Imagination</t>
+          <t>Louis Vuitton Pacific Chill</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Lato (upały), późna wiosna</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>wiosna, lato</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
@@ -7627,166 +7691,182 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lato (upały), późna wiosna</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>wiosna, lato</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p02</t>
+          <t>p03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Louis Vuitton Pacific Chill</t>
+          <t>Louis Vuitton Afternoon Swim</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>p02</t>
+          <t>p05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Louis Vuitton Pacific Chill</t>
+          <t>Louis Vuitton Ombre Nomade</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Agarowo-różana</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>orientalna</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>p03</t>
+          <t>p05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Louis Vuitton Afternoon Swim</t>
+          <t>Louis Vuitton Ombre Nomade</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>Amouage Otlands -&gt; otlands</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>p03</t>
+          <t>p06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Louis Vuitton Afternoon Swim</t>
+          <t>Xerjoff Torino21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>podobne</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>p04</t>
+          <t>p07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Louis Vuitton Nouveau Monde</t>
+          <t>Xerjoff Renaissance (XJ 1861)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Wiosna, lato, wczesna jesień</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>p05</t>
+          <t>p08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Louis Vuitton Ombre Nomade</t>
+          <t>Xerjoff Erba Pura</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7796,12 +7876,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Agarowo-różana</t>
+          <t>Owocowo-ambrowa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>orientalna</t>
+          <t>ambrowa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -7813,568 +7893,584 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>p05</t>
+          <t>p08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Louis Vuitton Ombre Nomade</t>
+          <t>Xerjoff Erba Pura</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Amouage Otlands -&gt; otlands</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>Cały rok, najlepiej wiosna i lato</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień, zima</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>p05</t>
+          <t>p09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Louis Vuitton Ombre Nomade</t>
+          <t>Xerjoff Uden</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Jesień, zima, wczesna wiosna</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>wiosna, jesień, zima</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>p06</t>
+          <t>p09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Xerjoff Torino21</t>
+          <t>Xerjoff Uden</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>pora</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Wieczór, chłodny dzień</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>p07</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance (XJ 1861)</t>
+          <t>Creed Aventus</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wiosna, lato, wczesna jesień</t>
+          <t>Owocowo-drzewna</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>p08</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Xerjoff Erba Pura</t>
+          <t>Creed Aventus</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Owocowo-ambrowa</t>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ambrowa</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>p08</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Xerjoff Erba Pura</t>
+          <t>Creed Absolu Aventus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i lato</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>p09</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Xerjoff Uden</t>
+          <t>Creed Absolu Aventus</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Jesień, zima, wczesna wiosna</t>
+          <t>owocowo-drzewna</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>wiosna, jesień, zima</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>p09</t>
+          <t>p13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Xerjoff Uden</t>
+          <t>Creed Virgin Island Water</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>nazwa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wieczór, chłodny dzień</t>
+          <t>Virgin Island Water</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>uniwersalna</t>
+          <t>Virgin Island Water</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
+          <t>nazwa do potwierdzenia (w ofercie „Virgin Mountain Water”)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Creed Aventus</t>
+          <t>Creed Virgin Island Water</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Owocowo-drzewna</t>
+          <t>NIEDOSTĘPNY</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Creed Aventus</t>
+          <t>Creed Silver Mountain Water</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
+          <t>zielono-herbaciana</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>świeża</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Creed Absolu Aventus</t>
+          <t>Creed Silver Mountain Water</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Creed Absolu Aventus</t>
+          <t>Amouage Search</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>owocowo-drzewna</t>
+          <t>Wiosna, jesień (uniwersalny)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>wiosna, jesień</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>p13</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Creed Virgin Island Water</t>
+          <t>Amouage Search</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nazwa</t>
+          <t>ceny</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Virgin Island Water</t>
+          <t>5 ml – 120 zł | 10 ml – 220 zł | 20 ml – 400 zł (promocja)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Virgin Island Water</t>
+          <t>5 ml 120 zł | 10 ml 220 zł | 20 ml 400 zł</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>nazwa do potwierdzenia (w ofercie „Virgin Mountain Water”)</t>
+          <t>cena oznaczona jako promocja; API nie ma pola na starą cenę, pokażemy ją jako zwykłą</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>p13</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Creed Virgin Island Water</t>
+          <t>Amouage Reflection Man</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>p14</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Creed Silver Mountain Water</t>
+          <t>Amouage Interlude Black Iris</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>aktywny</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>zielono-herbaciana</t>
+          <t>pewność danych: niska</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>świeża</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>p14</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Creed Silver Mountain Water</t>
+          <t>Amouage Interlude Black Iris</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>Irysowo-kadzidlana</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>kwiatowa</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Amouage Search</t>
+          <t>Amouage Interlude Black Iris</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wiosna, jesień (uniwersalny)</t>
+          <t>NIEDOSTĘPNY</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>wiosna, jesień</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Amouage Search</t>
+          <t>Amouage Interlude Man</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ceny</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>5 ml – 120 zł | 10 ml – 220 zł | 20 ml – 400 zł (promocja)</t>
+          <t>Dymno-żywiczna</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5 ml 120 zł | 10 ml 220 zł | 20 ml 400 zł</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>cena oznaczona jako promocja; API nie ma pola na starą cenę, pokażemy ją jako zwykłą</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Amouage Reflection Man</t>
+          <t>Amouage Interlude Man</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8384,12 +8480,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
+          <t>Zima, późna jesień</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>jesień, zima</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -8401,232 +8497,232 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Amouage Interlude Black Iris</t>
+          <t>Mancera Lemon Line</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>pewność danych: niska</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amouage Interlude Black Iris</t>
+          <t>Mancera Lemon Line</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Irysowo-kadzidlana</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>kwiatowa</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Amouage Interlude Black Iris</t>
+          <t>Mancera Tonka Cola</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amouage Interlude Man</t>
+          <t>Mancera Red Tobacco</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Dymno-żywiczna</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Amouage Interlude Man</t>
+          <t>Mancera Red Tobacco</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Zima, późna jesień</t>
+          <t>Korzenna</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>jesień, zima</t>
+          <t>orientalna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>p21</t>
+          <t>p26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mancera Lemon Line</t>
+          <t>Mancera Instant Crush</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>aktywny</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>pewność danych: niska</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>p21</t>
+          <t>p26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mancera Lemon Line</t>
+          <t>Mancera Instant Crush</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>NIEDOSTĘPNY</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>p24</t>
+          <t>p30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mancera Tonka Cola</t>
+          <t>Montale Honey Aoud</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -8653,108 +8749,100 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>p31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mancera Red Tobacco</t>
+          <t>Montale Intense Pepper</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>Amouage Reflection -&gt; reflection</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>p32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mancera Red Tobacco</t>
+          <t>Tom Ford Ombré Leather</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Korzenna</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>orientalna</t>
-        </is>
-      </c>
+          <t>LV Nouvau Monde -&gt; nouvau monde</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>p26</t>
+          <t>p33</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mancera Instant Crush</t>
+          <t>Tom Ford Noir Extreme</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>pewność danych: niska</t>
+          <t>Korzenno-gourmand</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>gourmand</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>p26</t>
+          <t>p34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mancera Instant Crush</t>
+          <t>Tom Ford Lost Cherry</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -8781,536 +8869,544 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>p30</t>
+          <t>p35</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Montale Honey Aoud</t>
+          <t>Tom Ford Tobacco Vanille</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Korzenno-gourmand</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>gourmand</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>p31</t>
+          <t>p36</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Montale Intense Pepper</t>
+          <t>Tom Ford Bois Pacifique</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Amouage Reflection -&gt; reflection</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>Jesień, zima, wczesna wiosna</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>wiosna, jesień, zima</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>p32</t>
+          <t>p37</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tom Ford Ombré Leather</t>
+          <t>Tom Ford Oud Wood</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LV Nouvau Monde -&gt; nouvau monde</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
+          <t>NIEDOSTĘPNY</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>p33</t>
+          <t>p38</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tom Ford Noir Extreme</t>
+          <t>Tom Ford Ébène Fumé</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Korzenno-gourmand</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>gourmand</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>p34</t>
+          <t>p38</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tom Ford Lost Cherry</t>
+          <t>Tom Ford Ébène Fumé</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
+          <t>Dymno-drzewna</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>p35</t>
+          <t>p39</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tom Ford Tobacco Vanille</t>
+          <t>Marc-Antoine Barrois Ganymede</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Korzenno-gourmand</t>
+          <t>Wiosna, jesień (uniwersalny)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>gourmand</t>
+          <t>wiosna, jesień</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>p36</t>
+          <t>p39</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tom Ford Bois Pacifique</t>
+          <t>Marc-Antoine Barrois Ganymede</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>ceny</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Jesień, zima, wczesna wiosna</t>
+          <t>5 ml – 70 zł | 10 ml – 140 zł (?) | 20 ml – 250 zł</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>wiosna, jesień, zima</t>
+          <t>5 ml 70 zł | 20 ml 250 zł</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>cena 10 ml oznaczona w źródle jako niepewna "(?)", wariant pominięty do potwierdzenia</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>p37</t>
+          <t>p40</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tom Ford Oud Wood</t>
+          <t>Tiziana Terenzi Kirke</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>p38</t>
+          <t>p41</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tom Ford Ébène Fumé</t>
+          <t>Maison Crivelli Oud Maracujá</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Owocowo-agarowa</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>słodka</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>p38</t>
+          <t>p41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tom Ford Ébène Fumé</t>
+          <t>Maison Crivelli Oud Maracujá</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Dymno-drzewna</t>
+          <t>Jesień, zima, chłodna wiosna</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>wiosna, jesień, zima</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>p39</t>
+          <t>p41</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Marc-Antoine Barrois Ganymede</t>
+          <t>Maison Crivelli Oud Maracujá</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wiosna, jesień (uniwersalny)</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>wiosna, jesień</t>
-        </is>
-      </c>
+          <t>LV Nouvau Monde -&gt; nouvau monde</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>p39</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Marc-Antoine Barrois Ganymede</t>
+          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ceny</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5 ml – 70 zł | 10 ml – 140 zł (?) | 20 ml – 250 zł</t>
+          <t>Cały rok, najlepiej jesień i zima</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5 ml 70 zł | 20 ml 250 zł</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>cena 10 ml oznaczona w źródle jako niepewna "(?)", wariant pominięty do potwierdzenia</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>p40</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tiziana Terenzi Kirke</t>
+          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>pora</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
+          <t>Wieczór (działa też w dzień)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>uniwersalna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>p41</t>
+          <t>p44</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Maison Crivelli Oud Maracujá</t>
+          <t>Essential Parfums Bois Impérial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Owocowo-agarowa</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>słodka</t>
-        </is>
-      </c>
+          <t>Nous Tous Saffrano Absolu -&gt; saffrano absolu</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>p41</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Maison Crivelli Oud Maracujá</t>
+          <t>Nous Tous Secco di Como</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Jesień, zima, chłodna wiosna</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>wiosna, jesień, zima</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>p41</t>
+          <t>p48</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Maison Crivelli Oud Maracujá</t>
+          <t>Nous Tous Aurora Siciliana</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LV Nouvau Monde -&gt; nouvau monde</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
+          <t>Owocowo-kwiatowa</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>kwiatowa</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>p42</t>
+          <t>p50</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Maison Francis Kurkdjian Grand Soir</t>
+          <t>Nous Tous Milano 3AM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>korzenna</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>orientalna</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p50</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
+          <t>Nous Tous Milano 3AM</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -9320,7 +9416,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej jesień i zima</t>
+          <t>Cały rok, najlepiej chłodne wieczory</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -9337,244 +9433,220 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
+          <t>Dior Sauvage Parfum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>pora</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Wieczór (działa też w dzień)</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>uniwersalna</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p53</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
+          <t>Dior Sauvage Elixir</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Korzenno-ambrowa</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>ambrowa</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>p44</t>
+          <t>p55</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Essential Parfums Bois Impérial</t>
+          <t>Versace Eros Parfum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Nous Tous Saffrano Absolu -&gt; saffrano absolu</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>p47</t>
+          <t>p56</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nous Tous Secco di Como</t>
+          <t>wiersz Lp. 56 (bez nazwy)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>podobne</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
+          <t>marka, nazwa</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>p48</t>
+          <t>p56</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nous Tous Aurora Siciliana</t>
+          <t>wiersz Lp. 56 (bez nazwy)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Owocowo-kwiatowa</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>kwiatowa</t>
-        </is>
-      </c>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>p50</t>
+          <t>p56</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nous Tous Milano 3AM</t>
+          <t>wiersz Lp. 56 (bez nazwy)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>korzenna</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>orientalna</t>
-        </is>
-      </c>
+          <t>pora</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>p50</t>
+          <t>p56</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nous Tous Milano 3AM</t>
+          <t>wiersz Lp. 56 (bez nazwy)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>sezon</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Cały rok, najlepiej chłodne wieczory</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>wiosna, lato, jesień, zima</t>
-        </is>
-      </c>
+          <t>trwalosc</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>p51</t>
+          <t>p56</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dior Homme Cologne</t>
+          <t>wiersz Lp. 56 (bez nazwy)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
+          <t>projekcja</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p56</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dior Sauvage Parfum</t>
+          <t>wiersz Lp. 56 (bez nazwy)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -9593,225 +9665,217 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>p53</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dior Sauvage Elixir</t>
+          <t>wiersz Lp. 57 (bez nazwy)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Korzenno-ambrowa</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>ambrowa</t>
-        </is>
-      </c>
+          <t>marka, nazwa</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>p53</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dior Sauvage Elixir</t>
+          <t>wiersz Lp. 57 (bez nazwy)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Korzenno-drzewna</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>p54</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dior Sauvage Extrait</t>
+          <t>wiersz Lp. 57 (bez nazwy)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>p55</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Versace Eros Parfum</t>
+          <t>wiersz Lp. 57 (bez nazwy)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>pora</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>p55</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Versace Eros Parfum</t>
+          <t>wiersz Lp. 57 (bez nazwy)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
+          <t>trwalosc</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>wiersz Lp. 57 (bez nazwy)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>marka, nazwa</t>
+          <t>projekcja</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>wiersz Lp. 57 (bez nazwy)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>wiersz Lp. 58 (bez nazwy)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>marka, nazwa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>wiersz Lp. 58 (bez nazwy)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>trwalosc</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -9825,17 +9889,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>wiersz Lp. 58 (bez nazwy)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>projekcja</t>
+          <t>pora</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -9849,380 +9913,452 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>wiersz Lp. 58 (bez nazwy)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
+          <t>trwalosc</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>wiersz Lp. 58 (bez nazwy)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>marka, nazwa</t>
+          <t>projekcja</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>wiersz Lp. 58 (bez nazwy)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Korzenno-drzewna</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>drzewna</t>
-        </is>
-      </c>
+          <t>ceny</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak cen</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>wiersz Lp. 58 (bez nazwy)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p59</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>Hugo Boss Bottled Elixir</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>pora</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p59</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>Hugo Boss Bottled Elixir</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>trwalosc</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Korzenno-drzewna</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p60</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>Hugo Boss Bottled Absolu</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>projekcja</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+          <t>aktywny</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>pewność danych: niska</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p60</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>Hugo Boss Bottled Absolu</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Korzenno-gourmand</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p60</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>Hugo Boss Bottled Absolu</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>marka, nazwa</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p61</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>Hugo Boss Bottled Beyond</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>sezon</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p63</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>YSL Y Parfum</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>pora</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p63</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>YSL Y Parfum</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>trwalosc</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień, zima</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p64</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>YSL MYSLF Parfum</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>projekcja</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p65</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ceny</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>brak cen</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p65</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Wiosna, lato, wczesna jesień</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>p59</t>
+          <t>p66</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Elixir</t>
+          <t>Rabanne Black XS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -10249,12 +10385,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>p59</t>
+          <t>p66</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Elixir</t>
+          <t>Rabanne Black XS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10264,12 +10400,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Korzenno-drzewna</t>
+          <t>Korzenno-cytrusowa</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>cytrusowa</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10281,100 +10417,108 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>p60</t>
+          <t>p68</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Absolu</t>
+          <t>Rabanne One Million</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>pewność danych: niska</t>
+          <t>Korzenno-słodka</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>słodka</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>p60</t>
+          <t>p69</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Absolu</t>
+          <t>Azzaro Chrome</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Korzenno-gourmand</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>gourmand</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>p60</t>
+          <t>p70</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Absolu</t>
+          <t>Azzaro Forever Wanted Elixir</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>p61</t>
+          <t>p71</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Beyond</t>
+          <t>Azzaro The Most Wanted Parfum</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -10401,308 +10545,280 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>p63</t>
+          <t>p71</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>YSL Y Parfum</t>
+          <t>Azzaro The Most Wanted Parfum</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Korzenno-drzewna</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>p63</t>
+          <t>z01</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>YSL Y Parfum</t>
+          <t>LV DISCOVERY SET</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>sezon</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>wiosna, lato, jesień, zima</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>p63</t>
+          <t>z01</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>YSL Y Parfum</t>
+          <t>LV DISCOVERY SET</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>p64</t>
+          <t>z02</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>YSL MYSLF Parfum</t>
+          <t>XERJOFF DISCOVERY SET</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>sklad</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>5 × 5 ml (do ustalenia skład, sugerowane: Torino21, Renaissance, Erba Pura, Uden, Naxos)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>p06:5, p07:5, p08:5, p09:5, p10:5</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>skład „do ustalenia”; wpisano propozycję ze źródła, zestaw wyłączony</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>p64</t>
+          <t>z02</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>YSL MYSLF Parfum</t>
+          <t>XERJOFF DISCOVERY SET</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>p65</t>
+          <t>z02</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
+          <t>XERJOFF DISCOVERY SET</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>p65</t>
+          <t>z02</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
+          <t>XERJOFF DISCOVERY SET</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>sezon</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Wiosna, lato, wczesna jesień</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>wiosna, lato, jesień</t>
-        </is>
-      </c>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>p65</t>
+          <t>z03</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
+          <t>NOUS TOUS DISCOVERY SET</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
+          <t>cena</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>350 zł</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>cena zapisana jako tekst</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>p66</t>
+          <t>z03</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Rabanne Black XS</t>
+          <t>NOUS TOUS DISCOVERY SET</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>p66</t>
+          <t>z03</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Rabanne Black XS</t>
+          <t>NOUS TOUS DISCOVERY SET</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Korzenno-cytrusowa</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>cytrusowa</t>
-        </is>
-      </c>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>p68</t>
+          <t>z04</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Rabanne One Million</t>
+          <t>SWEET &amp; SPICY SET</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -10710,239 +10826,203 @@
           <t>rodzina</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Korzenno-słodka</t>
-        </is>
-      </c>
+      <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>słodka</t>
+          <t>gourmand</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>propozycja z opisu zestawu w źródle (gourmand wprost w treści)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>p69</t>
+          <t>z04</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Azzaro Chrome</t>
+          <t>SWEET &amp; SPICY SET</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>p70</t>
+          <t>z05</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Azzaro Forever Wanted Elixir</t>
+          <t>ENTRY SET</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>sklad</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>Amouage Reflection -&gt; reflection</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>p71</t>
+          <t>z05</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Azzaro The Most Wanted Parfum</t>
+          <t>ENTRY SET</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>p71</t>
+          <t>z05</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Azzaro The Most Wanted Parfum</t>
+          <t>ENTRY SET</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Korzenno-drzewna</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>drzewna</t>
-        </is>
-      </c>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>z01</t>
+          <t>z06</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>LV DISCOVERY SET</t>
+          <t>AUTUMN DISCOVERY SET</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>YSL Y le Parfum -&gt; y le parfum</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>z01</t>
+          <t>z06</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LV DISCOVERY SET</t>
+          <t>AUTUMN DISCOVERY SET</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>z06</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>AUTUMN DISCOVERY SET</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>5 × 5 ml (do ustalenia skład, sugerowane: Torino21, Renaissance, Erba Pura, Uden, Naxos)</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>p06:5, p07:5, p08:5, p09:5, p10:5</t>
-        </is>
-      </c>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>skład „do ustalenia”; wpisano propozycję ze źródła, zestaw wyłączony</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>z07</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>WINTER DISCOVERY SET</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -10952,25 +11032,29 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr"/>
+          <t>5x ml (BOSS Bottled Absolu, MFK Grand Soir, Maison Crivelli Oud Maracuja, Tom Ford Tobacco Vanille, Montale Arabians Tonka)</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>p60:5, p42:5, p41:5, p35:5, p28:5</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>w źródle „5x ml” bez pojemności; przyjęto 5 ml</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>z07</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>WINTER DISCOVERY SET</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -10989,12 +11073,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>z07</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>WINTER DISCOVERY SET</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -11005,370 +11089,6 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
-        <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>z03</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>NOUS TOUS DISCOVERY SET</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>cena</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>350 zł</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>cena zapisana jako tekst</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>z03</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>NOUS TOUS DISCOVERY SET</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>z03</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>NOUS TOUS DISCOVERY SET</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>z04</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>SWEET &amp; SPICY SET</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>gourmand</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>propozycja z opisu zestawu w źródle (gourmand wprost w treści)</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>z04</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>SWEET &amp; SPICY SET</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>z05</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>ENTRY SET</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>Amouage Reflection -&gt; reflection</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>z05</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>ENTRY SET</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>z05</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>ENTRY SET</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>z06</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>AUTUMN DISCOVERY SET</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>YSL Y le Parfum -&gt; y le parfum</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>z06</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>AUTUMN DISCOVERY SET</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>z06</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>AUTUMN DISCOVERY SET</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>z07</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>WINTER DISCOVERY SET</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>5x ml (BOSS Bottled Absolu, MFK Grand Soir, Maison Crivelli Oud Maracuja, Tom Ford Tobacco Vanille, Montale Arabians Tonka)</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>p60:5, p42:5, p41:5, p35:5, p28:5</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>w źródle „5x ml” bez pojemności; przyjęto 5 ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>z07</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>WINTER DISCOVERY SET</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>z07</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>WINTER DISCOVERY SET</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr">
         <is>
           <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>

--- a/dev/dane/import-do-arkusza.xlsx
+++ b/dev/dane/import-do-arkusza.xlsx
@@ -5583,7 +5583,11 @@
           <t>p53, p54, p11</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>/img/produkty/p52-800.webp</t>
+        </is>
+      </c>
       <c r="V53" t="n">
         <v>52</v>
       </c>
@@ -7583,7 +7587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9433,88 +9437,88 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>p52</t>
+          <t>p53</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dior Sauvage Parfum</t>
+          <t>Dior Sauvage Elixir</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Korzenno-ambrowa</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ambrowa</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>p53</t>
+          <t>p55</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dior Sauvage Elixir</t>
+          <t>Versace Eros Parfum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Korzenno-ambrowa</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ambrowa</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>p55</t>
+          <t>p56</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Versace Eros Parfum</t>
+          <t>wiersz Lp. 56 (bez nazwy)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>marka, nazwa</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
         </is>
       </c>
     </row>
@@ -9531,14 +9535,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>marka, nazwa</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
@@ -9555,7 +9559,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>pora</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -9579,7 +9583,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>trwalosc</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -9603,7 +9607,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>trwalosc</t>
+          <t>projekcja</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -9627,38 +9631,38 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>projekcja</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>wiersz Lp. 57 (bez nazwy)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
+          <t>marka, nazwa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
         </is>
       </c>
     </row>
@@ -9675,14 +9679,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>marka, nazwa</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Korzenno-drzewna</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
@@ -9699,22 +9711,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Korzenno-drzewna</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>drzewna</t>
-        </is>
-      </c>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
@@ -9731,7 +9735,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>pora</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -9755,7 +9759,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>trwalosc</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -9779,7 +9783,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>trwalosc</t>
+          <t>projekcja</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -9803,38 +9807,38 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>projekcja</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>wiersz Lp. 58 (bez nazwy)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
+          <t>marka, nazwa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
         </is>
       </c>
     </row>
@@ -9851,14 +9855,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>marka, nazwa</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
+          <t>brak w źródle</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9879,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>pora</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -9899,7 +9903,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>trwalosc</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -9923,7 +9927,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>trwalosc</t>
+          <t>projekcja</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -9947,14 +9951,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>projekcja</t>
+          <t>ceny</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>brak cen</t>
         </is>
       </c>
     </row>
@@ -9971,38 +9975,46 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ceny</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>brak cen</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p59</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>Hugo Boss Bottled Elixir</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
@@ -10019,54 +10031,54 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Korzenno-drzewna</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>p59</t>
+          <t>p60</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Elixir</t>
+          <t>Hugo Boss Bottled Absolu</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>aktywny</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Korzenno-drzewna</t>
+          <t>pewność danych: niska</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
         </is>
       </c>
     </row>
@@ -10083,22 +10095,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>pewność danych: niska</t>
+          <t>Korzenno-gourmand</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>gourmand</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
@@ -10115,58 +10127,58 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Korzenno-gourmand</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>gourmand</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>p60</t>
+          <t>p61</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Absolu</t>
+          <t>Hugo Boss Bottled Beyond</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>p61</t>
+          <t>p63</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Beyond</t>
+          <t>YSL Y Parfum</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -10203,66 +10215,66 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>p63</t>
+          <t>p64</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YSL Y Parfum</t>
+          <t>YSL MYSLF Parfum</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>p64</t>
+          <t>p65</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>YSL MYSLF Parfum</t>
+          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -10299,54 +10311,54 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Wiosna, lato, wczesna jesień</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>wiosna, lato, jesień</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>p65</t>
+          <t>p66</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
+          <t>Rabanne Black XS</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Wiosna, lato, wczesna jesień</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
@@ -10363,34 +10375,34 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Korzenno-cytrusowa</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>cytrusowa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>p66</t>
+          <t>p68</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Rabanne Black XS</t>
+          <t>Rabanne One Million</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10400,12 +10412,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Korzenno-cytrusowa</t>
+          <t>Korzenno-słodka</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>cytrusowa</t>
+          <t>słodka</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10417,44 +10429,44 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>p68</t>
+          <t>p69</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Rabanne One Million</t>
+          <t>Azzaro Chrome</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Korzenno-słodka</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>słodka</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>p69</t>
+          <t>p70</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Azzaro Chrome</t>
+          <t>Azzaro Forever Wanted Elixir</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10481,12 +10493,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>p70</t>
+          <t>p71</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Azzaro Forever Wanted Elixir</t>
+          <t>Azzaro The Most Wanted Parfum</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -10523,34 +10535,34 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Korzenno-drzewna</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>p71</t>
+          <t>z01</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Azzaro The Most Wanted Parfum</t>
+          <t>LV DISCOVERY SET</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -10558,19 +10570,11 @@
           <t>rodzina</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Korzenno-drzewna</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>drzewna</t>
-        </is>
-      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -10587,38 +10591,46 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>z01</t>
+          <t>z02</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>LV DISCOVERY SET</t>
+          <t>XERJOFF DISCOVERY SET</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>5 × 5 ml (do ustalenia skład, sugerowane: Torino21, Renaissance, Erba Pura, Uden, Naxos)</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>p06:5, p07:5, p08:5, p09:5, p10:5</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>skład „do ustalenia”; wpisano propozycję ze źródła, zestaw wyłączony</t>
         </is>
       </c>
     </row>
@@ -10640,17 +10652,13 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5 × 5 ml (do ustalenia skład, sugerowane: Torino21, Renaissance, Erba Pura, Uden, Naxos)</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>p06:5, p07:5, p08:5, p09:5, p10:5</t>
-        </is>
-      </c>
+          <t>Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>skład „do ustalenia”; wpisano propozycję ze źródła, zestaw wyłączony</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
@@ -10667,18 +10675,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -10695,38 +10699,46 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>z03</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>NOUS TOUS DISCOVERY SET</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+          <t>cena</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>350 zł</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>cena zapisana jako tekst</t>
         </is>
       </c>
     </row>
@@ -10743,22 +10755,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>cena</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>350 zł</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>cena zapisana jako tekst</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -10775,38 +10779,42 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>z03</t>
+          <t>z04</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NOUS TOUS DISCOVERY SET</t>
+          <t>SWEET &amp; SPICY SET</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>propozycja z opisu zestawu w źródle (gourmand wprost w treści)</t>
         </is>
       </c>
     </row>
@@ -10823,42 +10831,42 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>gourmand</t>
-        </is>
-      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>propozycja z opisu zestawu w źródle (gourmand wprost w treści)</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>z04</t>
+          <t>z05</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SWEET &amp; SPICY SET</t>
+          <t>ENTRY SET</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Amouage Reflection -&gt; reflection</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
@@ -10875,18 +10883,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Amouage Reflection -&gt; reflection</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -10903,38 +10907,42 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>z05</t>
+          <t>z06</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ENTRY SET</t>
+          <t>AUTUMN DISCOVERY SET</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>YSL Y le Parfum -&gt; y le parfum</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
@@ -10951,18 +10959,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>YSL Y le Parfum -&gt; y le parfum</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -10979,38 +10983,46 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>z06</t>
+          <t>z07</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AUTUMN DISCOVERY SET</t>
+          <t>WINTER DISCOVERY SET</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>5x ml (BOSS Bottled Absolu, MFK Grand Soir, Maison Crivelli Oud Maracuja, Tom Ford Tobacco Vanille, Montale Arabians Tonka)</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>p60:5, p42:5, p41:5, p35:5, p28:5</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>w źródle „5x ml” bez pojemności; przyjęto 5 ml</t>
         </is>
       </c>
     </row>
@@ -11027,22 +11039,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>5x ml (BOSS Bottled Absolu, MFK Grand Soir, Maison Crivelli Oud Maracuja, Tom Ford Tobacco Vanille, Montale Arabians Tonka)</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>p60:5, p42:5, p41:5, p35:5, p28:5</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>w źródle „5x ml” bez pojemności; przyjęto 5 ml</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -11059,36 +11063,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
-        <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>z07</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>WINTER DISCOVERY SET</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr">
         <is>
           <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>

--- a/dev/dane/import-do-arkusza.xlsx
+++ b/dev/dane/import-do-arkusza.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W72"/>
+  <dimension ref="A1:Z101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,21 @@
           <t>okazja</t>
         </is>
       </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>bestseller</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>klimat</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>renoma</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -629,6 +644,19 @@
         <v>1</v>
       </c>
       <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>cytrusowy, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -728,6 +756,15 @@
           <t>Wakacje, plaża, miasto latem, sport, casual</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -827,6 +864,15 @@
           <t>Wakacje, weekend, casual, spotkania w dzień</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -926,6 +972,15 @@
           <t>Kolacja, wyjście, impreza, ważne spotkanie, garnitur</t>
         </is>
       </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>orientalny, slodki</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1025,6 +1080,19 @@
           <t>Wyjście, klub, bardzo eleganckie spotkanie, randka wieczorem</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>orientalny, kwiatowy</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1124,6 +1192,15 @@
           <t>Biuro, sport, codzienność, spotkania w dzień, wakacje</t>
         </is>
       </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>cytrusowy, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1223,6 +1300,15 @@
           <t>Biuro, spotkania, codzienność, uczelnia</t>
         </is>
       </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1322,6 +1408,19 @@
           <t>codzienność, randka, klub, wyjście, prezent</t>
         </is>
       </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>cytrusowy, slodki</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1421,6 +1520,15 @@
           <t>Kolacja, wyjście, biznes, spotkania</t>
         </is>
       </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>cytrusowy, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1520,6 +1628,19 @@
           <t>Kolacja, randka, wyjście, chłodne dni, prezent</t>
         </is>
       </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>slodki, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1618,6 +1739,19 @@
         <is>
           <t>Biznes, spotkania, wyjście, garnitur, prezent</t>
         </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>cytrusowy, drzewny</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1715,6 +1849,15 @@
         <is>
           <t>Codzienność, biuro, spotkania w dzień, garniur</t>
         </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>cytrusowy, drzewny</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1807,6 +1950,15 @@
           <t>Wakacje, plaża, urlop</t>
         </is>
       </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>cytrusowy, slodki</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1906,6 +2058,15 @@
           <t>Biuro, codzienność, sport, spotkania w dzień</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2005,6 +2166,15 @@
           <t>Biznes, spotkania, wyjście, codzienność premium</t>
         </is>
       </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>cytrusowy, orientalny</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2088,7 +2258,7 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>p09, p15</t>
+          <t>p09, p31, p100, p64</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2104,6 +2274,15 @@
           <t>Garnitur, biznes, ślub, elegancka kolacja</t>
         </is>
       </c>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>kwiatowy, drzewny</t>
+        </is>
+      </c>
+      <c r="Z17" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2202,6 +2381,15 @@
         <is>
           <t>Wyjście, event, kolacja, okazje specjalne</t>
         </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>orientalny, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2294,6 +2482,15 @@
           <t>Elegancki wieczór, event</t>
         </is>
       </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>orientalny, kwiatowy</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2393,6 +2590,15 @@
           <t>Wyjście, event, chłodne wieczory</t>
         </is>
       </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>orientalny, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2491,6 +2697,15 @@
         <is>
           <t>Codzienność premium, spotkania, kolacja</t>
         </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>aromatyczny, orientalny</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -2589,6 +2804,15 @@
           <t>Codzienność, biuro latem, weekend, prezent</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2686,6 +2910,15 @@
           <t>Uniwersalny: biuro, wyjście, codzienność premium</t>
         </is>
       </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>cytrusowy, drzewny</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2783,6 +3016,15 @@
           <t>Wakacje, plaża, weekend, casual</t>
         </is>
       </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2880,6 +3122,15 @@
           <t>Randka, wyjście, klub, chłodne dni</t>
         </is>
       </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>slodki</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2976,6 +3227,15 @@
         <is>
           <t>Klub, wyjście, event</t>
         </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>aromatyczny, orientalny</t>
+        </is>
+      </c>
+      <c r="Z26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -3068,6 +3328,15 @@
           <t>Randka, wyjście</t>
         </is>
       </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>slodki</t>
+        </is>
+      </c>
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3165,6 +3434,15 @@
           <t>Randka, kolacja, wyjście</t>
         </is>
       </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>slodki, kwiatowy</t>
+        </is>
+      </c>
+      <c r="Z28" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3262,6 +3540,15 @@
           <t>Randka, wyjście, chłodne dni</t>
         </is>
       </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>orientalny, slodki</t>
+        </is>
+      </c>
+      <c r="Z29" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3359,6 +3646,19 @@
           <t>Randka, kawiarnia, casual zimą (nie do biura), prezent</t>
         </is>
       </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>slodki</t>
+        </is>
+      </c>
+      <c r="Z30" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3456,6 +3756,15 @@
           <t>Wyjście, event, okazje specjalne, święta</t>
         </is>
       </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>orientalny, slodki</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3553,6 +3862,15 @@
           <t>Wyjście, kolacja, biznes</t>
         </is>
       </c>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>aromatyczny, drzewny</t>
+        </is>
+      </c>
+      <c r="Z32" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3650,6 +3968,15 @@
           <t>Wyjście, randka, klub, chłodne dni</t>
         </is>
       </c>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>drzewny</t>
+        </is>
+      </c>
+      <c r="Z33" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3746,6 +4073,15 @@
         <is>
           <t>Randka, kolacja, wyjście, prezent</t>
         </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>slodki, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -3842,6 +4178,15 @@
           <t>Randka, wyjście, prezent</t>
         </is>
       </c>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>slodki, cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z35" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3940,6 +4285,19 @@
         <is>
           <t>Kolacja, święta, chłodne wieczory</t>
         </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>slodki, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -4037,6 +4395,15 @@
         <is>
           <t>Biznes, spotkania, kolacja</t>
         </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>drzewny, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -4133,6 +4500,15 @@
           <t>Biznes, kolacja, elegancki wieczór</t>
         </is>
       </c>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>drzewny, orientalny</t>
+        </is>
+      </c>
+      <c r="Z38" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4231,6 +4607,15 @@
         <is>
           <t>Wyjście, kolacja, event</t>
         </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>drzewny, orientalny</t>
+        </is>
+      </c>
+      <c r="Z39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -4329,6 +4714,15 @@
           <t>prezent, codzienność premium, spotkania, wyjście</t>
         </is>
       </c>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>drzewny</t>
+        </is>
+      </c>
+      <c r="Z40" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4426,6 +4820,19 @@
           <t>Wyjście, randka, klub, codzienność</t>
         </is>
       </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>cytrusowy, slodki</t>
+        </is>
+      </c>
+      <c r="Z41" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4525,6 +4932,15 @@
           <t>Wyjście, event, okazje specjalne</t>
         </is>
       </c>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>orientalny, cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z42" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4608,7 +5024,7 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
-          <t>p10, p35, p70</t>
+          <t>p30, p10, p35</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4624,6 +5040,15 @@
           <t>Kolacja, randka, elegancki wieczór</t>
         </is>
       </c>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>orientalny, slodki</t>
+        </is>
+      </c>
+      <c r="Z43" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4707,7 +5132,7 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
-          <t>p42, p40, p08</t>
+          <t>p73, p40, p08</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -4722,6 +5147,19 @@
         <is>
           <t>Wyjście, randka, event, prezent</t>
         </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>slodki, orientalny</t>
+        </is>
+      </c>
+      <c r="Z44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -4804,7 +5242,7 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr">
         <is>
-          <t>p39, p65, p49</t>
+          <t>p73, p39, p65</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -4819,6 +5257,19 @@
         <is>
           <t>Biuro, biznes, codzienność, uczelnia, prezent</t>
         </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>drzewny, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z45" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="46">
@@ -4917,6 +5368,19 @@
           <t>Biuro, spotkania, codzienność premium, prezent</t>
         </is>
       </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>cytrusowy, drzewny</t>
+        </is>
+      </c>
+      <c r="Z46" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5014,6 +5478,15 @@
           <t>Codzienność, spotkania, wakacje, biuro</t>
         </is>
       </c>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z47" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5111,6 +5584,15 @@
           <t>Biuro, spotkania, wakacje</t>
         </is>
       </c>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>cytrusowy, kwiatowy</t>
+        </is>
+      </c>
+      <c r="Z48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5208,6 +5690,15 @@
           <t>Wakacje, codzienność, wyjście latem</t>
         </is>
       </c>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>cytrusowy, kwiatowy</t>
+        </is>
+      </c>
+      <c r="Z49" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5305,6 +5796,15 @@
           <t>Kolacja, event, formalne wyjścia</t>
         </is>
       </c>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>orientalny, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z50" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5402,6 +5902,15 @@
           <t>Wyjście, klub, randka</t>
         </is>
       </c>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>aromatyczny, cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z51" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5499,6 +6008,15 @@
           <t>Biuro, upały, codzienność, sport</t>
         </is>
       </c>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z52" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5596,6 +6114,15 @@
           <t>Klub, wyjście, codzienność zimą</t>
         </is>
       </c>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>aromatyczny, drzewny</t>
+        </is>
+      </c>
+      <c r="Z53" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5693,6 +6220,19 @@
           <t>Wyjście, klub, randka, event</t>
         </is>
       </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>aromatyczny, drzewny</t>
+        </is>
+      </c>
+      <c r="Z54" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5791,6 +6331,15 @@
         <is>
           <t>Wyjście, event, okazje specjalne</t>
         </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>drzewny, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -5889,6 +6438,15 @@
           <t>Wyjście, klub, randka</t>
         </is>
       </c>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>aromatyczny, slodki</t>
+        </is>
+      </c>
+      <c r="Z56" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5898,11 +6456,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NIE</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Versace</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Eros Energy</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>cytrusowa</t>
@@ -5933,11 +6499,25 @@
           <t>Sześć różnych cytrusów naraz, czyli otwarcie tak jasne, że brzmi jak zimna woda z lodem w środku sierpnia. Prosty i energetyczny, bez niczego, co mogłoby komuś przeszkadzać. Dobry pierwszy zakup dla kogoś, kto boi się mocnych i słodkich zapachów. Trzeba go odświeżyć po kilku godzinach i to jedyne zastrzeżenie.</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>wiosna, lato</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>dzień</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N57" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="n">
         <v>70</v>
@@ -5955,7 +6535,20 @@
       <c r="V57" t="n">
         <v>56</v>
       </c>
-      <c r="W57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Codzienność, sport, uczelnia, wakacje</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>cytrusowy, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z57" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5968,7 +6561,11 @@
           <t>NIE</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Versace</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
@@ -6000,11 +6597,25 @@
           <t>Najbardziej zaskakująca pozycja w tej cenie: karmel, przyprawy i ciemne drewno orientalne, czyli coś, co normalnie kosztuje pięć razy więcej. „Najim” znaczy po arabsku „gwiazda” i ten zapach faktycznie brzmi jak coś z zupełnie innej półki cenowej. Ludzie nie rozpoznają go z drogerii, więc pytają o nazwę. Najtańszy sposób, żeby spróbować orientalnych zapachów.</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>wieczór</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>4</v>
+      </c>
+      <c r="N58" t="n">
+        <v>4</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3</v>
+      </c>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="n">
         <v>70</v>
@@ -6022,7 +6633,14 @@
       <c r="V58" t="n">
         <v>57</v>
       </c>
-      <c r="W58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Wyjście, klub, randka, event</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6035,7 +6653,11 @@
           <t>NIE</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Versace</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
@@ -6067,21 +6689,50 @@
           <t>Krwista pomarańcza z pieprzem, a pod spodem ciepła wanilia z drewnem. Zapach na tę część roku, kiedy jest już chłodno, ale jeszcze nie zimno. Najbardziej uniwersalny z całej linii: sprawdza się w ciągu dnia i wieczorem, w pracy i na wyjściu. Trzyma długo i wyraźnie go czuć, więc ludzie zapamiętują cię po jednym spotkaniu.</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>4</v>
+      </c>
+      <c r="N59" t="n">
+        <v>4</v>
+      </c>
+      <c r="O59" t="n">
+        <v>3</v>
+      </c>
       <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="Q59" t="n">
+        <v>70</v>
+      </c>
+      <c r="R59" t="n">
+        <v>130</v>
+      </c>
       <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>p55, p59, p52</t>
+        </is>
+      </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="n">
         <v>58</v>
       </c>
-      <c r="W59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Codzienność, wyjście, randka</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6179,6 +6830,15 @@
           <t>Biuro, biznes, spotkania</t>
         </is>
       </c>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>aromatyczny, drzewny</t>
+        </is>
+      </c>
+      <c r="Z60" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6272,6 +6932,15 @@
           <t>Biuro, codzienność, kolacja</t>
         </is>
       </c>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>orientalny, slodki</t>
+        </is>
+      </c>
+      <c r="Z61" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6369,6 +7038,15 @@
           <t>Biuro, spotkania, wyjście</t>
         </is>
       </c>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>drzewny</t>
+        </is>
+      </c>
+      <c r="Z62" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6466,6 +7144,15 @@
           <t>Biuro, codzienność, upały</t>
         </is>
       </c>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>cytrusowy, drzewny</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6563,6 +7250,15 @@
           <t>Biuro, biznes, codzienność, wieczorne wyjścia</t>
         </is>
       </c>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>aromatyczny, cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6660,6 +7356,15 @@
           <t>Biuro, randka, spotkania, ślub</t>
         </is>
       </c>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>kwiatowy, drzewny</t>
+        </is>
+      </c>
+      <c r="Z65" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6756,6 +7461,15 @@
         <is>
           <t>Biuro, biznes, spotkania, codzienność</t>
         </is>
+      </c>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>drzewny, cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -6852,6 +7566,15 @@
           <t>Codzienność, klub</t>
         </is>
       </c>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>slodki, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z67" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6947,6 +7670,15 @@
           <t>Sport, siłownia, codzienność, upały</t>
         </is>
       </c>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z68" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7042,6 +7774,15 @@
           <t>Randka, wyjście, codzienność zimną porą</t>
         </is>
       </c>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>slodki, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z69" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7137,6 +7878,15 @@
           <t>Biuro, codzienność, sport, upały</t>
         </is>
       </c>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7234,6 +7984,15 @@
           <t>Randka, wyjście, codzienność zimną porą</t>
         </is>
       </c>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>slodki, drzewny</t>
+        </is>
+      </c>
+      <c r="Z71" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7330,6 +8089,3089 @@
         <is>
           <t>Randka, wyjście, codzienność zimną porą</t>
         </is>
+      </c>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>slodki, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>p72</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Carner Barcelona</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Cuirs</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>skórzana</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Szafran, kminek</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Drewno sandałowe, gwajakowiec, paczula, cedr Virginia, fiołek</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Oud, skóra, francuskie labdanum, fasola tonka, bursztyn, piżmo, cypriol, amyris</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Otulające przyprawy okryte gładką skórą. Słodkawy z zachowanym balansem elegancji, przy czym bardzo uniwersalny. Nada się na randkę jak i na mniej zobowiązujące wyjścia w chłodniejsze dni w roku. Idealne wprowadzenie w zapachy skórzane.</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>wiosna, jesień, zima</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>wieczór</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>4</v>
+      </c>
+      <c r="N73" t="n">
+        <v>4</v>
+      </c>
+      <c r="O73" t="n">
+        <v>3</v>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="n">
+        <v>70</v>
+      </c>
+      <c r="R73" t="n">
+        <v>130</v>
+      </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>p32, p04, p33, p49</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>/img/produkty/p72-800.webp</t>
+        </is>
+      </c>
+      <c r="V73" t="n">
+        <v>72</v>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Randka, wyjście, codzienność zimną porą</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>drzewny, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z73" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>p73</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>New Notes</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Akigala Mandarino</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Mandarynka, marakuja, malina, jabłko</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Frezja, jaśmin, konwalia</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Akigalawood, ambra</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Mandarynka z maliną i marakują, podane tak soczyście, że pierwsze minuty pachną jak miska owoców postawiona na słońcu, a w tle mineralne akordy akigalawood oraz szafran. Potem robi się kwiatowo i miękko, a na dnie zostaje ciepłe, lekko pieprzne drewno. Tej marki nie zna w Polsce prawie nikt, więc pytania o nazwę przychodzą same.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>dzień</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>4</v>
+      </c>
+      <c r="N74" t="n">
+        <v>4</v>
+      </c>
+      <c r="O74" t="n">
+        <v>3</v>
+      </c>
+      <c r="P74" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>180</v>
+      </c>
+      <c r="R74" t="n">
+        <v>330</v>
+      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>p39, p44, p43</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="n">
+        <v>73</v>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Uniwersalny: biuro, wyjście, codzienność premium</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>cytrusowy, kwiatowy</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>p74</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Xerjoff</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Opera</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>kwiatowa</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Kosz owoców, róża turecka</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Skóra, ambra, gałka muszkatołowa, ylang-ylang</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Cedr wirginijski, wetyweria haitańska, piżmo, paczula, wanilia</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Owocowy, różany start, który po kwadransie zamienia się w gładką skórę z przyprawą. Na końcu zostaje pudrowa wanilia na ciepłym drewnie. Trzyma ponad osiem godzin i wypełnia pomieszczenie, więc dwa psiknięcia to górna granica. Zapach na operę, kolację i każdą sytuację, do której zakładasz coś lepszego niż bluzę. Przez swoją kwiatowość częściej wybierany przez kobiety.</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>wieczór</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4</v>
+      </c>
+      <c r="O75" t="n">
+        <v>3</v>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="n">
+        <v>110</v>
+      </c>
+      <c r="R75" t="n">
+        <v>210</v>
+      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>p88, p83, p87, p04</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>/img/produkty/p74-800.webp</t>
+        </is>
+      </c>
+      <c r="V75" t="n">
+        <v>74</v>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Teatr, kolacja, okazje formalne</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>kwiatowy, orientalny</t>
+        </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>p75</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Parfums de Marly</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Layton</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ambrowa</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Jabłko, bergamotka, kardamon</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Lawenda, fiołek, geranium</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Paczula, wanilia, drzewo gwajakowe, praliny</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Flagowy zapach Parfums de Marly i jeden z tych, z którymi trudno się nie polubić. Soczyste jabłko z kardamonem na wejściu. Po godzinie słodka, kremowa wanilia z pralinami i dymnym drewnem. Trzyma od ośmiu do dziesięciu godzin, a na kurtce zostaje kilka dni. Jeśli szukasz zapachu, po którym ktoś się odwróci na jesiennej imprezie, to bardzo pewny wybór.</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>4</v>
+      </c>
+      <c r="N76" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O76" t="n">
+        <v>3</v>
+      </c>
+      <c r="P76" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>120</v>
+      </c>
+      <c r="R76" t="n">
+        <v>220</v>
+      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>p89, p52, p10, p71</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>/img/produkty/p75-800.webp</t>
+        </is>
+      </c>
+      <c r="V76" t="n">
+        <v>75</v>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Randka, wyjście, klub, codzienność zimą</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>slodki, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z76" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>p76</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Parfums de Marly</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Pegasus Exclusif</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Różowy pieprz, kardamon, migdał</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Lawenda, kwiat pomarańczy, geranium</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Wanilia, ambroksan, oud, drzewo gwajakowe</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Migdał z wanilią na ciepłym, lekko dymnym drewnie. Pachnie jak wnętrze drogiej cukierni, do której ktoś wstawił skórzane fotele: słodko, ale zdecydowanie dorośle. Wersja parfum, czyli gęsta, i przy jednym psiknięciu trzyma kilkanaście godzin. Dobra propozycja dla kogoś, kto lubi Laytona i chce czegoś mniej rozpoznawalnego.</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>wieczór</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N77" t="n">
+        <v>4</v>
+      </c>
+      <c r="O77" t="n">
+        <v>3</v>
+      </c>
+      <c r="P77" t="n">
+        <v>90</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>130</v>
+      </c>
+      <c r="R77" t="n">
+        <v>240</v>
+      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>p75, p89, p95</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>/img/produkty/p76-800.webp</t>
+        </is>
+      </c>
+      <c r="V77" t="n">
+        <v>76</v>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Kolacja, wyjście, okazje formalne</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>slodki, drzewny</t>
+        </is>
+      </c>
+      <c r="Z77" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>p77</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Parfums de Marly</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Sedley</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Bergamotka, mięta kędzierzawa, pomarańcza</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Geranium, lawandyna, sosna</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Sandałowiec, ambroksan, białe piżma</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Mięta z cytrusami i mydlana czystość, czyli zapach dobrze prowadzonego barber shopu. Lekki i uporządkowany, nikomu nie przeszkodzi w małym pomieszczeniu, dlatego świetnie pracuje w biurze. Na ciepłe miesiące i na dni, w których masz spotkanie i chcesz po prostu dobrze wyglądać.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>wiosna, lato</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>dzień</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="P78" t="n">
+        <v>80</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>120</v>
+      </c>
+      <c r="R78" t="n">
+        <v>160</v>
+      </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>p14, p06, p64</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>/img/produkty/p77-800.webp</t>
+        </is>
+      </c>
+      <c r="V78" t="n">
+        <v>77</v>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Biuro, codzienność, spotkania w dzień</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>cytrusowy, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z78" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>p78</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Amouage</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>kwiatowa</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Gruszka, kadzidło, orzech laskowy</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Szafran, róża, jaśmin sambac, osmanthus</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Labdanum (cistus), sandałowiec, akigalawood, ambra szara, wanilia</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Gruszka z orzechem laskowym brzmi prawie deserowo, dopóki nie wejdzie kadzidło i nie zrobi z tego czegoś poważnego. Serce jest kwiatowe i korzenne, a koniec ciepły, żywiczny i waniliowy, z tych, które zostają na ubraniu kilka dni. Dwadzieścia pięć procent olejków oznacza jedno psiknięcie na cały dzień. Amouage dostał za ten zapach dwie europejskie nagrody w 2024 roku, co w perfumerii niszowej zdarza się rzadko.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>5</v>
+      </c>
+      <c r="N79" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O79" t="n">
+        <v>3</v>
+      </c>
+      <c r="P79" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>220</v>
+      </c>
+      <c r="R79" t="n">
+        <v>400</v>
+      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>p83, p42, p88</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>/img/produkty/p78-800.webp</t>
+        </is>
+      </c>
+      <c r="V79" t="n">
+        <v>78</v>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Kolacja, event, okazje specjalne, codzienność premium</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>kwiatowy, orientalny</t>
+        </is>
+      </c>
+      <c r="Z79" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>p79</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Creed</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Delphinus</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Pieprz czarny, kadzidło, migdał, pieprz różowy</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Heliotrop, orchidea, masło irysowe</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Paczula, tonka, amberwood, akord skórzany, wanilia Bourbon z Madagaskaru</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Creed sprzedaje to jako zapach drzewny. Ludzie, którzy go noszą, mówią o migdale i wanilii, i mają rację: jest tu gęsty, kremowy marcepan z pieprzem i pudrowym irysem. Trzyma powyżej ośmiu godzin, przy czym bardzo łatwo przesadzić, bo po dwóch psiknięciach ty przestajesz go czuć, a inni nie. Dla kogoś, kto lubi słodkie zapachy i chce mieć je w butelce z napisem Creed.</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>wieczór</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N80" t="n">
+        <v>4</v>
+      </c>
+      <c r="O80" t="n">
+        <v>3</v>
+      </c>
+      <c r="P80" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>230</v>
+      </c>
+      <c r="R80" t="n">
+        <v>400</v>
+      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>p76, p10</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>/img/produkty/p79-800.webp</t>
+        </is>
+      </c>
+      <c r="V80" t="n">
+        <v>79</v>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Kolacja, wyjście, okazje specjalne</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>slodki, drzewny</t>
+        </is>
+      </c>
+      <c r="Z80" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>p80</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Essential Parfums</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Velvet Iris</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Esencja liścia kurkumy, różowy pieprz, liść buchu</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Konkret irysowy, galbanum, mastyks, akord zamszu Saffiano</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Labdanum, kremowy akord drzewny, drzewo sandałowe</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Irys wytrawny i cielesny, bez pudru i bez kwiatowej słodyczy. Zielony, lekko korzenny start przechodzi w zamsz, a kończy się suchym, kremowym drewnem. To zapach na bliski dystans, który pracuje w rozmowie i przy stole. Dla kogoś, kto ma już w szufladzie cytrusy i słodycze i chce czegoś, czego nikt nie rozpozna.</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>wiosna, jesień</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>3</v>
+      </c>
+      <c r="N81" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="n">
+        <v>80</v>
+      </c>
+      <c r="R81" t="n">
+        <v>150</v>
+      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>p95, p35, p100</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>/img/produkty/p80-800.webp</t>
+        </is>
+      </c>
+      <c r="V81" t="n">
+        <v>80</v>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Biuro, spotkania, codzienność premium</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>kwiatowy, drzewny</t>
+        </is>
+      </c>
+      <c r="Z81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>p81</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Essential Parfums</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Ambre Latte</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Akord mleka migdałowego, pianka mleczna, prażona fasolka tonka</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Karmel dulce de leche, wanilia, benzoina, białe piżmo</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Ambrofix, Georgywood, Akigalawood, biały sandałowiec</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Zimowe cappuccino: mleko migdałowe, karmel i prażona tonka, podane ciepło i leniwie. Pomysł jest prosty, a efekt działa dokładnie tam, gdzie powinien, czyli przy stole i w kołnierzu kurtki. Pod spodem siedzą drzewne molekuły, które trzymają słodycz w ryzach i rozciągają ją na wiele godzin. Premiera z tego roku, więc mogłeś nie doświadczyć tego wokół ciebie.</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>wieczór</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>4</v>
+      </c>
+      <c r="N82" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O82" t="n">
+        <v>2</v>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="n">
+        <v>80</v>
+      </c>
+      <c r="R82" t="n">
+        <v>150</v>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>p42, p27, p10</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>/img/produkty/p81-800.webp</t>
+        </is>
+      </c>
+      <c r="V82" t="n">
+        <v>81</v>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Randka, kawiarnia, chłodne wieczory</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>slodki</t>
+        </is>
+      </c>
+      <c r="Z82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>p82</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ormonde Jayne</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Kashmir</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Bergamotka, kardamon, nasiona kolendry, szafran, różowy pieprz</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Jaśmin, irys, róża, niebieski mak, jodła himalajska</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Cedr himalajski (deodar), sandałowiec, cashmeran, benzoina, wanilia, paczula, kadzidło, mirra, piżmo</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Zapach jak ciepły szal narzucony na ramiona pod koniec października. Korzenny i cytrusowy początek, miękkie kwiatowe serce, a na końcu gęste, żywiczne drewno z kadzidłem. Nosi się go cały dzień bez dopsiknięć. Ślad w powietrzu jest wyczuwalny i nikogo nie przytłacza. Ormonde Jayne to marka, której w Polsce praktycznie nie widać, więc ryzyko spotkania kogoś w tym samym zapachu jest bliskie zeru. Świetnie pachnie na kobiecie jak i na mężczyźnie.</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N83" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O83" t="n">
+        <v>2</v>
+      </c>
+      <c r="P83" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>170</v>
+      </c>
+      <c r="R83" t="n">
+        <v>310</v>
+      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>p20, p83, p95</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>/img/produkty/p82-800.webp</t>
+        </is>
+      </c>
+      <c r="V83" t="n">
+        <v>82</v>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Codzienność premium, kolacja, spotkania</t>
+        </is>
+      </c>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>drzewny, orientalny</t>
+        </is>
+      </c>
+      <c r="Z83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>p83</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Maison Francis Kurkdjian</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Oud Satin Mood</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>kwiatowa</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Fiołek</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Oud, róża damasceńska</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Akord waniliowo-ambrowy, benzoina</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Róża i wanilia na ciemnym drewnie, tak gładko, że słowo satin w nazwie nie jest przesadą. Od pierwszej sekundy jest ciepło, bez żadnej surowej fazy, a fiołek dorzuca odrobinę pudru. Zapach układa się wokół ciebie aurą, więc nikomu nie przeszkodzi w restauracji.</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>wieczór</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>4</v>
+      </c>
+      <c r="N84" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O84" t="n">
+        <v>3</v>
+      </c>
+      <c r="P84" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>280</v>
+      </c>
+      <c r="R84" t="n">
+        <v>520</v>
+      </c>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>p43, p30, p49</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="n">
+        <v>83</v>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Randka, kolacja, elegancki wieczór</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>orientalny, kwiatowy</t>
+        </is>
+      </c>
+      <c r="Z84" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>p84</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Nishane</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Wūlóng Chá</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>cytrusowa</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Bergamotka, pomarańcza, litsea cubeba, mandarynka</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Herbata oolong, gałka muszkatołowa</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Piżmo, figa</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>Cytrusy z herbatą oolong, czyli świeżość, która nie wyparowuje po godzinie. Pachnie jak zimna herbata z cytryną pita w upał, czysto i bez grama słodyczy. Cała sztuczka siedzi w tym, jak mocno jest skoncentrowany: dostajesz lekkie odczucie przy trwałości, jakiej letnie zapachy zwykle nie mają. Jeśli męczy cię to, że twoje świeże perfumy giną po dwóch godzinach, to jest rozwiązanie.</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>wiosna, lato</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>dzień</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>4</v>
+      </c>
+      <c r="N85" t="n">
+        <v>3</v>
+      </c>
+      <c r="O85" t="n">
+        <v>2</v>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="n">
+        <v>120</v>
+      </c>
+      <c r="R85" t="n">
+        <v>210</v>
+      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>p01, p14, p07, p97</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>/img/produkty/p84-800.webp</t>
+        </is>
+      </c>
+      <c r="V85" t="n">
+        <v>84</v>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Biuro, upały, codzienność, wakacje</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z85" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>p85</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Sospiro</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Basso</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Grejpfrut, głóg, galbanum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Goździk, labdanum, nasiona selera, czarny i różowy pieprz, gałka muszkatołowa</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Sandałowiec, wetyweria, drzewo gwajakowe, mech dębowy, cedr</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>Grejpfrut, cytryna i zieleń na wejściu, a pod nimi ciemne, pieprzne drewno oraz delikatna słodycz dla równowagi. Brzmi poważnie i trochę surowo, jak dobrze skrojony garnitur w kolorze węgla, dlatego dobrze wypada przy ludziach starszych od ciebie. Bardziej złożona i wzmocniona wersja klasyka od Hermesa.</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>4</v>
+      </c>
+      <c r="N86" t="n">
+        <v>4</v>
+      </c>
+      <c r="O86" t="n">
+        <v>3</v>
+      </c>
+      <c r="P86" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>130</v>
+      </c>
+      <c r="R86" t="n">
+        <v>220</v>
+      </c>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>p45, p65, p15</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>/img/produkty/p85-800.webp</t>
+        </is>
+      </c>
+      <c r="V86" t="n">
+        <v>85</v>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Biuro, spotkania biznesowe, wieczorne wyjścia</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>drzewny, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z86" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>p86</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Tom Ford</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Velvet Orchid</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>kwiatowa</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Bergamotka włoska, mandarynka, absolut rumowy, miód</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Orchidea, jaśmin absolut, kwiat pomarańczy, róża turecka, heliotrop, magnolia, narcyz</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Balsam peruwiański, mirra, labdanum, sandałowiec, zamsz, wanilia, tonka</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>Cieplejsza, bardziej miodowa siostra Black Orchid. Rumowo-cytrusowy start, gęsty bukiet kwiatów, a po kilku godzinach wanilia z zamszem. Trzyma osiem do dziesięciu godzin i wyraźnie go czuć, więc dwa psiknięcia to norma. Idealne na zimny wieczór, najczęściej wybierany przez kobiety.</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>wieczór</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N87" t="n">
+        <v>4</v>
+      </c>
+      <c r="O87" t="n">
+        <v>3</v>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="n">
+        <v>90</v>
+      </c>
+      <c r="R87" t="n">
+        <v>160</v>
+      </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>p87, p83, p98</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>/img/produkty/p86-800.webp</t>
+        </is>
+      </c>
+      <c r="V87" t="n">
+        <v>86</v>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Randka, kolacja, okazje formalne</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>kwiatowy, slodki</t>
+        </is>
+      </c>
+      <c r="Z87" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>p87</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tom Ford</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Black Orchid</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ambrowa</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Czarna trufla, ylang-ylang, bergamotka, gorzka pomarańcza</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Czarna orchidea, czarna śliwka, absolut rumowy</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Paczula, wanilia, meksykańska czekolada, kadzidło, sandałowiec, wetyweria</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>Od dwudziestu lat dzieli ludzi i od dwudziestu lat sprzedaje się świetnie. Ciemna śliwka, trufla i czekolada brzmią jak wnętrze bardzo drogiego i bardzo ciemnego klubu. Ludzie wiedzą, że wszedłeś do budynku, więc dwa psiknięcia są maksimum, a na tkaninie zapach zostaje nawet półtora dnia. Weź go, jeśli chcesz, żeby cię zapamiętali, i odpuść, jeśli zależy ci, żeby spodobać się wszystkim.</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>wieczór</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N88" t="n">
+        <v>5</v>
+      </c>
+      <c r="O88" t="n">
+        <v>3</v>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="n">
+        <v>90</v>
+      </c>
+      <c r="R88" t="n">
+        <v>160</v>
+      </c>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>p86, p29</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>/img/produkty/p87-800.webp</t>
+        </is>
+      </c>
+      <c r="V88" t="n">
+        <v>87</v>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Kolacja, drinki, teatr, wyjście (nie do biura)</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>orientalny, kwiatowy, slodki</t>
+        </is>
+      </c>
+      <c r="Z88" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>p88</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Tom Ford</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Oud Voyager</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Absolut geranium, czerwona piwonia</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Osmanthus, oud</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Floral Oud Tri-Distillate, cypriol</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>Oud podany kwiatowo, co na rynku zdarza się rzadko. Geranium z czerwoną piwonią dają jasny, prawie różowy początek, a pod spodem siedzi ciemne, wilgotne drewno z dymem. Mimo wszystko jest to uniwersalne pachnidło dla kobiet i świetnie nada się na bezpieczny prezent. Premiera jest z tego roku, więc nikt wokół go nie zna, pytania o nazwę przychodzą szybko, a na chłodne miesiące wystarczą dwa psiknięcia w dzień.</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>wiosna, jesień, zima</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>4</v>
+      </c>
+      <c r="N89" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O89" t="n">
+        <v>2</v>
+      </c>
+      <c r="P89" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>230</v>
+      </c>
+      <c r="R89" t="n">
+        <v>420</v>
+      </c>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>p83, p42, p92</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>/img/produkty/p88-800.webp</t>
+        </is>
+      </c>
+      <c r="V89" t="n">
+        <v>88</v>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Wyjście, kolacja, okazje formalne</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>orientalny, kwiatowy</t>
+        </is>
+      </c>
+      <c r="Z89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>p89</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Kilian</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Angels' Share</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Esencja koniaku</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Esencja cynamonu, absolut tonki</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Sandałowiec, praliny, wanilia</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>W butelce jest prawdziwa esencja koniaku i dlatego płyn ma kolor whisky. Pachnie jak kieliszek postawiony obok ciasta z cynamonem: alkoholowo, ciepło i słodko, bez przechodzenia w cukier. Trzyma od dziewięciu do trzynastu godzin, więc nawet dziesięć mililitrów wystarcza na długo. Na jesienne i zimowe wieczory, i na sytuacje, w których chcesz, żeby ktoś podszedł bliżej. Perfumy z duszą dla kogoś, kto chce się wyróżnić.</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>wieczór</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>5</v>
+      </c>
+      <c r="N90" t="n">
+        <v>4</v>
+      </c>
+      <c r="O90" t="n">
+        <v>3</v>
+      </c>
+      <c r="P90" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>200</v>
+      </c>
+      <c r="R90" t="n">
+        <v>370</v>
+      </c>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>p10, p35, p24</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="n">
+        <v>89</v>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Randka, wyjście, klub, chłodne wieczory</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>slodki</t>
+        </is>
+      </c>
+      <c r="Z90" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>p90</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Kilian</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Angels' Share On The Rocks</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Akord On The Rocks (bergamotka, grejpfrut, aldehydy), gorzka pomarańcza</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Koniak, cynamon, rezyna mirry</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Absolut tonki, dąb</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>Ten sam koniak, tylko polany czymś zimnym. Gorzka pomarańcza i bergamotka kładą na ciepłym rdzeniu chłodną, musującą warstwę, dzięki czemu całość jest lżejsza i mniej słodka od oryginału. Trzyma około sześciu do siedmiu godzin, czyli zauważalnie krócej. Jeśli kupujesz pierwszy flakon z tej linii, weź klasyczny Angels' Share. Ten bierz wtedy, gdy masz już oryginał i chcesz wersję na cieplejsze dni.</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>wiosna, jesień</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N91" t="n">
+        <v>3</v>
+      </c>
+      <c r="O91" t="n">
+        <v>2</v>
+      </c>
+      <c r="P91" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>200</v>
+      </c>
+      <c r="R91" t="n">
+        <v>370</v>
+      </c>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>p89, p09</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="n">
+        <v>90</v>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Codzienność, spotkania, cieplejsze wieczory</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>slodki, cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z91" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>p91</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Kilian</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Roses On Ice</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>świeża</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Ogórek</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Jagody jałowca, róża</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Sandałowiec, piżmo</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>Gin z tonikiem przełożony na perfumy, z ogórkiem i jałowcem na pierwszym planie. Chłód naprawdę się tu czuje. Róża jest nowoczesna i wytrawna, więc nie przypomina ani kwiaciarni, ani cukierka. Lekki i casualowy, lepiej wypada w dzień, wieczorem zaś piękny, alkoholowy akcent może się gubić. Na wiosnę i lato, dla kobiety, która chce świeżości z pomysłem.</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>wiosna, lato</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>dzień</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N92" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O92" t="n">
+        <v>1</v>
+      </c>
+      <c r="P92" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>200</v>
+      </c>
+      <c r="R92" t="n">
+        <v>370</v>
+      </c>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>p47, p23, p97</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="n">
+        <v>91</v>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Codzienność, casual, upały</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr"/>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>kwiatowy, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z92" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>p92</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Kilian</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Woman in Gold</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>kwiatowa</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Bergamotka, różowy pieprz</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Róża, geranium</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Tonka, akigalawood</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Inspiracją jest złoty portret Klimta i to naprawdę się słyszy: cytrusowy błysk na wejściu, ciepła, prawie piankowa baza na końcu. Róża jest nowoczesna i czysta, a tonka dodaje ciepła, po którym ludzie podchodzą bliżej. Nada się to od biura po kolację i spokojnie wytrzymuje pełny dzień pracy. Przede wszystkim na wiosnę oraz jesień.</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>wiosna, jesień, zima</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>4</v>
+      </c>
+      <c r="N93" t="n">
+        <v>3</v>
+      </c>
+      <c r="O93" t="n">
+        <v>2</v>
+      </c>
+      <c r="P93" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>200</v>
+      </c>
+      <c r="R93" t="n">
+        <v>370</v>
+      </c>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>p93, p83, p73</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="n">
+        <v>92</v>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Biuro, codzienność, kolacja, eleganckie wyjścia</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>kwiatowy, slodki</t>
+        </is>
+      </c>
+      <c r="Z93" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>p93</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Kilian</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Good girl gone Bad</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>kwiatowa</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Kwiat pomarańczy, absolut róży majowej</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Absolut osmanthusa, absolut tuberozy, jaśmin</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Narcyz</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Bukiet białych kwiatów z morelowym rozbłyskiem osmanthusa, podany gęsto i bez skromności. Pachnie drogo w sposób, który ludzie wyczuwają natychmiast, nawet jeśli nie umieją nazwać ani jednej nuty. Trzyma osiem do dziesięciu godzin. Zapach uniwersalny, lecz wiosną i latem wypadniesz w nim najlepiej. Zapach jednoznacznie kobiecy.</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>4</v>
+      </c>
+      <c r="N94" t="n">
+        <v>3</v>
+      </c>
+      <c r="O94" t="n">
+        <v>2</v>
+      </c>
+      <c r="P94" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>200</v>
+      </c>
+      <c r="R94" t="n">
+        <v>370</v>
+      </c>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>p86, p92</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="n">
+        <v>93</v>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Codzienność, spotkania, kolacja, prezent</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr"/>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>kwiatowy</t>
+        </is>
+      </c>
+      <c r="Z94" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>p94</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Kilian</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Sparkling Royal</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>świeża</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Mięta, cytryna</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Róża, czarna porzeczka (akord Kir Royal)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Prażona fasolka tonka, delikatne piżmo</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>Kir Royal przełożony na zapach: czarna porzeczka z różą, a nad tym mięta i cytryna, które robią efekt bąbelków. Lekki i elegancki, nosi się go od brunchu po wieczorne wyjście. Kilian podaje ponad pięć godzin trwałości, co przy takiej konstrukcji jest wartością uczciwą, ale nie licz na chmurę w pomieszczeniu. Premiera z sierpnia, więc swoją popularność dopiero zyskuje. Idealny dla kobiet z klasą.</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>wiosna, lato</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N95" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1</v>
+      </c>
+      <c r="P95" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>200</v>
+      </c>
+      <c r="R95" t="n">
+        <v>370</v>
+      </c>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>p47, p91, p07</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="n">
+        <v>94</v>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Brunch, spotkania w dzień, wieczorne celebracje</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>kwiatowy, cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z95" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>p95</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Atkinsons</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Shine Despite Everything</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Kadzidło somalijskie, nasiona kurkumy, ziele angielskie</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Irys, karmel, Ambrofix, akord różany</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Kumaryna, wanilia z Madagaskaru, Akigalawood</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>Karmel i irys na dymnym kadzidle, czyli słodycz, która nie przypomina deseru. Początek jest korzenny i trochę ostry, lecz szybko robi się pudrowo i ciepło z mocnymi akcentami wanilii i drewna. Parfum Intense trzyma dziewięć do dziesięciu godzin, a na ubraniu zostaje po kilka dni. Dobry wybór na formalny zimowy wieczór dla kogoś, kto chce orientalnego pazura i jednocześnie boi się oudu. Świetnie sprawdzi się dla kobiety jak i dla mężczyzny.</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>wieczór</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N96" t="n">
+        <v>4</v>
+      </c>
+      <c r="O96" t="n">
+        <v>3</v>
+      </c>
+      <c r="P96" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>200</v>
+      </c>
+      <c r="R96" t="n">
+        <v>370</v>
+      </c>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>p100, p78, p10</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>/img/produkty/p95-800.webp</t>
+        </is>
+      </c>
+      <c r="V96" t="n">
+        <v>95</v>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Okazje formalne, kolacja, event</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>orientalny, slodki</t>
+        </is>
+      </c>
+      <c r="Z96" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>p96</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Atkinsons</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Oud Save the King</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>orientalna</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Akord bergamotki Earl Grey (herbata, bergamotka)</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Irys, zamsz</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Sandałowiec, akord oudowy (agar)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>Herbata Earl Grey z bergamotką spotyka zamsz i subtelny oud. Efekt jest zaskakująco kulturalny, bo oud jest tu lekki i wygładzony, przez co zapach brzmi jak angielski klub, a nie arabski bazar. Trzyma bardzo długo oraz potrafi wypełnić pomieszczenie. Dobre wejście w oud dla kogoś, kto boi się przesady, zwłaszcza do garnituru.</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>wieczór</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N97" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O97" t="n">
+        <v>2</v>
+      </c>
+      <c r="P97" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>200</v>
+      </c>
+      <c r="R97" t="n">
+        <v>370</v>
+      </c>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>p30, p16, p54</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>/img/produkty/p96-800.webp</t>
+        </is>
+      </c>
+      <c r="V97" t="n">
+        <v>96</v>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Garnitur, okazje formalne, kolacja</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>orientalny, drzewny</t>
+        </is>
+      </c>
+      <c r="Z97" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>p97</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Atkinsons</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Mint &amp; Tonic</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>cytrusowa</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Limonka, grejpfrut, mięta, mandarynka</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Imbir, geranium</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Cedr, wetyweria, piżmo</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>Mięta z limonką i grejpfrutem, czyli zapach zimnego drinka w upalny dzień. Lekki, zielony, bez grama słodyczy i bez ciężaru. Trzyma trzy do pięciu godzin i to cała prawda o nim, więc traktuj go jako zapach do odświeżania w ciągu dnia. Na lato i na biuro, kiedy chcesz pachnieć czysto i nic ponad to.</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>wiosna, lato</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>dzień</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>2</v>
+      </c>
+      <c r="N98" t="n">
+        <v>2</v>
+      </c>
+      <c r="O98" t="n">
+        <v>1</v>
+      </c>
+      <c r="P98" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>200</v>
+      </c>
+      <c r="R98" t="n">
+        <v>370</v>
+      </c>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>p51, p84</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>/img/produkty/p97-800.webp</t>
+        </is>
+      </c>
+      <c r="V98" t="n">
+        <v>97</v>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Biuro, codzienność, upały</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>cytrusowy, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z98" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>p98</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Bohoboco</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Wet Cherry Liquor</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Wiśnia, nuty likierowe</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Syrop czereśniowy, truskawka, karmel, róża turecka</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Sandałowiec, wetyweria, fasolka tonka, wanilia</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>Dojrzała wiśnia podlana likierem, z karmelem i różą w tle. Bohoboco zrobiło tu coś, co wielu uważa za dojrzalszą wersję Lost Cherry: mniej cukierka, więcej wytrawności i wyraźne drewno na końcu. Słodko, ale bez lepkości, z trwałością i śladem, które realnie pracują. Polska marka niszowa, co bywa mocnym argumentem dla kogoś, kto szuka czegoś poza oczywistymi nazwami. Idealny dla kobiety jak i mężczyzny.</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>wieczór</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>4</v>
+      </c>
+      <c r="N99" t="n">
+        <v>4</v>
+      </c>
+      <c r="O99" t="n">
+        <v>3</v>
+      </c>
+      <c r="P99" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>200</v>
+      </c>
+      <c r="R99" t="n">
+        <v>370</v>
+      </c>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>p34, p27</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="n">
+        <v>98</v>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Randka, wyjście, chłodne wieczory</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>slodki, cytrusowy</t>
+        </is>
+      </c>
+      <c r="Z99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>p99</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Sisley</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Soir d'Orient</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Cytryna włoska, galbanum irańskie</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Akord szafranowy, czarny pieprz z Madagaskaru, absolut róży tureckiej, geranium egipskie</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Akord sandałowy, kadzidło somalijskie, paczula indonezyjska, nuty skórzane</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>Szafran, róża i kadzidło, czyli klasyczny orientalny układ zrobiony przez francuski dom kosmetyczny. Otwarcie wypełnia pomieszczenie i brzmi bardzo drogo, a po dwóch godzinach zapach robi się intymny i zostaje blisko skóry. To zapach do eleganckiej garsonki i na wieczory zaplanowane z góry, nie na obiad w mieście. Chłodne miesiące i wieczór, dla kogoś, kto chce brzmieć dostojnie.</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>wieczór</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N100" t="n">
+        <v>4</v>
+      </c>
+      <c r="O100" t="n">
+        <v>3</v>
+      </c>
+      <c r="P100" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>200</v>
+      </c>
+      <c r="R100" t="n">
+        <v>370</v>
+      </c>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>p27, p83, p93</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="n">
+        <v>99</v>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Okazje formalne, przyjęcia, wieczorne wyjścia</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>orientalny, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z100" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>p100</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Bohoboco</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Vanilla Black Pepper</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>ambrowa</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>unisex</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Kwiat pomarańczy, wierzbówka kiprzyca</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Heliotrop, kadzidło (olibanum), róża, gałka muszkatołowa</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Czarny pieprz, wanilia, cedr, białe piżmo</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>Wanilia dla kogoś, kto nie chce pachnieć deserem. Czarny pieprz i kadzidło zabierają jej słodycz, a kwiatowe serce robi z całości rzecz raczej elegancką. Zapach siedzi bardzo blisko skóry: w biurze ani w windzie nikomu nie przeszkodzi, ale trzeba podejść, żeby go wyczuć. Flagowiec polskiego Bohoboco i jeden z niewielu zapachów z tej listy, które naprawdę nosi się przez cały rok. Idealny dla kobiety jak i mężczyzny.</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień, zima</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>4</v>
+      </c>
+      <c r="N101" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O101" t="n">
+        <v>2</v>
+      </c>
+      <c r="P101" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>200</v>
+      </c>
+      <c r="R101" t="n">
+        <v>370</v>
+      </c>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>p95, p35, p31, p80</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="n">
+        <v>100</v>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Biuro, codzienność, kolacja</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr"/>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>slodki, aromatyczny</t>
+        </is>
+      </c>
+      <c r="Z101" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7491,7 +11333,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>p08:5, p24:5, p29:5, p34:5, p43:5</t>
+          <t>p08:5, p24:5, p29:5, p98:5, p43:5</t>
         </is>
       </c>
     </row>
@@ -7587,7 +11429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7777,12 +11619,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>p05</t>
+          <t>p06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Louis Vuitton Ombre Nomade</t>
+          <t>Xerjoff Torino21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7792,7 +11634,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Amouage Otlands -&gt; otlands</t>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -7805,60 +11647,64 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>p06</t>
+          <t>p07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Xerjoff Torino21</t>
+          <t>Xerjoff Renaissance (XJ 1861)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>Wiosna, lato, wczesna jesień</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>p07</t>
+          <t>p08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance (XJ 1861)</t>
+          <t>Xerjoff Erba Pura</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wiosna, lato, wczesna jesień</t>
+          <t>Owocowo-ambrowa</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień</t>
+          <t>ambrowa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
@@ -7875,34 +11721,34 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Owocowo-ambrowa</t>
+          <t>Cały rok, najlepiej wiosna i lato</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ambrowa</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>p08</t>
+          <t>p09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Xerjoff Erba Pura</t>
+          <t>Xerjoff Uden</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -7912,12 +11758,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i lato</t>
+          <t>Jesień, zima, wczesna wiosna</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>wiosna, jesień, zima</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -7939,54 +11785,54 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>pora</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Jesień, zima, wczesna wiosna</t>
+          <t>Wieczór, chłodny dzień</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>wiosna, jesień, zima</t>
+          <t>uniwersalna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>p09</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Xerjoff Uden</t>
+          <t>Creed Aventus</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wieczór, chłodny dzień</t>
+          <t>Owocowo-drzewna</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>uniwersalna</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
@@ -8003,54 +11849,54 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Owocowo-drzewna</t>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Creed Aventus</t>
+          <t>Creed Absolu Aventus</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
@@ -8067,54 +11913,54 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>owocowo-drzewna</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Creed Absolu Aventus</t>
+          <t>Creed Virgin Island Water</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nazwa</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>owocowo-drzewna</t>
+          <t>Virgin Island Water</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>Virgin Island Water</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>nazwa do potwierdzenia (w ofercie „Virgin Mountain Water”)</t>
         </is>
       </c>
     </row>
@@ -8131,54 +11977,54 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nazwa</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Virgin Island Water</t>
+          <t>NIEDOSTĘPNY</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Virgin Island Water</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>nazwa do potwierdzenia (w ofercie „Virgin Mountain Water”)</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>p13</t>
+          <t>p14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Creed Virgin Island Water</t>
+          <t>Creed Silver Mountain Water</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
+          <t>zielono-herbaciana</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>świeża</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
@@ -8195,50 +12041,50 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>zielono-herbaciana</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>świeża</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>p14</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Creed Silver Mountain Water</t>
+          <t>Amouage Search</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>Wiosna, jesień (uniwersalny)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>wiosna, jesień</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
@@ -8255,54 +12101,54 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>ceny</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wiosna, jesień (uniwersalny)</t>
+          <t>5 ml – 120 zł | 10 ml – 220 zł | 20 ml – 400 zł (promocja)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>wiosna, jesień</t>
+          <t>5 ml 120 zł | 10 ml 220 zł | 20 ml 400 zł</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>cena oznaczona jako promocja; API nie ma pola na starą cenę, pokażemy ją jako zwykłą</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Amouage Search</t>
+          <t>Amouage Reflection Man</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ceny</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5 ml – 120 zł | 10 ml – 220 zł | 20 ml – 400 zł (promocja)</t>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5 ml 120 zł | 10 ml 220 zł | 20 ml 400 zł</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>cena oznaczona jako promocja; API nie ma pola na starą cenę, pokażemy ją jako zwykłą</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
@@ -8319,22 +12165,18 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>wiosna, lato, jesień, zima</t>
-        </is>
-      </c>
+          <t>MFK Baccarat Rouge</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>nazwa nie pasuje do żadnej pozycji katalogu</t>
         </is>
       </c>
     </row>
@@ -8781,188 +12623,192 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>p32</t>
+          <t>p33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tom Ford Ombré Leather</t>
+          <t>Tom Ford Noir Extreme</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LV Nouvau Monde -&gt; nouvau monde</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>Korzenno-gourmand</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>p33</t>
+          <t>p34</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tom Ford Noir Extreme</t>
+          <t>Tom Ford Lost Cherry</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Korzenno-gourmand</t>
+          <t>NIEDOSTĘPNY</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>gourmand</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>p34</t>
+          <t>p35</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tom Ford Lost Cherry</t>
+          <t>Tom Ford Tobacco Vanille</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
+          <t>Korzenno-gourmand</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>gourmand</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>p35</t>
+          <t>p36</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tom Ford Tobacco Vanille</t>
+          <t>Tom Ford Bois Pacifique</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Korzenno-gourmand</t>
+          <t>Jesień, zima, wczesna wiosna</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>gourmand</t>
+          <t>wiosna, jesień, zima</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>p36</t>
+          <t>p37</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tom Ford Bois Pacifique</t>
+          <t>Tom Ford Oud Wood</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Jesień, zima, wczesna wiosna</t>
+          <t>NIEDOSTĘPNY</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>wiosna, jesień, zima</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>p37</t>
+          <t>p38</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tom Ford Oud Wood</t>
+          <t>Tom Ford Ébène Fumé</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
@@ -8979,54 +12825,54 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Dymno-drzewna</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>p38</t>
+          <t>p39</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tom Ford Ébène Fumé</t>
+          <t>Marc-Antoine Barrois Ganymede</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Dymno-drzewna</t>
+          <t>Wiosna, jesień (uniwersalny)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>wiosna, jesień</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
@@ -9043,86 +12889,86 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>ceny</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Wiosna, jesień (uniwersalny)</t>
+          <t>5 ml – 70 zł | 10 ml – 140 zł (?) | 20 ml – 250 zł</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>wiosna, jesień</t>
+          <t>5 ml 70 zł | 20 ml 250 zł</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>cena 10 ml oznaczona w źródle jako niepewna "(?)", wariant pominięty do potwierdzenia</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>p39</t>
+          <t>p40</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Marc-Antoine Barrois Ganymede</t>
+          <t>Tiziana Terenzi Kirke</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ceny</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5 ml – 70 zł | 10 ml – 140 zł (?) | 20 ml – 250 zł</t>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5 ml 70 zł | 20 ml 250 zł</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>cena 10 ml oznaczona w źródle jako niepewna "(?)", wariant pominięty do potwierdzenia</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>p40</t>
+          <t>p41</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tiziana Terenzi Kirke</t>
+          <t>Maison Crivelli Oud Maracujá</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
+          <t>Owocowo-agarowa</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>słodka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
@@ -9139,34 +12985,34 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Owocowo-agarowa</t>
+          <t>Jesień, zima, chłodna wiosna</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>słodka</t>
+          <t>wiosna, jesień, zima</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>p41</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Maison Crivelli Oud Maracujá</t>
+          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -9176,12 +13022,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Jesień, zima, chłodna wiosna</t>
+          <t>Cały rok, najlepiej jesień i zima</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>wiosna, jesień, zima</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9193,160 +13039,168 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>p41</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Maison Crivelli Oud Maracujá</t>
+          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>pora</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LV Nouvau Monde -&gt; nouvau monde</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
+          <t>Wieczór (działa też w dzień)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
+          <t>Nous Tous Secco di Como</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej jesień i zima</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>wiosna, lato, jesień, zima</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p48</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
+          <t>Nous Tous Aurora Siciliana</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Wieczór (działa też w dzień)</t>
+          <t>Owocowo-kwiatowa</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>uniwersalna</t>
+          <t>kwiatowa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>p44</t>
+          <t>p50</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Essential Parfums Bois Impérial</t>
+          <t>Nous Tous Milano 3AM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Nous Tous Saffrano Absolu -&gt; saffrano absolu</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
+          <t>korzenna</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>orientalna</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>p47</t>
+          <t>p50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nous Tous Secco di Como</t>
+          <t>Nous Tous Milano 3AM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>Cały rok, najlepiej chłodne wieczory</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień, zima</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>p48</t>
+          <t>p53</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nous Tous Aurora Siciliana</t>
+          <t>Dior Sauvage Elixir</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -9356,12 +13210,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Owocowo-kwiatowa</t>
+          <t>Korzenno-ambrowa</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>kwiatowa</t>
+          <t>ambrowa</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -9373,876 +13227,980 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>p50</t>
+          <t>p55</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nous Tous Milano 3AM</t>
+          <t>Versace Eros Parfum</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>korzenna</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>orientalna</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>p50</t>
+          <t>p56</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Nous Tous Milano 3AM</t>
+          <t>Versace Eros Energy</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>sezon</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Cały rok, najlepiej chłodne wieczory</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>wiosna, lato, jesień, zima</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>p53</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Dior Sauvage Elixir</t>
+          <t>Versace</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Korzenno-ambrowa</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>ambrowa</t>
-        </is>
-      </c>
+          <t>marka, nazwa</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>p55</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Versace Eros Parfum</t>
+          <t>Versace</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Korzenno-drzewna</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>Versace</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>marka, nazwa</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>Versace</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>marka, nazwa</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>Versace</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p59</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>Hugo Boss Bottled Elixir</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>trwalosc</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p59</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>Hugo Boss Bottled Elixir</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>projekcja</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Korzenno-drzewna</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p60</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>wiersz Lp. 56 (bez nazwy)</t>
+          <t>Hugo Boss Bottled Absolu</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+          <t>aktywny</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>pewność danych: niska</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>NIE</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p60</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>Hugo Boss Bottled Absolu</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>marka, nazwa</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Korzenno-gourmand</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p60</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>Hugo Boss Bottled Absolu</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Korzenno-drzewna</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>drzewna</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p61</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>Hugo Boss Bottled Beyond</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>sezon</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p63</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>YSL Y Parfum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>pora</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p63</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>YSL Y Parfum</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>trwalosc</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień, zima</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p64</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>YSL MYSLF Parfum</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>projekcja</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p65</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>wiersz Lp. 57 (bez nazwy)</t>
+          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p65</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>marka, nazwa</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Wiosna, lato, wczesna jesień</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p66</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>Rabanne Black XS</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sezon</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p66</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>Rabanne Black XS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>pora</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Korzenno-cytrusowa</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>cytrusowa</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p68</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>Rabanne One Million</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>trwalosc</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Korzenno-słodka</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>słodka</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p69</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>Azzaro Chrome</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>projekcja</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>brak w źródle</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p70</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>Azzaro Forever Wanted Elixir</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ceny</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>brak cen</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p71</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>wiersz Lp. 58 (bez nazwy)</t>
+          <t>Azzaro The Most Wanted Parfum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>p59</t>
+          <t>p71</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Elixir</t>
+          <t>Azzaro The Most Wanted Parfum</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Korzenno-drzewna</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>p59</t>
+          <t>p72</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Elixir</t>
+          <t>Carner Barcelona Cuirs</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / opis</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Korzenno-drzewna</t>
+          <t>pewność danych: Do weryfikacji</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>w źródle bez potwierdzenia nut i opisu; zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>p60</t>
+          <t>p73</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Absolu</t>
+          <t>New Notes Akigala Mandarino</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>pewność danych: niska</t>
+          <t>słońcu, a tle mineralne</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>słońcu, a w tle mineralne</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>p60</t>
+          <t>p73</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Absolu</t>
+          <t>New Notes Akigala Mandarino</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Korzenno-gourmand</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>gourmand</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>p60</t>
+          <t>p73</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Absolu</t>
+          <t>New Notes Akigala Mandarino</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Owocowo-drzewna</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>p61</t>
+          <t>p73</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Beyond</t>
+          <t>New Notes Akigala Mandarino</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>p63</t>
+          <t>p75</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YSL Y Parfum</t>
+          <t>Parfums de Marly Layton</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>z któymi</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>z którymi</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>p63</t>
+          <t>p75</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>YSL Y Parfum</t>
+          <t>Parfums de Marly Layton</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
+          <t>Fougère ambrowo-owocowa</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>ambrowa</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>p64</t>
+          <t>p76</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>YSL MYSLF Parfum</t>
+          <t>Parfums de Marly Pegasus Exclusif</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -10269,140 +14227,136 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>p65</t>
+          <t>p77</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
+          <t>Parfums de Marly Sedley</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>YSL MYSLF PRAFUM -&gt; myslf prafum</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>p65</t>
+          <t>p78</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
+          <t>Amouage Guidance</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>nazwa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Wiosna, lato, wczesna jesień</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień</t>
+          <t>Guidance</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>potwierdzić u dostawcy wariant: Guidance albo droższy Guidance 46 (inna kompozycja)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>p66</t>
+          <t>p78</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Rabanne Black XS</t>
+          <t>Amouage Guidance</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Jesień, zima (realnie całoroczny)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>jesień, zima</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>p66</t>
+          <t>p80</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Rabanne Black XS</t>
+          <t>Essential Parfums Velvet Iris</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Korzenno-cytrusowa</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>cytrusowa</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>p68</t>
+          <t>p80</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Rabanne One Million</t>
+          <t>Essential Parfums Velvet Iris</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -10412,12 +14366,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Korzenno-słodka</t>
+          <t>Zielono-drzewna z irysem</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>słodka</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -10429,44 +14383,44 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>p69</t>
+          <t>p81</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Azzaro Chrome</t>
+          <t>Essential Parfums Ambre Latte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>wokół Ciebie</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>wokół ciebie</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>p70</t>
+          <t>p81</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Azzaro Forever Wanted Elixir</t>
+          <t>Essential Parfums Ambre Latte</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10493,288 +14447,296 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>p71</t>
+          <t>p82</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Azzaro The Most Wanted Parfum</t>
+          <t>Ormonde Jayne Kashmir</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>Atkinsons Sine Despite Everything -&gt; sine despite everything</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>p71</t>
+          <t>p83</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Azzaro The Most Wanted Parfum</t>
+          <t>Maison Francis Kurkdjian Oud Satin Mood</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Korzenno-drzewna</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>drzewna</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>z01</t>
+          <t>p84</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LV DISCOVERY SET</t>
+          <t>Nishane Wūlóng Chá</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>podobne</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>z01</t>
+          <t>p85</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>LV DISCOVERY SET</t>
+          <t>Sospiro Basso</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Wiosna, lato, wczesna jesień</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>p85</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>Sospiro Basso</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>sklad</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>5 × 5 ml (do ustalenia skład, sugerowane: Torino21, Renaissance, Erba Pura, Uden, Naxos)</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>p06:5, p07:5, p08:5, p09:5, p10:5</t>
-        </is>
-      </c>
+          <t>Terre d'Hermes -&gt; terre d'hermes</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>skład „do ustalenia”; wpisano propozycję ze źródła, zestaw wyłączony</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>p88</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>Tom Ford Oud Voyager</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>sklad</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
+          <t>śweitnie</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>świetnie</t>
+        </is>
+      </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>p88</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>Tom Ford Oud Voyager</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>p88</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>Tom Ford Oud Voyager</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
+          <t>pora</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Wieczór (w dzień przy lekkiej aplikacji)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>z03</t>
+          <t>p89</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NOUS TOUS DISCOVERY SET</t>
+          <t>Kilian Angels' Share</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>cena</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>350 zł</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>cena zapisana jako tekst</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>z03</t>
+          <t>p90</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NOUS TOUS DISCOVERY SET</t>
+          <t>Kilian Angels' Share On The Rocks</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>z03</t>
+          <t>p91</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NOUS TOUS DISCOVERY SET</t>
+          <t>Kilian Roses On Ice</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -10782,161 +14744,177 @@
           <t>opis</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>wieczorem zaś - piękny alkoholowy akcent</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>wieczorem zaś piękny, alkoholowy akcent</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>z04</t>
+          <t>p91</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SWEET &amp; SPICY SET</t>
+          <t>Kilian Roses On Ice</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>gourmand</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>propozycja z opisu zestawu w źródle (gourmand wprost w treści)</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>z04</t>
+          <t>p92</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SWEET &amp; SPICY SET</t>
+          <t>Kilian Woman in Gold</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>z05</t>
+          <t>p93</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>ENTRY SET</t>
+          <t>Kilian Good girl gone Bad</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>sklad</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Amouage Reflection -&gt; reflection</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>Zpach uniwersalny lecz</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Zapach uniwersalny, lecz</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>z05</t>
+          <t>p93</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>ENTRY SET</t>
+          <t>Kilian Good girl gone Bad</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>z05</t>
+          <t>p94</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ENTRY SET</t>
+          <t>Kilian Sparkling Royal</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>z06</t>
+          <t>p94</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>AUTUMN DISCOVERY SET</t>
+          <t>Kilian Sparkling Royal</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>sklad</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>YSL Y le Parfum -&gt; y le parfum</t>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
         </is>
       </c>
       <c r="E114" t="inlineStr"/>
@@ -10949,126 +14927,1062 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>z06</t>
+          <t>p94</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>AUTUMN DISCOVERY SET</t>
+          <t>Kilian Sparkling Royal</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>zdjecie_url</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>z06</t>
+          <t>p95</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>AUTUMN DISCOVERY SET</t>
+          <t>Atkinsons Shine Despite Everything</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr"/>
+          <t>ceny</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>5ml - 140zł | 10ml - 200zł | 20ml - 370zł</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>5 ml 140 zł | 10 ml 200 zł | 20 ml 370 zł</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>ceny identyczne z Kilianem (140/200/370 zł); sprawdzić przed włączeniem sprzedaży</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>z07</t>
+          <t>p96</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>WINTER DISCOVERY SET</t>
+          <t>Atkinsons Oud Save the King</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>sklad</t>
+          <t>ceny</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>5x ml (BOSS Bottled Absolu, MFK Grand Soir, Maison Crivelli Oud Maracuja, Tom Ford Tobacco Vanille, Montale Arabians Tonka)</t>
+          <t>5ml - 140zł | 10ml - 200zł | 20ml - 370zł</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>p60:5, p42:5, p41:5, p35:5, p28:5</t>
+          <t>5 ml 140 zł | 10 ml 200 zł | 20 ml 370 zł</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>w źródle „5x ml” bez pojemności; przyjęto 5 ml</t>
+          <t>ceny identyczne z Kilianem (140/200/370 zł); sprawdzić przed włączeniem sprzedaży</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>z07</t>
+          <t>p97</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>WINTER DISCOVERY SET</t>
+          <t>Atkinsons Mint &amp; Tonic</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>p97</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Atkinsons Mint &amp; Tonic</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ceny</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>5ml - 140zł | 10ml - 200zł | 20ml - 370zł</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>5 ml 140 zł | 10 ml 200 zł | 20 ml 370 zł</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>ceny identyczne z Kilianem (140/200/370 zł); sprawdzić przed włączeniem sprzedaży</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>p98</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Bohoboco Wet Cherry Liquor</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>p98</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Bohoboco Wet Cherry Liquor</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Owocowo-gourmand, w bazie drzewno-waniliowa</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>p98</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Bohoboco Wet Cherry Liquor</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ceny</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>5ml - 140zł | 10ml - 200zł | 20ml - 370zł</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>5 ml 140 zł | 10 ml 200 zł | 20 ml 370 zł</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>ceny identyczne z Kilianem (140/200/370 zł); sprawdzić przed włączeniem sprzedaży</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>p98</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Bohoboco Wet Cherry Liquor</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>p99</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Sisley Soir d'Orient</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>elegankiej</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>eleganckiej</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>p99</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Sisley Soir d'Orient</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Przyprawowo-drzewna</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>p99</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Sisley Soir d'Orient</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ceny</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>5ml - 140zł | 10ml - 200zł | 20ml - 370zł</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>5 ml 140 zł | 10 ml 200 zł | 20 ml 370 zł</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>ceny identyczne z Kilianem (140/200/370 zł); sprawdzić przed włączeniem sprzedaży</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>p99</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Sisley Soir d'Orient</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>p100</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Bohoboco Vanilla Black Pepper</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>p100</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Bohoboco Vanilla Black Pepper</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Korzenno-waniliowa, ambrowa</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>ambrowa</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>p100</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Bohoboco Vanilla Black Pepper</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ceny</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>5ml - 140zł | 10ml - 200zł | 20ml - 370zł</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>5 ml 140 zł | 10 ml 200 zł | 20 ml 370 zł</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>ceny identyczne z Kilianem (140/200/370 zł); sprawdzić przed włączeniem sprzedaży</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>p100</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Bohoboco Vanilla Black Pepper</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>z01</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>LV DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>z01</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>LV DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>z02</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>XERJOFF DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>5 × 5 ml (do ustalenia skład, sugerowane: Torino21, Renaissance, Erba Pura, Uden, Naxos)</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>p06:5, p07:5, p08:5, p09:5, p10:5</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>skład „do ustalenia”; wpisano propozycję ze źródła, zestaw wyłączony</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>z02</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>XERJOFF DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>z02</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>XERJOFF DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>z02</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>XERJOFF DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>z03</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>NOUS TOUS DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>cena</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>350 zł</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>cena zapisana jako tekst</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>z03</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>NOUS TOUS DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>z03</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>NOUS TOUS DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>z04</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SWEET &amp; SPICY SET</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>p34</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>p98</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>zamiana na prośbę właściciela: zestaw ma być dostępny, a składnik ze źródła jest niedostępny</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>z04</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SWEET &amp; SPICY SET</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>propozycja z opisu zestawu w źródle (gourmand wprost w treści)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>z04</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SWEET &amp; SPICY SET</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>z05</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ENTRY SET</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Amouage Reflection -&gt; reflection</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>z05</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>ENTRY SET</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>z05</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ENTRY SET</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>z06</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>AUTUMN DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>YSL Y le Parfum -&gt; y le parfum</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>z06</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>AUTUMN DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>z06</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>AUTUMN DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
           <t>z07</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B150" t="inlineStr">
         <is>
           <t>WINTER DISCOVERY SET</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>5x ml (BOSS Bottled Absolu, MFK Grand Soir, Maison Crivelli Oud Maracuja, Tom Ford Tobacco Vanille, Montale Arabians Tonka)</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>p60:5, p42:5, p41:5, p35:5, p28:5</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>w źródle „5x ml” bez pojemności; przyjęto 5 ml</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>z07</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>WINTER DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>z07</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>WINTER DISCOVERY SET</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
         <is>
           <t>opis</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr">
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
         <is>
           <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>

--- a/dev/dane/import-do-arkusza.xlsx
+++ b/dev/dane/import-do-arkusza.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:AB101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,16 @@
           <t>renoma</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>nowosc</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>odbior</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -657,6 +667,8 @@
       <c r="Z2" t="n">
         <v>3</v>
       </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -740,7 +752,7 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>p03, p21, p07</t>
+          <t>p03, p21, p07, p84</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -765,6 +777,8 @@
       <c r="Z3" t="n">
         <v>2</v>
       </c>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -873,6 +887,8 @@
       <c r="Z4" t="n">
         <v>2</v>
       </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -956,7 +972,7 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>p05, p32, p19, p17</t>
+          <t>p05, p72, p32, p19, p17</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -981,6 +997,8 @@
       <c r="Z5" t="n">
         <v>2</v>
       </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1093,6 +1111,12 @@
       <c r="Z6" t="n">
         <v>3</v>
       </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1201,6 +1225,8 @@
       <c r="Z7" t="n">
         <v>3</v>
       </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1309,6 +1335,8 @@
       <c r="Z8" t="n">
         <v>2</v>
       </c>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1392,7 +1420,7 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>p40, p43, p22, p46, p45</t>
+          <t>p40, p43, p48, p46</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1421,6 +1449,8 @@
       <c r="Z9" t="n">
         <v>3</v>
       </c>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1504,7 +1534,7 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
-          <t>p01, p10, p27, p33</t>
+          <t>p90, p01, p10, p33</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1529,6 +1559,12 @@
       <c r="Z10" t="n">
         <v>2</v>
       </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1612,7 +1648,7 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>p35, p28, p09</t>
+          <t>p89, p35, p28, p09</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1641,6 +1677,12 @@
       <c r="Z11" t="n">
         <v>3</v>
       </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1722,11 +1764,7 @@
         <v>270</v>
       </c>
       <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>p12, p22, p52</t>
-        </is>
-      </c>
+      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>/img/produkty/p11-800.webp</t>
@@ -1753,6 +1791,8 @@
       <c r="Z12" t="n">
         <v>3</v>
       </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1859,6 +1899,8 @@
       <c r="Z13" t="n">
         <v>2</v>
       </c>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1959,6 +2001,8 @@
       <c r="Z14" t="n">
         <v>1</v>
       </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2067,6 +2111,8 @@
       <c r="Z15" t="n">
         <v>2</v>
       </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2175,6 +2221,12 @@
       <c r="Z16" t="n">
         <v>2</v>
       </c>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2258,7 +2310,7 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>p09, p31, p100, p64</t>
+          <t>p85, p31, p43, p64</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2283,6 +2335,8 @@
       <c r="Z17" t="n">
         <v>3</v>
       </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2390,6 +2444,12 @@
       </c>
       <c r="Z18" t="n">
         <v>2</v>
+      </c>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -2491,6 +2551,8 @@
       <c r="Z19" t="n">
         <v>2</v>
       </c>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2599,6 +2661,8 @@
       <c r="Z20" t="n">
         <v>3</v>
       </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2706,6 +2770,12 @@
       </c>
       <c r="Z21" t="n">
         <v>2</v>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -2813,6 +2883,8 @@
       <c r="Z22" t="n">
         <v>2</v>
       </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2919,6 +2991,12 @@
       <c r="Z23" t="n">
         <v>2</v>
       </c>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3025,6 +3103,8 @@
       <c r="Z24" t="n">
         <v>2</v>
       </c>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3131,6 +3211,8 @@
       <c r="Z25" t="n">
         <v>2</v>
       </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3236,6 +3318,12 @@
       </c>
       <c r="Z26" t="n">
         <v>3</v>
+      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -3337,6 +3425,8 @@
       <c r="Z27" t="n">
         <v>1</v>
       </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3443,6 +3533,12 @@
       <c r="Z28" t="n">
         <v>2</v>
       </c>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3549,6 +3645,12 @@
       <c r="Z29" t="n">
         <v>2</v>
       </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3659,6 +3761,8 @@
       <c r="Z30" t="n">
         <v>3</v>
       </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3765,6 +3869,12 @@
       <c r="Z31" t="n">
         <v>2</v>
       </c>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3871,6 +3981,12 @@
       <c r="Z32" t="n">
         <v>2</v>
       </c>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3977,6 +4093,12 @@
       <c r="Z33" t="n">
         <v>3</v>
       </c>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4083,6 +4205,8 @@
       <c r="Z34" t="n">
         <v>2</v>
       </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4187,6 +4311,12 @@
       <c r="Z35" t="n">
         <v>3</v>
       </c>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4298,6 +4428,12 @@
       </c>
       <c r="Z36" t="n">
         <v>3</v>
+      </c>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -4404,6 +4540,12 @@
       </c>
       <c r="Z37" t="n">
         <v>2</v>
+      </c>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -4509,6 +4651,12 @@
       <c r="Z38" t="n">
         <v>3</v>
       </c>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4616,6 +4764,12 @@
       </c>
       <c r="Z39" t="n">
         <v>2</v>
+      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -4723,6 +4877,8 @@
       <c r="Z40" t="n">
         <v>2</v>
       </c>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4833,6 +4989,12 @@
       <c r="Z41" t="n">
         <v>3</v>
       </c>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4941,6 +5103,8 @@
       <c r="Z42" t="n">
         <v>2</v>
       </c>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5049,6 +5213,8 @@
       <c r="Z43" t="n">
         <v>3</v>
       </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5161,6 +5327,8 @@
       <c r="Z44" t="n">
         <v>3</v>
       </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5242,7 +5410,7 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr">
         <is>
-          <t>p73, p39, p65</t>
+          <t>p73, p39, p85, p65</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5270,6 +5438,12 @@
       </c>
       <c r="Z45" t="n">
         <v>3</v>
+      </c>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -5352,7 +5526,7 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
         <is>
-          <t>p01, p09, p46</t>
+          <t>p85, p01, p06, p09, p46</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5381,6 +5555,8 @@
       <c r="Z46" t="n">
         <v>3</v>
       </c>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5462,7 +5638,7 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr">
         <is>
-          <t>p01, p45, p09</t>
+          <t>p01, p06, p85, p45, p21</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5487,6 +5663,8 @@
       <c r="Z47" t="n">
         <v>1</v>
       </c>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5568,7 +5746,7 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
-          <t>p07, p23, p02</t>
+          <t>p94, p91, p07, p84, p02</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5593,6 +5771,8 @@
       <c r="Z48" t="n">
         <v>1</v>
       </c>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5699,6 +5879,12 @@
       <c r="Z49" t="n">
         <v>1</v>
       </c>
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5780,7 +5966,7 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr">
         <is>
-          <t>p39, p41, p20</t>
+          <t>p39, p41, p96</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5804,6 +5990,12 @@
       </c>
       <c r="Z50" t="n">
         <v>1</v>
+      </c>
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -5886,7 +6078,7 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr">
         <is>
-          <t>p49, p33</t>
+          <t>p53, p52, p12, p33</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5911,6 +6103,8 @@
       <c r="Z51" t="n">
         <v>1</v>
       </c>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5992,7 +6186,7 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr">
         <is>
-          <t>p14, p06, p62</t>
+          <t>p21, p14, p06, p62</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6017,6 +6211,8 @@
       <c r="Z52" t="n">
         <v>2</v>
       </c>
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6098,7 +6294,7 @@
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr">
         <is>
-          <t>p53, p54, p11</t>
+          <t>p53, p50, p54, p12</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6123,6 +6319,8 @@
       <c r="Z53" t="n">
         <v>2</v>
       </c>
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6204,7 +6402,7 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr">
         <is>
-          <t>p54, p52, p11, p70</t>
+          <t>p54, p52, p12, p50</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6233,6 +6431,8 @@
       <c r="Z54" t="n">
         <v>3</v>
       </c>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6316,7 +6516,7 @@
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr">
         <is>
-          <t>p53, p38, p05, p41</t>
+          <t>p53, p38, p05, p41, p59</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6341,6 +6541,12 @@
       <c r="Z55" t="n">
         <v>2</v>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6447,6 +6653,8 @@
       <c r="Z56" t="n">
         <v>2</v>
       </c>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6531,7 +6739,11 @@
           <t>p12, p21, p62</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>/img/produkty/p56-800.webp</t>
+        </is>
+      </c>
       <c r="V57" t="n">
         <v>56</v>
       </c>
@@ -6549,6 +6761,8 @@
       <c r="Z57" t="n">
         <v>1</v>
       </c>
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6641,6 +6855,8 @@
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6733,6 +6949,8 @@
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6839,6 +7057,8 @@
       <c r="Z60" t="n">
         <v>2</v>
       </c>
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6941,6 +7161,8 @@
       <c r="Z61" t="n">
         <v>2</v>
       </c>
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7047,6 +7269,8 @@
       <c r="Z62" t="n">
         <v>2</v>
       </c>
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7153,6 +7377,8 @@
       <c r="Z63" t="n">
         <v>2</v>
       </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7234,7 +7460,7 @@
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr">
         <is>
-          <t>p44, p52, p10</t>
+          <t>p52, p10, p64</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -7259,6 +7485,8 @@
       <c r="Z64" t="n">
         <v>2</v>
       </c>
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7340,7 +7568,7 @@
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr">
         <is>
-          <t>p63, p33, p52</t>
+          <t>p63, p33, p52, p85</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7365,6 +7593,8 @@
       <c r="Z65" t="n">
         <v>2</v>
       </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7446,7 +7676,7 @@
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr">
         <is>
-          <t>p44, p11, p45</t>
+          <t>p44, p85, p12, p45</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
@@ -7471,6 +7701,8 @@
       <c r="Z66" t="n">
         <v>3</v>
       </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7575,6 +7807,8 @@
       <c r="Z67" t="n">
         <v>2</v>
       </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7654,7 +7888,7 @@
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr">
         <is>
-          <t>p14, p46</t>
+          <t>p14, p85, p46</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
@@ -7679,6 +7913,8 @@
       <c r="Z68" t="n">
         <v>2</v>
       </c>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7783,6 +8019,8 @@
       <c r="Z69" t="n">
         <v>2</v>
       </c>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7887,6 +8125,8 @@
       <c r="Z70" t="n">
         <v>2</v>
       </c>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7993,6 +8233,8 @@
       <c r="Z71" t="n">
         <v>2</v>
       </c>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8099,6 +8341,8 @@
       <c r="Z72" t="n">
         <v>2</v>
       </c>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8148,7 +8392,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Otulające przyprawy okryte gładką skórą. Słodkawy z zachowanym balansem elegancji, przy czym bardzo uniwersalny. Nada się na randkę jak i na mniej zobowiązujące wyjścia w chłodniejsze dni w roku. Idealne wprowadzenie w zapachy skórzane.</t>
+          <t>Otulające przyprawy okryte gładką skórą. Słodkawy z zachowanym balansem elegancji, przy czym bardzo uniwersalny. Nada się na randkę jak i na mniej zobowiązujące wyjścia w chłodniejsze dni roku. Idealne wprowadzenie w zapachy skórzane oraz niszowe.</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -8180,7 +8424,7 @@
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr">
         <is>
-          <t>p32, p04, p33, p49</t>
+          <t>p32, p04, p96, p33, p49</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -8205,6 +8449,12 @@
       <c r="Z73" t="n">
         <v>2</v>
       </c>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>męski</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8291,7 +8541,11 @@
           <t>p39, p44, p43</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr"/>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>/img/produkty/p73-800.webp</t>
+        </is>
+      </c>
       <c r="V74" t="n">
         <v>73</v>
       </c>
@@ -8308,6 +8562,12 @@
       </c>
       <c r="Z74" t="n">
         <v>1</v>
+      </c>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -8415,6 +8675,12 @@
       <c r="Z75" t="n">
         <v>2</v>
       </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8498,7 +8764,7 @@
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr">
         <is>
-          <t>p89, p52, p10, p71</t>
+          <t>p89, p90, p52, p10, p71</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -8523,6 +8789,8 @@
       <c r="Z76" t="n">
         <v>3</v>
       </c>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8631,6 +8899,8 @@
       <c r="Z77" t="n">
         <v>2</v>
       </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8739,6 +9009,8 @@
       <c r="Z78" t="n">
         <v>2</v>
       </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8847,6 +9119,12 @@
       <c r="Z79" t="n">
         <v>2</v>
       </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8955,6 +9233,8 @@
       <c r="Z80" t="n">
         <v>2</v>
       </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9061,6 +9341,12 @@
       <c r="Z81" t="n">
         <v>1</v>
       </c>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9167,6 +9453,16 @@
       <c r="Z82" t="n">
         <v>1</v>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9216,7 +9512,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Zapach jak ciepły szal narzucony na ramiona pod koniec października. Korzenny i cytrusowy początek, miękkie kwiatowe serce, a na końcu gęste, żywiczne drewno z kadzidłem. Nosi się go cały dzień bez dopsiknięć. Ślad w powietrzu jest wyczuwalny i nikogo nie przytłacza. Ormonde Jayne to marka, której w Polsce praktycznie nie widać, więc ryzyko spotkania kogoś w tym samym zapachu jest bliskie zeru. Świetnie pachnie na kobiecie jak i na mężczyźnie.</t>
+          <t>Zapach jak ciepły szal narzucony na ramiona pod koniec października. Korzenny i cytrusowy początek, miękkie kwiatowe serce, a na końcu gęste, żywiczne drewno z kadzidłem. Nosi się go cały dzień bez dopsikiwania. Ślad w powietrzu jest wyczuwalny i nikogo nie przytłacza. Ormonde Jayne to marka, której w Polsce praktycznie nie widać, więc ryzyko spotkania kogoś w tym samym zapachu jest bliskie zeru. Świetnie pachnie na kobiecie jak i na mężczyźnie.</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -9275,6 +9571,8 @@
       <c r="Z83" t="n">
         <v>1</v>
       </c>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -9324,7 +9622,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Róża i wanilia na ciemnym drewnie, tak gładko, że słowo satin w nazwie nie jest przesadą. Od pierwszej sekundy jest ciepło, bez żadnej surowej fazy, a fiołek dorzuca odrobinę pudru. Zapach układa się wokół ciebie aurą, więc nikomu nie przeszkodzi w restauracji.</t>
+          <t>Róża i wanilia na ciemnym drewnie, tak gładko, że słowo satin w nazwie nie jest przesadą. Od pierwszej sekundy jest ciepło, bez żadnej surowej fazy, a fiołek dorzuca odrobinę pudru. Zapach układa się wokół ciebie aurą, więc nikomu nie przeszkodzi w restauracji, a ponadto zaciekawi otoczenie niezależnie od tego, kto go użyje.</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -9379,6 +9677,12 @@
       <c r="Z84" t="n">
         <v>3</v>
       </c>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -9428,7 +9732,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Cytrusy z herbatą oolong, czyli świeżość, która nie wyparowuje po godzinie. Pachnie jak zimna herbata z cytryną pita w upał, czysto i bez grama słodyczy. Cała sztuczka siedzi w tym, jak mocno jest skoncentrowany: dostajesz lekkie odczucie przy trwałości, jakiej letnie zapachy zwykle nie mają. Jeśli męczy cię to, że twoje świeże perfumy giną po dwóch godzinach, to jest rozwiązanie.</t>
+          <t>Cytrusy z herbatą oolong, czyli świeżość, która nie wyparuje po godzinie. Pachnie jak zimna herbata z cytryną pita w upał, czysto i bez grama słodyczy. Cała sztuczka siedzi w tym, jak mocno jest skoncentrowany: dostajesz ciekawy niuans przy trwałości, jakiego letnie zapachy zwykle nie mają. Jeśli męczy cię to, że twoje świeże perfumy giną po dwóch godzinach, mamy na to rozwiązanie.</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -9485,6 +9789,8 @@
       <c r="Z85" t="n">
         <v>2</v>
       </c>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -9514,7 +9820,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>unisex</t>
+          <t>męski</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -9534,7 +9840,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Grejpfrut, cytryna i zieleń na wejściu, a pod nimi ciemne, pieprzne drewno oraz delikatna słodycz dla równowagi. Brzmi poważnie i trochę surowo, jak dobrze skrojony garnitur w kolorze węgla, dlatego dobrze wypada przy ludziach starszych od ciebie. Bardziej złożona i wzmocniona wersja klasyka od Hermesa.</t>
+          <t>Grejpfrut, cytryna i zieleń na wejściu, a pod nimi eleganckie, pieprzne drewno oraz delikatna słodycz dla równowagi. Brzmi poważnie i trochę surowo, jak dobrze skrojony garnitur w kolorze węgla, dlatego dobrze wypada przy ludziach starszych od ciebie. Uniwersalne pachnidło na cały rok dla mężczyzny z klasą. Bardziej rozbudowana i wzmocniona wersja klasyka od Hermesa.</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -9593,6 +9899,8 @@
       <c r="Z86" t="n">
         <v>1</v>
       </c>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9699,6 +10007,8 @@
       <c r="Z87" t="n">
         <v>2</v>
       </c>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9805,6 +10115,8 @@
       <c r="Z88" t="n">
         <v>3</v>
       </c>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9854,7 +10166,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Oud podany kwiatowo, co na rynku zdarza się rzadko. Geranium z czerwoną piwonią dają jasny, prawie różowy początek, a pod spodem siedzi ciemne, wilgotne drewno z dymem. Mimo wszystko jest to uniwersalne pachnidło dla kobiet i świetnie nada się na bezpieczny prezent. Premiera jest z tego roku, więc nikt wokół go nie zna, pytania o nazwę przychodzą szybko, a na chłodne miesiące wystarczą dwa psiknięcia w dzień.</t>
+          <t>Oud podany kwiatowo, co na rynku zdarza się rzadko. Geranium z czerwoną piwonią dają jasny, prawie różowy początek, a pod spodem siedzi ciemne, wilgotne drewno z dymem. Mimo wszystko jest to uniwersalne pachnidło dla kobiet i świetnie nada się na bezpieczny prezent. Premiera była we wrześniu 2025 roku, więc nikt wokół go nie zna, a pytania o nazwę przychodzą szybko.</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -9913,6 +10225,8 @@
       <c r="Z89" t="n">
         <v>1</v>
       </c>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9999,7 +10313,11 @@
           <t>p10, p35, p24</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr"/>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>/img/produkty/p89-800.webp</t>
+        </is>
+      </c>
       <c r="V90" t="n">
         <v>89</v>
       </c>
@@ -10017,6 +10335,8 @@
       <c r="Z90" t="n">
         <v>3</v>
       </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10066,7 +10386,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Ten sam koniak, tylko polany czymś zimnym. Gorzka pomarańcza i bergamotka kładą na ciepłym rdzeniu chłodną, musującą warstwę, dzięki czemu całość jest lżejsza i mniej słodka od oryginału. Trzyma około sześciu do siedmiu godzin, czyli zauważalnie krócej. Jeśli kupujesz pierwszy flakon z tej linii, weź klasyczny Angels' Share. Ten bierz wtedy, gdy masz już oryginał i chcesz wersję na cieplejsze dni.</t>
+          <t>Ten sam koniak, tylko polany czymś zimnym. Gorzka pomarańcza i bergamotka kładą na ciepłym rdzeniu chłodną, musującą warstwę, dzięki czemu całość jest lżejsza i mniej słodka od oryginału. Trzyma około sześciu do siedmiu godzin. Jeśli kupujesz pierwszy flakon z tej linii, weź klasyczny Angels' Share. Ten bierz wtedy, gdy znasz oryginał i chcesz wersję na cieplejsze dni.</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -10103,7 +10423,11 @@
           <t>p89, p09</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr"/>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>/img/produkty/p90-800.webp</t>
+        </is>
+      </c>
       <c r="V91" t="n">
         <v>90</v>
       </c>
@@ -10121,6 +10445,8 @@
       <c r="Z91" t="n">
         <v>2</v>
       </c>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10207,7 +10533,11 @@
           <t>p47, p23, p97</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr"/>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>/img/produkty/p91-800.webp</t>
+        </is>
+      </c>
       <c r="V92" t="n">
         <v>91</v>
       </c>
@@ -10225,6 +10555,8 @@
       <c r="Z92" t="n">
         <v>2</v>
       </c>
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10311,7 +10643,11 @@
           <t>p93, p83, p73</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr"/>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>/img/produkty/p92-800.webp</t>
+        </is>
+      </c>
       <c r="V93" t="n">
         <v>92</v>
       </c>
@@ -10329,6 +10665,8 @@
       <c r="Z93" t="n">
         <v>1</v>
       </c>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10415,7 +10753,11 @@
           <t>p86, p92</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr"/>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>/img/produkty/p93-800.webp</t>
+        </is>
+      </c>
       <c r="V94" t="n">
         <v>93</v>
       </c>
@@ -10433,6 +10775,8 @@
       <c r="Z94" t="n">
         <v>3</v>
       </c>
+      <c r="AA94" t="inlineStr"/>
+      <c r="AB94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10482,7 +10826,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Kir Royal przełożony na zapach: czarna porzeczka z różą, a nad tym mięta i cytryna, które robią efekt bąbelków. Lekki i elegancki, nosi się go od brunchu po wieczorne wyjście. Kilian podaje ponad pięć godzin trwałości, co przy takiej konstrukcji jest wartością uczciwą, ale nie licz na chmurę w pomieszczeniu. Premiera z sierpnia, więc swoją popularność dopiero zyskuje. Idealny dla kobiet z klasą.</t>
+          <t>Kir Royal przełożony na zapach: czarna porzeczka z różą, a nad tym mięta i cytryna, które robią efekt bąbelków. Lekki i elegancki, nosi się go od brunchu po wieczorne wyjście. Kilian podaje ponad pięć godzin trwałości, co przy takiej konstrukcji jest uczciwą wartością. Premiera z sierpnia, więc swoją popularność dopiero zyskuje. Zapach idealny dla kobiety z klasą.</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -10519,7 +10863,11 @@
           <t>p47, p91, p07</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr"/>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>/img/produkty/p94-800.webp</t>
+        </is>
+      </c>
       <c r="V95" t="n">
         <v>94</v>
       </c>
@@ -10537,6 +10885,12 @@
       <c r="Z95" t="n">
         <v>1</v>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>TAK</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10586,7 +10940,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Karmel i irys na dymnym kadzidle, czyli słodycz, która nie przypomina deseru. Początek jest korzenny i trochę ostry, lecz szybko robi się pudrowo i ciepło z mocnymi akcentami wanilii i drewna. Parfum Intense trzyma dziewięć do dziesięciu godzin, a na ubraniu zostaje po kilka dni. Dobry wybór na formalny zimowy wieczór dla kogoś, kto chce orientalnego pazura i jednocześnie boi się oudu. Świetnie sprawdzi się dla kobiety jak i dla mężczyzny.</t>
+          <t>Karmel i irys na dymnym kadzidle ze sporą dozą wanilii, czyli słodycz, która nie przypomina deseru. Początek jest korzenny i trochę ostry, lecz szybko robi się pudrowo i ciepło z mocnymi akcentami kremowości drewna. Parfum Intense trzyma dziewięć do dziesięciu godzin, a na ubraniu zostaje po kilka dni. Dobry wybór na formalny zimowy wieczór dla kogoś, kto chce orientalnego pazura i jednocześnie boi się oudu. Świetnie sprawdzi się dla kobiety jak i dla mężczyzny.</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -10645,6 +10999,8 @@
       <c r="Z96" t="n">
         <v>1</v>
       </c>
+      <c r="AA96" t="inlineStr"/>
+      <c r="AB96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10694,7 +11050,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Herbata Earl Grey z bergamotką spotyka zamsz i subtelny oud. Efekt jest zaskakująco kulturalny, bo oud jest tu lekki i wygładzony, przez co zapach brzmi jak angielski klub, a nie arabski bazar. Trzyma bardzo długo oraz potrafi wypełnić pomieszczenie. Dobre wejście w oud dla kogoś, kto boi się przesady, zwłaszcza do garnituru.</t>
+          <t>Gorycz herbaty Earl Grey spotyka zamsz i subtelny oud. Efekt jest zaskakująco kulturalny, bo oud jest tu lekki i wygładzony, przez co zapach brzmi jak angielski klub, a nie arabski bazar. Trzyma bardzo długo oraz potrafi wypełnić pomieszczenie. Dobre wejście w oud dla kogoś, kto boi się przesady, zwłaszcza do garnituru.</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -10753,6 +11109,8 @@
       <c r="Z97" t="n">
         <v>2</v>
       </c>
+      <c r="AA97" t="inlineStr"/>
+      <c r="AB97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10802,7 +11160,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Mięta z limonką i grejpfrutem, czyli zapach zimnego drinka w upalny dzień. Lekki, zielony, bez grama słodyczy i bez ciężaru. Trzyma trzy do pięciu godzin i to cała prawda o nim, więc traktuj go jako zapach do odświeżania w ciągu dnia. Na lato i na biuro, kiedy chcesz pachnieć czysto i nic ponad to.</t>
+          <t>Mięta z limonką i grejpfrutem, czyli zapach zimnego drinka w upalny dzień. Lekki, zielony, bez grama słodyczy i bez ciężaru. Nie jest on demonem trwałości, więc traktuj go jako zapach do odświeżania w ciągu dnia. Na lato i na biuro, kiedy chcesz pachnieć czysto i nic ponad to.</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -10861,6 +11219,8 @@
       <c r="Z98" t="n">
         <v>1</v>
       </c>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10910,7 +11270,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Dojrzała wiśnia podlana likierem, z karmelem i różą w tle. Bohoboco zrobiło tu coś, co wielu uważa za dojrzalszą wersję Lost Cherry: mniej cukierka, więcej wytrawności i wyraźne drewno na końcu. Słodko, ale bez lepkości, z trwałością i śladem, które realnie pracują. Polska marka niszowa, co bywa mocnym argumentem dla kogoś, kto szuka czegoś poza oczywistymi nazwami. Idealny dla kobiety jak i mężczyzny.</t>
+          <t>Dojrzała wiśnia podlana likierem, z karmelem i różą w tle. Bohoboco zrobiło tu coś, co wielu uważa za dojrzalszą wersję Lost Cherry: wyraźniejsze parametry, mniej cukierka, więcej wytrawności i wyraźne drewno na końcu. Słodko, ale bez lepkości, z trwałością i śladem, które realnie pracują. Polska marka niszowa, co bywa mocnym argumentem dla kogoś, kto szuka czegoś poza oczywistymi nazwami. Idealny dla kobiety jak i mężczyzny.</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -10965,6 +11325,12 @@
       <c r="Z99" t="n">
         <v>1</v>
       </c>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>damski</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11014,7 +11380,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Szafran, róża i kadzidło, czyli klasyczny orientalny układ zrobiony przez francuski dom kosmetyczny. Otwarcie wypełnia pomieszczenie i brzmi bardzo drogo, a po dwóch godzinach zapach robi się intymny i zostaje blisko skóry. To zapach do eleganckiej garsonki i na wieczory zaplanowane z góry, nie na obiad w mieście. Chłodne miesiące i wieczór, dla kogoś, kto chce brzmieć dostojnie.</t>
+          <t>Szafran, róża i kadzidło, czyli klasyczny orientalny układ zrobiony przez francuski dom kosmetyczny. Otwarcie wypełnia pomieszczenie i brzmi bardzo drogo, a po dwóch godzinach zapach robi się intymny i zostaje blisko skóry. To zapach do eleganckiej garsonki i na wieczory zaplanowane z góry. Na chłodne miesiące i wieczór, dla kogoś, kto chce brzmieć dostojnie.</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -11051,7 +11417,11 @@
           <t>p27, p83, p93</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr"/>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>/img/produkty/p99-800.webp</t>
+        </is>
+      </c>
       <c r="V100" t="n">
         <v>99</v>
       </c>
@@ -11069,6 +11439,8 @@
       <c r="Z100" t="n">
         <v>1</v>
       </c>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11155,7 +11527,11 @@
           <t>p95, p35, p31, p80</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr"/>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>/img/produkty/p100-800.webp</t>
+        </is>
+      </c>
       <c r="V101" t="n">
         <v>100</v>
       </c>
@@ -11173,6 +11549,8 @@
       <c r="Z101" t="n">
         <v>1</v>
       </c>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11429,7 +11807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11743,392 +12121,384 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>p09</t>
+          <t>p08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Xerjoff Uden</t>
+          <t>Xerjoff Erba Pura</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Jesień, zima, wczesna wiosna</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>wiosna, jesień, zima</t>
-        </is>
-      </c>
+          <t>Nous Tous Aurora Sicilliana -&gt; aurora sicilliana</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>p09</t>
+          <t>p08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Xerjoff Uden</t>
+          <t>Xerjoff Erba Pura</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wieczór, chłodny dzień</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>uniwersalna</t>
-        </is>
-      </c>
+          <t>Nous Tous Casa di Caprii -&gt; casa di caprii</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Creed Aventus</t>
+          <t>Xerjoff Uden</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Owocowo-drzewna</t>
+          <t>Jesień, zima, wczesna wiosna</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>wiosna, jesień, zima</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>p11</t>
+          <t>p09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Creed Aventus</t>
+          <t>Xerjoff Uden</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>pora</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
+          <t>Wieczór, chłodny dzień</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>uniwersalna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Creed Absolu Aventus</t>
+          <t>Creed Aventus</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Owocowo-drzewna</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>p12</t>
+          <t>p11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Creed Absolu Aventus</t>
+          <t>Creed Aventus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>owocowo-drzewna</t>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>p13</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Creed Virgin Island Water</t>
+          <t>Creed Absolu Aventus</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nazwa</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Virgin Island Water</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Virgin Island Water</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>nazwa do potwierdzenia (w ofercie „Virgin Mountain Water”)</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>p13</t>
+          <t>p12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Creed Virgin Island Water</t>
+          <t>Creed Absolu Aventus</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
+          <t>owocowo-drzewna</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>p14</t>
+          <t>p13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Creed Silver Mountain Water</t>
+          <t>Creed Virgin Island Water</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nazwa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>zielono-herbaciana</t>
+          <t>Virgin Island Water</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>świeża</t>
+          <t>Virgin Island Water</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>nazwa do potwierdzenia (w ofercie „Virgin Mountain Water”)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>p14</t>
+          <t>p13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Creed Silver Mountain Water</t>
+          <t>Creed Virgin Island Water</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>NIEDOSTĘPNY</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Amouage Search</t>
+          <t>Creed Silver Mountain Water</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Wiosna, jesień (uniwersalny)</t>
+          <t>zielono-herbaciana</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>wiosna, jesień</t>
+          <t>świeża</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>p15</t>
+          <t>p14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Amouage Search</t>
+          <t>Creed Silver Mountain Water</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ceny</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5 ml – 120 zł | 10 ml – 220 zł | 20 ml – 400 zł (promocja)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>5 ml 120 zł | 10 ml 220 zł | 20 ml 400 zł</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>cena oznaczona jako promocja; API nie ma pola na starą cenę, pokażemy ją jako zwykłą</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Amouage Reflection Man</t>
+          <t>Amouage Search</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -12138,12 +12508,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
+          <t>Wiosna, jesień (uniwersalny)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>wiosna, jesień</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -12155,92 +12525,92 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>p16</t>
+          <t>p15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Amouage Reflection Man</t>
+          <t>Amouage Search</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>ceny</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>MFK Baccarat Rouge</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>5 ml – 120 zł | 10 ml – 220 zł | 20 ml – 400 zł (promocja)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>5 ml 120 zł | 10 ml 220 zł | 20 ml 400 zł</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>nazwa nie pasuje do żadnej pozycji katalogu</t>
+          <t>cena oznaczona jako promocja; API nie ma pola na starą cenę, pokażemy ją jako zwykłą</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Amouage Interlude Black Iris</t>
+          <t>Amouage Reflection Man</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>pewność danych: niska</t>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>p18</t>
+          <t>p16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Amouage Interlude Black Iris</t>
+          <t>Amouage Reflection Man</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Irysowo-kadzidlana</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>kwiatowa</t>
-        </is>
-      </c>
+          <t>MFK Baccarat Rouge -&gt; baccarat rouge</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
@@ -12257,34 +12627,34 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>aktywny</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
+          <t>pewność danych: niska</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Amouage Interlude Man</t>
+          <t>Amouage Interlude Black Iris</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -12294,12 +12664,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Dymno-żywiczna</t>
+          <t>Irysowo-kadzidlana</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>kwiatowa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -12311,104 +12681,108 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>p19</t>
+          <t>p18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Amouage Interlude Man</t>
+          <t>Amouage Interlude Black Iris</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Zima, późna jesień</t>
+          <t>NIEDOSTĘPNY</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>jesień, zima</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>p21</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mancera Lemon Line</t>
+          <t>Amouage Interlude Man</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Dymno-żywiczna</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>p21</t>
+          <t>p19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mancera Lemon Line</t>
+          <t>Amouage Interlude Man</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>Zima, późna jesień</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>p24</t>
+          <t>p21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mancera Tonka Cola</t>
+          <t>Mancera Lemon Line</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -12435,264 +12809,260 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>p21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mancera Red Tobacco</t>
+          <t>Mancera Lemon Line</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>p24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mancera Red Tobacco</t>
+          <t>Mancera Tonka Cola</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Korzenna</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>orientalna</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>p26</t>
+          <t>p25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mancera Instant Crush</t>
+          <t>Mancera Red Tobacco</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>aktywny</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>pewność danych: niska</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>NIE</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>p26</t>
+          <t>p25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mancera Instant Crush</t>
+          <t>Mancera Red Tobacco</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
+          <t>Korzenna</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>orientalna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>p30</t>
+          <t>p26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Montale Honey Aoud</t>
+          <t>Mancera Instant Crush</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>aktywny</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>pewność danych: niska</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>p31</t>
+          <t>p26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Montale Intense Pepper</t>
+          <t>Mancera Instant Crush</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Amouage Reflection -&gt; reflection</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
+          <t>NIEDOSTĘPNY</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>p33</t>
+          <t>p30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tom Ford Noir Extreme</t>
+          <t>Montale Honey Aoud</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Korzenno-gourmand</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>gourmand</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>p34</t>
+          <t>p31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tom Ford Lost Cherry</t>
+          <t>Montale Intense Pepper</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+          <t>Amouage Reflection -&gt; reflection</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>p35</t>
+          <t>p33</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tom Ford Tobacco Vanille</t>
+          <t>Tom Ford Noir Extreme</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -12719,204 +13089,204 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>p36</t>
+          <t>p34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tom Ford Bois Pacifique</t>
+          <t>Tom Ford Lost Cherry</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Jesień, zima, wczesna wiosna</t>
+          <t>NIEDOSTĘPNY</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>wiosna, jesień, zima</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>p37</t>
+          <t>p35</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tom Ford Oud Wood</t>
+          <t>Tom Ford Tobacco Vanille</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ml_dostepne</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NIEDOSTĘPNY</t>
+          <t>Korzenno-gourmand</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>gourmand</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>p38</t>
+          <t>p36</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tom Ford Ébène Fumé</t>
+          <t>Tom Ford Bois Pacifique</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Jesień, zima, wczesna wiosna</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>wiosna, jesień, zima</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>p38</t>
+          <t>p37</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tom Ford Ébène Fumé</t>
+          <t>Tom Ford Oud Wood</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>ml_dostepne</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Dymno-drzewna</t>
+          <t>NIEDOSTĘPNY</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>niedostępny w źródle; karta pokaże „Wyprzedane” i podobne</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>p39</t>
+          <t>p38</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Marc-Antoine Barrois Ganymede</t>
+          <t>Tom Ford Ébène Fumé</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Wiosna, jesień (uniwersalny)</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>wiosna, jesień</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>p39</t>
+          <t>p38</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Marc-Antoine Barrois Ganymede</t>
+          <t>Tom Ford Ébène Fumé</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ceny</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5 ml – 70 zł | 10 ml – 140 zł (?) | 20 ml – 250 zł</t>
+          <t>Dymno-drzewna</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>5 ml 70 zł | 20 ml 250 zł</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>cena 10 ml oznaczona w źródle jako niepewna "(?)", wariant pominięty do potwierdzenia</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>p40</t>
+          <t>p39</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tiziana Terenzi Kirke</t>
+          <t>Marc-Antoine Barrois Ganymede</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -12926,12 +13296,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
+          <t>Wiosna, jesień (uniwersalny)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>wiosna, jesień</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -12943,44 +13313,44 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>p41</t>
+          <t>p39</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Maison Crivelli Oud Maracujá</t>
+          <t>Marc-Antoine Barrois Ganymede</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>ceny</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Owocowo-agarowa</t>
+          <t>5 ml – 70 zł | 10 ml – 140 zł (?) | 20 ml – 250 zł</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>słodka</t>
+          <t>5 ml 70 zł | 20 ml 250 zł</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>cena 10 ml oznaczona w źródle jako niepewna "(?)", wariant pominięty do potwierdzenia</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>p41</t>
+          <t>p40</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Maison Crivelli Oud Maracujá</t>
+          <t>Tiziana Terenzi Kirke</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -12990,12 +13360,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Jesień, zima, chłodna wiosna</t>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>wiosna, jesień, zima</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -13007,416 +13377,436 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
+          <t>Maison Crivelli Oud Maracujá</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej jesień i zima</t>
+          <t>Owocowo-agarowa</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>słodka</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>p43</t>
+          <t>p41</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
+          <t>Maison Crivelli Oud Maracujá</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wieczór (działa też w dzień)</t>
+          <t>Jesień, zima, chłodna wiosna</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>uniwersalna</t>
+          <t>wiosna, jesień, zima</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>p47</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nous Tous Secco di Como</t>
+          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>Cały rok, najlepiej jesień i zima</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień, zima</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>p48</t>
+          <t>p43</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nous Tous Aurora Siciliana</t>
+          <t>Maison Francis Kurkdjian Baccarat Rouge 540</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>pora</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Owocowo-kwiatowa</t>
+          <t>Wieczór (działa też w dzień)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>kwiatowa</t>
+          <t>uniwersalna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>p50</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nous Tous Milano 3AM</t>
+          <t>Nous Tous Secco di Como</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>korzenna</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>orientalna</t>
-        </is>
-      </c>
+          <t>Kilian Sparkling Royale -&gt; sparkling royale</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>p50</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Nous Tous Milano 3AM</t>
+          <t>Nous Tous Secco di Como</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej chłodne wieczory</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>wiosna, lato, jesień, zima</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>p53</t>
+          <t>p47</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Dior Sauvage Elixir</t>
+          <t>Nous Tous Secco di Como</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Korzenno-ambrowa</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>ambrowa</t>
-        </is>
-      </c>
+          <t>Nishane Woolong Cha -&gt; woolong cha</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>p55</t>
+          <t>p48</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Versace Eros Parfum</t>
+          <t>Nous Tous Aurora Siciliana</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Owocowo-kwiatowa</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>kwiatowa</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>p56</t>
+          <t>p50</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Versace Eros Energy</t>
+          <t>Nous Tous Milano 3AM</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>korzenna</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>orientalna</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p50</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Versace</t>
+          <t>Nous Tous Milano 3AM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>marka, nazwa</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Cały rok, najlepiej chłodne wieczory</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień, zima</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p50</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Versace</t>
+          <t>Nous Tous Milano 3AM</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Korzenno-drzewna</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>drzewna</t>
-        </is>
-      </c>
+          <t>Creed Aventus Absolu -&gt; aventus absolu</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>p57</t>
+          <t>p52</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Versace</t>
+          <t>Dior Sauvage Parfum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>podobne</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Creed Aventus Absolu -&gt; aventus absolu</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p53</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Versace</t>
+          <t>Dior Sauvage Elixir</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>marka, nazwa</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Korzenno-ambrowa</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ambrowa</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>p58</t>
+          <t>p53</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Versace</t>
+          <t>Dior Sauvage Elixir</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>podobne</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Creed Aventus Absolu -&gt; aventus absolu</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>p59</t>
+          <t>p55</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Elixir</t>
+          <t>Versace Eros Parfum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -13443,76 +13833,64 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>p59</t>
+          <t>p56</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Elixir</t>
+          <t>Versace Eros Energy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Korzenno-drzewna</t>
-        </is>
-      </c>
+          <t>nazwa</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>Eros Energy</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>komórka z nazwą pusta od 8.10.2026, reszta wiersza bez zmian; nazwa uzupełniona, potwierdzić albo ustawić status Niedostępny</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>p60</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Absolu</t>
+          <t>Versace</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>aktywny</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>pewność danych: niska</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>NIE</t>
-        </is>
-      </c>
+          <t>marka, nazwa</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
+          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>p60</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Absolu</t>
+          <t>Versace</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -13522,12 +13900,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Korzenno-gourmand</t>
+          <t>Korzenno-drzewna</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>gourmand</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13539,12 +13917,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>p60</t>
+          <t>p57</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Absolu</t>
+          <t>Versace</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -13563,332 +13941,308 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>p61</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hugo Boss Bottled Beyond</t>
+          <t>Versace</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>marka, nazwa</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak marki i nazwy; pozycja wyłączona do czasu uzupełnienia</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>p63</t>
+          <t>p58</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>YSL Y Parfum</t>
+          <t>Versace</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>p63</t>
+          <t>p59</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>YSL Y Parfum</t>
+          <t>Hugo Boss Bottled Elixir</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cały rok, najlepiej wiosna i jesień</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień, zima</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>p64</t>
+          <t>p59</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>YSL MYSLF Parfum</t>
+          <t>Hugo Boss Bottled Elixir</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Korzenno-drzewna</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>p65</t>
+          <t>p60</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
+          <t>Hugo Boss Bottled Absolu</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>aktywny</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>pewność danych: niska</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>NIE</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>instrukcja arkusza: nie publikować bez weryfikacji piramidy nut</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>p65</t>
+          <t>p60</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
+          <t>Hugo Boss Bottled Absolu</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Wiosna, lato, wczesna jesień</t>
+          <t>Korzenno-gourmand</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień</t>
+          <t>gourmand</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>p66</t>
+          <t>p60</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Rabanne Black XS</t>
+          <t>Hugo Boss Bottled Absolu</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>p66</t>
+          <t>p61</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Rabanne Black XS</t>
+          <t>Hugo Boss Bottled Beyond</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Korzenno-cytrusowa</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>cytrusowa</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>p68</t>
+          <t>p63</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Rabanne One Million</t>
+          <t>YSL Y Parfum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Korzenno-słodka</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>słodka</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>p69</t>
+          <t>p63</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Azzaro Chrome</t>
+          <t>YSL Y Parfum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Cały rok, najlepiej wiosna i jesień</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>wiosna, lato, jesień, zima</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>p70</t>
+          <t>p64</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Azzaro Forever Wanted Elixir</t>
+          <t>YSL MYSLF Parfum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -13915,12 +14269,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>p71</t>
+          <t>p65</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Azzaro The Most Wanted Parfum</t>
+          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -13947,140 +14301,136 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>p71</t>
+          <t>p65</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Azzaro The Most Wanted Parfum</t>
+          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Korzenno-drzewna</t>
+          <t>Wiosna, lato, wczesna jesień</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>wiosna, lato, jesień</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>p72</t>
+          <t>p65</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Carner Barcelona Cuirs</t>
+          <t>Hermès Terre d'Hermès Eau Intense Vétiver</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>nuty / opis</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>pewność danych: Do weryfikacji</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>Creed Aventus Absolu -&gt; aventus absolu</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>w źródle bez potwierdzenia nut i opisu; zweryfikować przed publikacją</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>p73</t>
+          <t>p66</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>New Notes Akigala Mandarino</t>
+          <t>Rabanne Black XS</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>słońcu, a tle mineralne</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>słońcu, a w tle mineralne</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>p73</t>
+          <t>p66</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>New Notes Akigala Mandarino</t>
+          <t>Rabanne Black XS</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Korzenno-cytrusowa</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>cytrusowa</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>p73</t>
+          <t>p68</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>New Notes Akigala Mandarino</t>
+          <t>Rabanne One Million</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -14090,12 +14440,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Owocowo-drzewna</t>
+          <t>Korzenno-słodka</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>słodka</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -14107,320 +14457,332 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>p73</t>
+          <t>p69</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>New Notes Akigala Mandarino</t>
+          <t>Azzaro Chrome</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>p75</t>
+          <t>p70</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Parfums de Marly Layton</t>
+          <t>Azzaro Forever Wanted Elixir</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>z któymi</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>z którymi</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>p75</t>
+          <t>p71</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Parfums de Marly Layton</t>
+          <t>Azzaro The Most Wanted Parfum</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Fougère ambrowo-owocowa</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ambrowa</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>p76</t>
+          <t>p71</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Parfums de Marly Pegasus Exclusif</t>
+          <t>Azzaro The Most Wanted Parfum</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Korzenno-drzewna</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>p77</t>
+          <t>p72</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Parfums de Marly Sedley</t>
+          <t>Carner Barcelona Cuirs</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>nuty / opis</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>YSL MYSLF PRAFUM -&gt; myslf prafum</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr"/>
+          <t>pewność danych: Do weryfikacji</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>w źródle bez potwierdzenia nut i opisu; zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>p78</t>
+          <t>p73</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Amouage Guidance</t>
+          <t>New Notes Akigala Mandarino</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>nazwa</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>słońcu, a tle mineralne</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Guidance</t>
+          <t>słońcu, a w tle mineralne</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>potwierdzić u dostawcy wariant: Guidance albo droższy Guidance 46 (inna kompozycja)</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>p78</t>
+          <t>p73</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Amouage Guidance</t>
+          <t>New Notes Akigala Mandarino</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Jesień, zima (realnie całoroczny)</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>jesień, zima</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>p80</t>
+          <t>p73</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Essential Parfums Velvet Iris</t>
+          <t>New Notes Akigala Mandarino</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Owocowo-drzewna</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>p80</t>
+          <t>p75</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Essential Parfums Velvet Iris</t>
+          <t>Parfums de Marly Layton</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Zielono-drzewna z irysem</t>
+          <t>z któymi</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>z którymi</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>p81</t>
+          <t>p75</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Essential Parfums Ambre Latte</t>
+          <t>Parfums de Marly Layton</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>wokół Ciebie</t>
+          <t>Fougère ambrowo-owocowa</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>wokół ciebie</t>
+          <t>ambrowa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>p81</t>
+          <t>p76</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Essential Parfums Ambre Latte</t>
+          <t>Parfums de Marly Pegasus Exclusif</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -14447,12 +14809,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>p82</t>
+          <t>p77</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ormonde Jayne Kashmir</t>
+          <t>Parfums de Marly Sedley</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -14462,7 +14824,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Atkinsons Sine Despite Everything -&gt; sine despite everything</t>
+          <t>YSL MYSLF PRAFUM -&gt; myslf prafum</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -14475,124 +14837,140 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>p83</t>
+          <t>p78</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Maison Francis Kurkdjian Oud Satin Mood</t>
+          <t>Amouage Guidance</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr"/>
+          <t>nazwa</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>potwierdzić u dostawcy wariant: Guidance albo droższy Guidance 46 (inna kompozycja)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>p84</t>
+          <t>p78</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Nishane Wūlóng Chá</t>
+          <t>Amouage Guidance</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr"/>
+          <t>Jesień, zima (realnie całoroczny)</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>jesień, zima</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>p85</t>
+          <t>p80</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Sospiro Basso</t>
+          <t>Essential Parfums Velvet Iris</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Wiosna, lato, wczesna jesień</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>wiosna, lato, jesień</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>p85</t>
+          <t>p80</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sospiro Basso</t>
+          <t>Essential Parfums Velvet Iris</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Terre d'Hermes -&gt; terre d'hermes</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
+          <t>Zielono-drzewna z irysem</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>p88</t>
+          <t>p81</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tom Ford Oud Voyager</t>
+          <t>Essential Parfums Ambre Latte</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -14602,12 +14980,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>śweitnie</t>
+          <t>wokół Ciebie</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>świetnie</t>
+          <t>wokół ciebie</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -14619,12 +14997,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>p88</t>
+          <t>p81</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Tom Ford Oud Voyager</t>
+          <t>Essential Parfums Ambre Latte</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -14651,68 +15029,72 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>p88</t>
+          <t>p82</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tom Ford Oud Voyager</t>
+          <t>Ormonde Jayne Kashmir</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Wieczór (w dzień przy lekkiej aplikacji)</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>uniwersalna</t>
-        </is>
-      </c>
+          <t>Atkinsons Sine Despite Everything -&gt; sine despite everything</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>p89</t>
+          <t>p83</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kilian Angels' Share</t>
+          <t>Maison Francis Kurkdjian Oud Satin Mood</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>niezależnie od tego kto</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>niezależnie od tego, kto</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>p90</t>
+          <t>p83</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kilian Angels' Share On The Rocks</t>
+          <t>Maison Francis Kurkdjian Oud Satin Mood</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -14731,12 +15113,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>p91</t>
+          <t>p84</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kilian Roses On Ice</t>
+          <t>Nishane Wūlóng Chá</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -14746,12 +15128,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>wieczorem zaś - piękny alkoholowy akcent</t>
+          <t>cikawy niuans</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>wieczorem zaś piękny, alkoholowy akcent</t>
+          <t>ciekawy niuans</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -14763,116 +15145,132 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>p91</t>
+          <t>p84</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kilian Roses On Ice</t>
+          <t>Nishane Wūlóng Chá</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>podobne</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>p92</t>
+          <t>p85</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kilian Woman in Gold</t>
+          <t>Sospiro Basso</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr"/>
+          <t>sezon</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Wiosna, lato, wczesna jesień</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>p93</t>
+          <t>p85</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kilian Good girl gone Bad</t>
+          <t>Sospiro Basso</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Zpach uniwersalny lecz</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Zapach uniwersalny, lecz</t>
-        </is>
-      </c>
+          <t>Terre d'Hermes -&gt; terre d'hermes</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>p93</t>
+          <t>p88</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Kilian Good girl gone Bad</t>
+          <t>Tom Ford Oud Voyager</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Premiera jest z tego roku</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Premiera była we wrześniu 2025 roku</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>nieaktualna informacja: Oud Voyager jest w sklepach od września 2025, nie z 2026</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>p94</t>
+          <t>p88</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Kilian Sparkling Royal</t>
+          <t>Tom Ford Oud Voyager</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -14899,344 +15297,360 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>p94</t>
+          <t>p88</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Kilian Sparkling Royal</t>
+          <t>Tom Ford Oud Voyager</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>pora</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr"/>
+          <t>Wieczór (w dzień przy lekkiej aplikacji)</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>uniwersalna</t>
+        </is>
+      </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>p94</t>
+          <t>p90</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Kilian Sparkling Royal</t>
+          <t>Kilian Angels' Share On The Rocks</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr"/>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>gdyznasz</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>gdy znasz</t>
+        </is>
+      </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>p95</t>
+          <t>p91</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Atkinsons Shine Despite Everything</t>
+          <t>Kilian Roses On Ice</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ceny</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>5ml - 140zł | 10ml - 200zł | 20ml - 370zł</t>
+          <t>wieczorem zaś - piękny alkoholowy akcent</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>5 ml 140 zł | 10 ml 200 zł | 20 ml 370 zł</t>
+          <t>wieczorem zaś piękny, alkoholowy akcent</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>ceny identyczne z Kilianem (140/200/370 zł); sprawdzić przed włączeniem sprzedaży</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>p96</t>
+          <t>p93</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Atkinsons Oud Save the King</t>
+          <t>Kilian Good girl gone Bad</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ceny</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>5ml - 140zł | 10ml - 200zł | 20ml - 370zł</t>
+          <t>Zpach uniwersalny lecz</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>5 ml 140 zł | 10 ml 200 zł | 20 ml 370 zł</t>
+          <t>Zapach uniwersalny, lecz</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>ceny identyczne z Kilianem (140/200/370 zł); sprawdzić przed włączeniem sprzedaży</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>p97</t>
+          <t>p94</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Atkinsons Mint &amp; Tonic</t>
+          <t>Kilian Sparkling Royal</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>zyskuje.Zapach</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>zyskuje. Zapach</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>p97</t>
+          <t>p94</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Atkinsons Mint &amp; Tonic</t>
+          <t>Kilian Sparkling Royal</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ceny</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>5ml - 140zł | 10ml - 200zł | 20ml - 370zł</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>5 ml 140 zł | 10 ml 200 zł | 20 ml 370 zł</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>ceny identyczne z Kilianem (140/200/370 zł); sprawdzić przed włączeniem sprzedaży</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>p98</t>
+          <t>p94</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Bohoboco Wet Cherry Liquor</t>
+          <t>Kilian Sparkling Royal</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>p98</t>
+          <t>p95</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Bohoboco Wet Cherry Liquor</t>
+          <t>Atkinsons Shine Despite Everything</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Owocowo-gourmand, w bazie drzewno-waniliowa</t>
+          <t>akcentami  kremowości</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>gourmand</t>
+          <t>akcentami kremowości</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>p98</t>
+          <t>p96</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Bohoboco Wet Cherry Liquor</t>
+          <t>Atkinsons Oud Save the King</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>ceny</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>5ml - 140zł | 10ml - 200zł | 20ml - 370zł</t>
+          <t>Earl Greyspotyka</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>5 ml 140 zł | 10 ml 200 zł | 20 ml 370 zł</t>
+          <t>Earl Grey spotyka</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>ceny identyczne z Kilianem (140/200/370 zł); sprawdzić przed włączeniem sprzedaży</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>p98</t>
+          <t>p97</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Bohoboco Wet Cherry Liquor</t>
+          <t>Atkinsons Mint &amp; Tonic</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
+          <t>nuty / osiągi</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>pewność danych: średnia</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>bez zmian</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>p99</t>
+          <t>p98</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Sisley Soir d'Orient</t>
+          <t>Bohoboco Wet Cherry Liquor</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>elegankiej</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>eleganckiej</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>p99</t>
+          <t>p98</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Sisley Soir d'Orient</t>
+          <t>Bohoboco Wet Cherry Liquor</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -15246,12 +15660,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Przyprawowo-drzewna</t>
+          <t>Owocowo-gourmand, w bazie drzewno-waniliowa</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>gourmand</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -15263,32 +15677,24 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>p99</t>
+          <t>p98</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Sisley Soir d'Orient</t>
+          <t>Bohoboco Wet Cherry Liquor</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ceny</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>5ml - 140zł | 10ml - 200zł | 20ml - 370zł</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>5 ml 140 zł | 10 ml 200 zł | 20 ml 370 zł</t>
-        </is>
-      </c>
+          <t>zdjecie_url</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>ceny identyczne z Kilianem (140/200/370 zł); sprawdzić przed włączeniem sprzedaży</t>
+          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
         </is>
       </c>
     </row>
@@ -15305,46 +15711,54 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>elegankiej</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>eleganckiej</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>p99</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bohoboco Vanilla Black Pepper</t>
+          <t>Sisley Soir d'Orient</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Przyprawowo-drzewna</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>drzewna</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
@@ -15361,22 +15775,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Korzenno-waniliowa, ambrowa</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>ambrowa</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
@@ -15393,46 +15807,46 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ceny</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>5ml - 140zł | 10ml - 200zł | 20ml - 370zł</t>
+          <t>Korzenno-waniliowa, ambrowa</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>5 ml 140 zł | 10 ml 200 zł | 20 ml 370 zł</t>
+          <t>ambrowa</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>ceny identyczne z Kilianem (140/200/370 zł); sprawdzić przed włączeniem sprzedaży</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>z01</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bohoboco Vanilla Black Pepper</t>
+          <t>LV DISCOVERY SET</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -15449,38 +15863,46 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>z01</t>
+          <t>z02</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>LV DISCOVERY SET</t>
+          <t>XERJOFF DISCOVERY SET</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>5 × 5 ml (do ustalenia skład, sugerowane: Torino21, Renaissance, Erba Pura, Uden, Naxos)</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>p06:5, p07:5, p08:5, p09:5, p10:5</t>
+        </is>
+      </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>skład „do ustalenia”; wpisano propozycję ze źródła, zestaw wyłączony</t>
         </is>
       </c>
     </row>
@@ -15502,17 +15924,13 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>5 × 5 ml (do ustalenia skład, sugerowane: Torino21, Renaissance, Erba Pura, Uden, Naxos)</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>p06:5, p07:5, p08:5, p09:5, p10:5</t>
-        </is>
-      </c>
+          <t>Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>skład „do ustalenia”; wpisano propozycję ze źródła, zestaw wyłączony</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
@@ -15529,18 +15947,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -15557,38 +15971,46 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>z03</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>NOUS TOUS DISCOVERY SET</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr"/>
+          <t>cena</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>350 zł</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>cena zapisana jako tekst</t>
         </is>
       </c>
     </row>
@@ -15605,22 +16027,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>cena</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>350 zł</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>cena zapisana jako tekst</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -15637,38 +16051,46 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>z03</t>
+          <t>z04</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>NOUS TOUS DISCOVERY SET</t>
+          <t>SWEET &amp; SPICY SET</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>p34</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>p98</t>
+        </is>
+      </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>zamiana na prośbę właściciela: zestaw ma być dostępny, a składnik ze źródła jest niedostępny</t>
         </is>
       </c>
     </row>
@@ -15685,22 +16107,18 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>p34</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>p98</t>
+          <t>gourmand</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>zamiana na prośbę właściciela: zestaw ma być dostępny, a składnik ze źródła jest niedostępny</t>
+          <t>propozycja z opisu zestawu w źródle (gourmand wprost w treści)</t>
         </is>
       </c>
     </row>
@@ -15717,42 +16135,42 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>gourmand</t>
-        </is>
-      </c>
+      <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>propozycja z opisu zestawu w źródle (gourmand wprost w treści)</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>z04</t>
+          <t>z05</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>SWEET &amp; SPICY SET</t>
+          <t>ENTRY SET</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Amouage Reflection -&gt; reflection</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
@@ -15769,18 +16187,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>Amouage Reflection -&gt; reflection</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -15797,38 +16211,42 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>z05</t>
+          <t>z06</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ENTRY SET</t>
+          <t>AUTUMN DISCOVERY SET</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>YSL Y le Parfum -&gt; y le parfum</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
@@ -15845,18 +16263,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>YSL Y le Parfum -&gt; y le parfum</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -15873,38 +16287,46 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>z06</t>
+          <t>z07</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>AUTUMN DISCOVERY SET</t>
+          <t>WINTER DISCOVERY SET</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>5x ml (BOSS Bottled Absolu, MFK Grand Soir, Maison Crivelli Oud Maracuja, Tom Ford Tobacco Vanille, Montale Arabians Tonka)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>p60:5, p42:5, p41:5, p35:5, p28:5</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>w źródle „5x ml” bez pojemności; przyjęto 5 ml</t>
         </is>
       </c>
     </row>
@@ -15921,22 +16343,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>5x ml (BOSS Bottled Absolu, MFK Grand Soir, Maison Crivelli Oud Maracuja, Tom Ford Tobacco Vanille, Montale Arabians Tonka)</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>p60:5, p42:5, p41:5, p35:5, p28:5</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>w źródle „5x ml” bez pojemności; przyjęto 5 ml</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -15953,36 +16367,12 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr">
-        <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>z07</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>WINTER DISCOVERY SET</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr">
         <is>
           <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>

--- a/dev/dane/import-do-arkusza.xlsx
+++ b/dev/dane/import-do-arkusza.xlsx
@@ -9659,7 +9659,11 @@
           <t>p43, p30, p49</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr"/>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>/img/produkty/p83-800.webp</t>
+        </is>
+      </c>
       <c r="V84" t="n">
         <v>83</v>
       </c>
@@ -11307,7 +11311,11 @@
           <t>p34, p27</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr"/>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>/img/produkty/p98-800.webp</t>
+        </is>
+      </c>
       <c r="V99" t="n">
         <v>98</v>
       </c>
@@ -11807,7 +11815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15089,24 +15097,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>p83</t>
+          <t>p84</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Maison Francis Kurkdjian Oud Satin Mood</t>
+          <t>Nishane Wūlóng Chá</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>cikawy niuans</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>ciekawy niuans</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
@@ -15123,50 +15139,50 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>cikawy niuans</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>ciekawy niuans</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>p84</t>
+          <t>p85</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Nishane Wūlóng Chá</t>
+          <t>Sospiro Basso</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>sezon</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr"/>
+          <t>Wiosna, lato, wczesna jesień</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>wiosna, lato, jesień</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>uproszczono do listy pór roku</t>
         </is>
       </c>
     </row>
@@ -15183,50 +15199,50 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>sezon</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Wiosna, lato, wczesna jesień</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>wiosna, lato, jesień</t>
-        </is>
-      </c>
+          <t>Terre d'Hermes -&gt; terre d'hermes</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>uproszczono do listy pór roku</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>p85</t>
+          <t>p88</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sospiro Basso</t>
+          <t>Tom Ford Oud Voyager</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Terre d'Hermes -&gt; terre d'hermes</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>Premiera jest z tego roku</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Premiera była we wrześniu 2025 roku</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>nieaktualna informacja: Oud Voyager jest w sklepach od września 2025, nie z 2026</t>
         </is>
       </c>
     </row>
@@ -15243,22 +15259,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Premiera jest z tego roku</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Premiera była we wrześniu 2025 roku</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>nieaktualna informacja: Oud Voyager jest w sklepach od września 2025, nie z 2026</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
@@ -15275,66 +15291,66 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>pora</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Wieczór (w dzień przy lekkiej aplikacji)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>uniwersalna</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>p88</t>
+          <t>p90</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tom Ford Oud Voyager</t>
+          <t>Kilian Angels' Share On The Rocks</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>pora</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Wieczór (w dzień przy lekkiej aplikacji)</t>
+          <t>gdyznasz</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>uniwersalna</t>
+          <t>gdy znasz</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>uproszczono do: dzień, wieczór, uniwersalna</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>p90</t>
+          <t>p91</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Kilian Angels' Share On The Rocks</t>
+          <t>Kilian Roses On Ice</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -15344,12 +15360,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>gdyznasz</t>
+          <t>wieczorem zaś - piękny alkoholowy akcent</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>gdy znasz</t>
+          <t>wieczorem zaś piękny, alkoholowy akcent</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -15361,12 +15377,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>p91</t>
+          <t>p93</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Kilian Roses On Ice</t>
+          <t>Kilian Good girl gone Bad</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -15376,12 +15392,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>wieczorem zaś - piękny alkoholowy akcent</t>
+          <t>Zpach uniwersalny lecz</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>wieczorem zaś piękny, alkoholowy akcent</t>
+          <t>Zapach uniwersalny, lecz</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -15393,12 +15409,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>p93</t>
+          <t>p94</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Kilian Good girl gone Bad</t>
+          <t>Kilian Sparkling Royal</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -15408,12 +15424,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Zpach uniwersalny lecz</t>
+          <t>zyskuje.Zapach</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Zapach uniwersalny, lecz</t>
+          <t>zyskuje. Zapach</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -15435,22 +15451,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>zyskuje.Zapach</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>zyskuje. Zapach</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
@@ -15467,62 +15483,62 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>podobne</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>Xerjoff Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>p94</t>
+          <t>p95</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Kilian Sparkling Royal</t>
+          <t>Atkinsons Shine Despite Everything</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>podobne</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Xerjoff Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr"/>
+          <t>akcentami  kremowości</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>akcentami kremowości</t>
+        </is>
+      </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>p95</t>
+          <t>p96</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Atkinsons Shine Despite Everything</t>
+          <t>Atkinsons Oud Save the King</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -15532,12 +15548,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>akcentami  kremowości</t>
+          <t>Earl Greyspotyka</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>akcentami kremowości</t>
+          <t>Earl Grey spotyka</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -15549,44 +15565,44 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>p96</t>
+          <t>p97</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Atkinsons Oud Save the King</t>
+          <t>Atkinsons Mint &amp; Tonic</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Earl Greyspotyka</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Earl Grey spotyka</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>p97</t>
+          <t>p98</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Atkinsons Mint &amp; Tonic</t>
+          <t>Bohoboco Wet Cherry Liquor</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -15623,122 +15639,130 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>pewność danych: średnia</t>
+          <t>Owocowo-gourmand, w bazie drzewno-waniliowa</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>bez zmian</t>
+          <t>gourmand</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>p98</t>
+          <t>p99</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Bohoboco Wet Cherry Liquor</t>
+          <t>Sisley Soir d'Orient</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>rodzina</t>
+          <t>opis</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Owocowo-gourmand, w bazie drzewno-waniliowa</t>
+          <t>elegankiej</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>gourmand</t>
+          <t>eleganckiej</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>p98</t>
+          <t>p99</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Bohoboco Wet Cherry Liquor</t>
+          <t>Sisley Soir d'Orient</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>zdjecie_url</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr"/>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Przyprawowo-drzewna</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>drzewna</t>
+        </is>
+      </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>brak zdjęcia: strona producenta blokuje pobieranie, potrzebne własne albo prasowe</t>
+          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>p99</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Sisley Soir d'Orient</t>
+          <t>Bohoboco Vanilla Black Pepper</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>nuty / osiągi</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>elegankiej</t>
+          <t>pewność danych: średnia</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>eleganckiej</t>
+          <t>bez zmian</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>poprawiona literówka albo myślnik (zasady tekstów marki)</t>
+          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>p99</t>
+          <t>p100</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Sisley Soir d'Orient</t>
+          <t>Bohoboco Vanilla Black Pepper</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -15748,12 +15772,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Przyprawowo-drzewna</t>
+          <t>Korzenno-waniliowa, ambrowa</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>drzewna</t>
+          <t>ambrowa</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -15765,112 +15789,108 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>z01</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bohoboco Vanilla Black Pepper</t>
+          <t>LV DISCOVERY SET</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>nuty / osiągi</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>pewność danych: średnia</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>bez zmian</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>instrukcja arkusza: zweryfikować przed publikacją</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>p100</t>
+          <t>z01</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Bohoboco Vanilla Black Pepper</t>
+          <t>LV DISCOVERY SET</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>Korzenno-waniliowa, ambrowa</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>ambrowa</t>
-        </is>
-      </c>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>pierwszy człon spoza 12 rodzin kanonicznych, propozycja</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>z01</t>
+          <t>z02</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>LV DISCOVERY SET</t>
+          <t>XERJOFF DISCOVERY SET</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>5 × 5 ml (do ustalenia skład, sugerowane: Torino21, Renaissance, Erba Pura, Uden, Naxos)</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>p06:5, p07:5, p08:5, p09:5, p10:5</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>skład „do ustalenia”; wpisano propozycję ze źródła, zestaw wyłączony</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>z01</t>
+          <t>z02</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>LV DISCOVERY SET</t>
+          <t>XERJOFF DISCOVERY SET</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Renaissance -&gt; renaissance</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
@@ -15887,22 +15907,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>5 × 5 ml (do ustalenia skład, sugerowane: Torino21, Renaissance, Erba Pura, Uden, Naxos)</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>p06:5, p07:5, p08:5, p09:5, p10:5</t>
-        </is>
-      </c>
+          <t>rodzina</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>skład „do ustalenia”; wpisano propozycję ze źródła, zestaw wyłączony</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -15919,66 +15931,70 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Renaissance -&gt; renaissance</t>
-        </is>
-      </c>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>z03</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>NOUS TOUS DISCOVERY SET</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
+          <t>cena</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>350 zł</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>cena zapisana jako tekst</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>z02</t>
+          <t>z03</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>XERJOFF DISCOVERY SET</t>
+          <t>NOUS TOUS DISCOVERY SET</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -15995,70 +16011,74 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>cena</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>350 zł</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>cena zapisana jako tekst</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>z03</t>
+          <t>z04</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NOUS TOUS DISCOVERY SET</t>
+          <t>SWEET &amp; SPICY SET</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>p34</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>p98</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>zamiana na prośbę właściciela: zestaw ma być dostępny, a składnik ze źródła jest niedostępny</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>z03</t>
+          <t>z04</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>NOUS TOUS DISCOVERY SET</t>
+          <t>SWEET &amp; SPICY SET</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>gourmand</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>propozycja z opisu zestawu w źródle (gourmand wprost w treści)</t>
         </is>
       </c>
     </row>
@@ -16075,74 +16095,66 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>p34</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>p98</t>
-        </is>
-      </c>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
       <c r="F140" t="inlineStr">
         <is>
-          <t>zamiana na prośbę właściciela: zestaw ma być dostępny, a składnik ze źródła jest niedostępny</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>z04</t>
+          <t>z05</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SWEET &amp; SPICY SET</t>
+          <t>ENTRY SET</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>gourmand</t>
-        </is>
-      </c>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Amouage Reflection -&gt; reflection</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
       <c r="F141" t="inlineStr">
         <is>
-          <t>propozycja z opisu zestawu w źródle (gourmand wprost w treści)</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>z04</t>
+          <t>z05</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SWEET &amp; SPICY SET</t>
+          <t>ENTRY SET</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -16159,66 +16171,66 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>Amouage Reflection -&gt; reflection</t>
-        </is>
-      </c>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>z05</t>
+          <t>z06</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ENTRY SET</t>
+          <t>AUTUMN DISCOVERY SET</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>YSL Y le Parfum -&gt; y le parfum</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>z05</t>
+          <t>z06</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ENTRY SET</t>
+          <t>AUTUMN DISCOVERY SET</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -16235,66 +16247,70 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>YSL Y le Parfum -&gt; y le parfum</t>
-        </is>
-      </c>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>dopasowano po poprawce literówki albo skrótu nazwy</t>
+          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>z06</t>
+          <t>z07</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>AUTUMN DISCOVERY SET</t>
+          <t>WINTER DISCOVERY SET</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
+          <t>sklad</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>5x ml (BOSS Bottled Absolu, MFK Grand Soir, Maison Crivelli Oud Maracuja, Tom Ford Tobacco Vanille, Montale Arabians Tonka)</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>p60:5, p42:5, p41:5, p35:5, p28:5</t>
+        </is>
+      </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
+          <t>w źródle „5x ml” bez pojemności; przyjęto 5 ml</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>z06</t>
+          <t>z07</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>AUTUMN DISCOVERY SET</t>
+          <t>WINTER DISCOVERY SET</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>opis</t>
+          <t>rodzina</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
+          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
         </is>
       </c>
     </row>
@@ -16311,68 +16327,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>sklad</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>5x ml (BOSS Bottled Absolu, MFK Grand Soir, Maison Crivelli Oud Maracuja, Tom Ford Tobacco Vanille, Montale Arabians Tonka)</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>p60:5, p42:5, p41:5, p35:5, p28:5</t>
-        </is>
-      </c>
+          <t>opis</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
-        <is>
-          <t>w źródle „5x ml” bez pojemności; przyjęto 5 ml</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>z07</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>WINTER DISCOVERY SET</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>rodzina</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>brak rodziny: quiz nie zaproponuje tego zestawu</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>z07</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>WINTER DISCOVERY SET</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>opis</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr">
         <is>
           <t>źródło ma tylko opis pozycjonowania dla doradcy; opis dla klienta do napisania</t>
         </is>
